--- a/Second-Draft-catalogue.xlsx
+++ b/Second-Draft-catalogue.xlsx
@@ -14,7 +14,7 @@
     <sheet name="Room list" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Products'!$A$1:$Q$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Products'!$A$1:$R$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q399"/>
+  <dimension ref="A1:R399"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -509,10 +509,11 @@
     <col width="30" customWidth="1" min="11" max="11"/>
     <col width="30" customWidth="1" min="12" max="12"/>
     <col width="42" customWidth="1" min="13" max="13"/>
-    <col width="38" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="30" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="38" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="30" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -583,20 +584,25 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>image_file</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>product_url</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>in_stock</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>lead_time_days</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -660,20 +666,21 @@
           <t>https://eleganza.example/img/marlow-bed.jpg</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr"/>
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://eleganza.example/p/marlow-bed</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="P2" s="2" t="n">
+      <c r="Q2" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="R2" s="2" t="inlineStr">
         <is>
           <t>King size</t>
         </is>
@@ -732,25 +739,26 @@
           <t>bedroom</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>https://eleganza.example/img/hale-wardrobe.jpg</t>
-        </is>
-      </c>
+      <c r="M3" s="2" t="inlineStr"/>
       <c r="N3" s="2" t="inlineStr">
         <is>
+          <t>hale-wardrobe-2400.jpg</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
           <t>https://eleganza.example/p/hale-wardrobe</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="P3" s="2" t="n">
+      <c r="Q3" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="R3" s="2" t="inlineStr">
         <is>
           <t>Two-door sliding</t>
         </is>
@@ -814,20 +822,21 @@
           <t>https://eleganza.example/img/fenn-desk.jpg</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr"/>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>https://eleganza.example/p/fenn-desk</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="P4" s="2" t="n">
+      <c r="Q4" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="Q4" s="2" t="inlineStr"/>
+      <c r="R4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n"/>
@@ -842,11 +851,12 @@
       <c r="J5" s="4" t="n"/>
       <c r="K5" s="4" t="n"/>
       <c r="L5" s="4" t="n"/>
-      <c r="M5" s="3" t="n"/>
+      <c r="M5" s="4" t="n"/>
       <c r="N5" s="4" t="n"/>
       <c r="O5" s="4" t="n"/>
       <c r="P5" s="4" t="n"/>
       <c r="Q5" s="4" t="n"/>
+      <c r="R5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n"/>
@@ -861,11 +871,12 @@
       <c r="J6" s="4" t="n"/>
       <c r="K6" s="4" t="n"/>
       <c r="L6" s="4" t="n"/>
-      <c r="M6" s="3" t="n"/>
+      <c r="M6" s="4" t="n"/>
       <c r="N6" s="4" t="n"/>
       <c r="O6" s="4" t="n"/>
       <c r="P6" s="4" t="n"/>
       <c r="Q6" s="4" t="n"/>
+      <c r="R6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n"/>
@@ -880,11 +891,12 @@
       <c r="J7" s="4" t="n"/>
       <c r="K7" s="4" t="n"/>
       <c r="L7" s="4" t="n"/>
-      <c r="M7" s="3" t="n"/>
+      <c r="M7" s="4" t="n"/>
       <c r="N7" s="4" t="n"/>
       <c r="O7" s="4" t="n"/>
       <c r="P7" s="4" t="n"/>
       <c r="Q7" s="4" t="n"/>
+      <c r="R7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n"/>
@@ -899,11 +911,12 @@
       <c r="J8" s="4" t="n"/>
       <c r="K8" s="4" t="n"/>
       <c r="L8" s="4" t="n"/>
-      <c r="M8" s="3" t="n"/>
+      <c r="M8" s="4" t="n"/>
       <c r="N8" s="4" t="n"/>
       <c r="O8" s="4" t="n"/>
       <c r="P8" s="4" t="n"/>
       <c r="Q8" s="4" t="n"/>
+      <c r="R8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n"/>
@@ -918,11 +931,12 @@
       <c r="J9" s="4" t="n"/>
       <c r="K9" s="4" t="n"/>
       <c r="L9" s="4" t="n"/>
-      <c r="M9" s="3" t="n"/>
+      <c r="M9" s="4" t="n"/>
       <c r="N9" s="4" t="n"/>
       <c r="O9" s="4" t="n"/>
       <c r="P9" s="4" t="n"/>
       <c r="Q9" s="4" t="n"/>
+      <c r="R9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n"/>
@@ -937,11 +951,12 @@
       <c r="J10" s="4" t="n"/>
       <c r="K10" s="4" t="n"/>
       <c r="L10" s="4" t="n"/>
-      <c r="M10" s="3" t="n"/>
+      <c r="M10" s="4" t="n"/>
       <c r="N10" s="4" t="n"/>
       <c r="O10" s="4" t="n"/>
       <c r="P10" s="4" t="n"/>
       <c r="Q10" s="4" t="n"/>
+      <c r="R10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n"/>
@@ -956,11 +971,12 @@
       <c r="J11" s="4" t="n"/>
       <c r="K11" s="4" t="n"/>
       <c r="L11" s="4" t="n"/>
-      <c r="M11" s="3" t="n"/>
+      <c r="M11" s="4" t="n"/>
       <c r="N11" s="4" t="n"/>
       <c r="O11" s="4" t="n"/>
       <c r="P11" s="4" t="n"/>
       <c r="Q11" s="4" t="n"/>
+      <c r="R11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n"/>
@@ -975,11 +991,12 @@
       <c r="J12" s="4" t="n"/>
       <c r="K12" s="4" t="n"/>
       <c r="L12" s="4" t="n"/>
-      <c r="M12" s="3" t="n"/>
+      <c r="M12" s="4" t="n"/>
       <c r="N12" s="4" t="n"/>
       <c r="O12" s="4" t="n"/>
       <c r="P12" s="4" t="n"/>
       <c r="Q12" s="4" t="n"/>
+      <c r="R12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n"/>
@@ -994,11 +1011,12 @@
       <c r="J13" s="4" t="n"/>
       <c r="K13" s="4" t="n"/>
       <c r="L13" s="4" t="n"/>
-      <c r="M13" s="3" t="n"/>
+      <c r="M13" s="4" t="n"/>
       <c r="N13" s="4" t="n"/>
       <c r="O13" s="4" t="n"/>
       <c r="P13" s="4" t="n"/>
       <c r="Q13" s="4" t="n"/>
+      <c r="R13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n"/>
@@ -1013,11 +1031,12 @@
       <c r="J14" s="4" t="n"/>
       <c r="K14" s="4" t="n"/>
       <c r="L14" s="4" t="n"/>
-      <c r="M14" s="3" t="n"/>
+      <c r="M14" s="4" t="n"/>
       <c r="N14" s="4" t="n"/>
       <c r="O14" s="4" t="n"/>
       <c r="P14" s="4" t="n"/>
       <c r="Q14" s="4" t="n"/>
+      <c r="R14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n"/>
@@ -1032,11 +1051,12 @@
       <c r="J15" s="4" t="n"/>
       <c r="K15" s="4" t="n"/>
       <c r="L15" s="4" t="n"/>
-      <c r="M15" s="3" t="n"/>
+      <c r="M15" s="4" t="n"/>
       <c r="N15" s="4" t="n"/>
       <c r="O15" s="4" t="n"/>
       <c r="P15" s="4" t="n"/>
       <c r="Q15" s="4" t="n"/>
+      <c r="R15" s="4" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n"/>
@@ -1051,11 +1071,12 @@
       <c r="J16" s="4" t="n"/>
       <c r="K16" s="4" t="n"/>
       <c r="L16" s="4" t="n"/>
-      <c r="M16" s="3" t="n"/>
+      <c r="M16" s="4" t="n"/>
       <c r="N16" s="4" t="n"/>
       <c r="O16" s="4" t="n"/>
       <c r="P16" s="4" t="n"/>
       <c r="Q16" s="4" t="n"/>
+      <c r="R16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n"/>
@@ -1070,11 +1091,12 @@
       <c r="J17" s="4" t="n"/>
       <c r="K17" s="4" t="n"/>
       <c r="L17" s="4" t="n"/>
-      <c r="M17" s="3" t="n"/>
+      <c r="M17" s="4" t="n"/>
       <c r="N17" s="4" t="n"/>
       <c r="O17" s="4" t="n"/>
       <c r="P17" s="4" t="n"/>
       <c r="Q17" s="4" t="n"/>
+      <c r="R17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n"/>
@@ -1089,11 +1111,12 @@
       <c r="J18" s="4" t="n"/>
       <c r="K18" s="4" t="n"/>
       <c r="L18" s="4" t="n"/>
-      <c r="M18" s="3" t="n"/>
+      <c r="M18" s="4" t="n"/>
       <c r="N18" s="4" t="n"/>
       <c r="O18" s="4" t="n"/>
       <c r="P18" s="4" t="n"/>
       <c r="Q18" s="4" t="n"/>
+      <c r="R18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n"/>
@@ -1108,11 +1131,12 @@
       <c r="J19" s="4" t="n"/>
       <c r="K19" s="4" t="n"/>
       <c r="L19" s="4" t="n"/>
-      <c r="M19" s="3" t="n"/>
+      <c r="M19" s="4" t="n"/>
       <c r="N19" s="4" t="n"/>
       <c r="O19" s="4" t="n"/>
       <c r="P19" s="4" t="n"/>
       <c r="Q19" s="4" t="n"/>
+      <c r="R19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n"/>
@@ -1127,11 +1151,12 @@
       <c r="J20" s="4" t="n"/>
       <c r="K20" s="4" t="n"/>
       <c r="L20" s="4" t="n"/>
-      <c r="M20" s="3" t="n"/>
+      <c r="M20" s="4" t="n"/>
       <c r="N20" s="4" t="n"/>
       <c r="O20" s="4" t="n"/>
       <c r="P20" s="4" t="n"/>
       <c r="Q20" s="4" t="n"/>
+      <c r="R20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n"/>
@@ -1146,11 +1171,12 @@
       <c r="J21" s="4" t="n"/>
       <c r="K21" s="4" t="n"/>
       <c r="L21" s="4" t="n"/>
-      <c r="M21" s="3" t="n"/>
+      <c r="M21" s="4" t="n"/>
       <c r="N21" s="4" t="n"/>
       <c r="O21" s="4" t="n"/>
       <c r="P21" s="4" t="n"/>
       <c r="Q21" s="4" t="n"/>
+      <c r="R21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n"/>
@@ -1165,11 +1191,12 @@
       <c r="J22" s="4" t="n"/>
       <c r="K22" s="4" t="n"/>
       <c r="L22" s="4" t="n"/>
-      <c r="M22" s="3" t="n"/>
+      <c r="M22" s="4" t="n"/>
       <c r="N22" s="4" t="n"/>
       <c r="O22" s="4" t="n"/>
       <c r="P22" s="4" t="n"/>
       <c r="Q22" s="4" t="n"/>
+      <c r="R22" s="4" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n"/>
@@ -1184,11 +1211,12 @@
       <c r="J23" s="4" t="n"/>
       <c r="K23" s="4" t="n"/>
       <c r="L23" s="4" t="n"/>
-      <c r="M23" s="3" t="n"/>
+      <c r="M23" s="4" t="n"/>
       <c r="N23" s="4" t="n"/>
       <c r="O23" s="4" t="n"/>
       <c r="P23" s="4" t="n"/>
       <c r="Q23" s="4" t="n"/>
+      <c r="R23" s="4" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n"/>
@@ -1203,11 +1231,12 @@
       <c r="J24" s="4" t="n"/>
       <c r="K24" s="4" t="n"/>
       <c r="L24" s="4" t="n"/>
-      <c r="M24" s="3" t="n"/>
+      <c r="M24" s="4" t="n"/>
       <c r="N24" s="4" t="n"/>
       <c r="O24" s="4" t="n"/>
       <c r="P24" s="4" t="n"/>
       <c r="Q24" s="4" t="n"/>
+      <c r="R24" s="4" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n"/>
@@ -1222,11 +1251,12 @@
       <c r="J25" s="4" t="n"/>
       <c r="K25" s="4" t="n"/>
       <c r="L25" s="4" t="n"/>
-      <c r="M25" s="3" t="n"/>
+      <c r="M25" s="4" t="n"/>
       <c r="N25" s="4" t="n"/>
       <c r="O25" s="4" t="n"/>
       <c r="P25" s="4" t="n"/>
       <c r="Q25" s="4" t="n"/>
+      <c r="R25" s="4" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n"/>
@@ -1241,11 +1271,12 @@
       <c r="J26" s="4" t="n"/>
       <c r="K26" s="4" t="n"/>
       <c r="L26" s="4" t="n"/>
-      <c r="M26" s="3" t="n"/>
+      <c r="M26" s="4" t="n"/>
       <c r="N26" s="4" t="n"/>
       <c r="O26" s="4" t="n"/>
       <c r="P26" s="4" t="n"/>
       <c r="Q26" s="4" t="n"/>
+      <c r="R26" s="4" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n"/>
@@ -1260,11 +1291,12 @@
       <c r="J27" s="4" t="n"/>
       <c r="K27" s="4" t="n"/>
       <c r="L27" s="4" t="n"/>
-      <c r="M27" s="3" t="n"/>
+      <c r="M27" s="4" t="n"/>
       <c r="N27" s="4" t="n"/>
       <c r="O27" s="4" t="n"/>
       <c r="P27" s="4" t="n"/>
       <c r="Q27" s="4" t="n"/>
+      <c r="R27" s="4" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n"/>
@@ -1279,11 +1311,12 @@
       <c r="J28" s="4" t="n"/>
       <c r="K28" s="4" t="n"/>
       <c r="L28" s="4" t="n"/>
-      <c r="M28" s="3" t="n"/>
+      <c r="M28" s="4" t="n"/>
       <c r="N28" s="4" t="n"/>
       <c r="O28" s="4" t="n"/>
       <c r="P28" s="4" t="n"/>
       <c r="Q28" s="4" t="n"/>
+      <c r="R28" s="4" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n"/>
@@ -1298,11 +1331,12 @@
       <c r="J29" s="4" t="n"/>
       <c r="K29" s="4" t="n"/>
       <c r="L29" s="4" t="n"/>
-      <c r="M29" s="3" t="n"/>
+      <c r="M29" s="4" t="n"/>
       <c r="N29" s="4" t="n"/>
       <c r="O29" s="4" t="n"/>
       <c r="P29" s="4" t="n"/>
       <c r="Q29" s="4" t="n"/>
+      <c r="R29" s="4" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n"/>
@@ -1317,11 +1351,12 @@
       <c r="J30" s="4" t="n"/>
       <c r="K30" s="4" t="n"/>
       <c r="L30" s="4" t="n"/>
-      <c r="M30" s="3" t="n"/>
+      <c r="M30" s="4" t="n"/>
       <c r="N30" s="4" t="n"/>
       <c r="O30" s="4" t="n"/>
       <c r="P30" s="4" t="n"/>
       <c r="Q30" s="4" t="n"/>
+      <c r="R30" s="4" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n"/>
@@ -1336,11 +1371,12 @@
       <c r="J31" s="4" t="n"/>
       <c r="K31" s="4" t="n"/>
       <c r="L31" s="4" t="n"/>
-      <c r="M31" s="3" t="n"/>
+      <c r="M31" s="4" t="n"/>
       <c r="N31" s="4" t="n"/>
       <c r="O31" s="4" t="n"/>
       <c r="P31" s="4" t="n"/>
       <c r="Q31" s="4" t="n"/>
+      <c r="R31" s="4" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n"/>
@@ -1355,11 +1391,12 @@
       <c r="J32" s="4" t="n"/>
       <c r="K32" s="4" t="n"/>
       <c r="L32" s="4" t="n"/>
-      <c r="M32" s="3" t="n"/>
+      <c r="M32" s="4" t="n"/>
       <c r="N32" s="4" t="n"/>
       <c r="O32" s="4" t="n"/>
       <c r="P32" s="4" t="n"/>
       <c r="Q32" s="4" t="n"/>
+      <c r="R32" s="4" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n"/>
@@ -1374,11 +1411,12 @@
       <c r="J33" s="4" t="n"/>
       <c r="K33" s="4" t="n"/>
       <c r="L33" s="4" t="n"/>
-      <c r="M33" s="3" t="n"/>
+      <c r="M33" s="4" t="n"/>
       <c r="N33" s="4" t="n"/>
       <c r="O33" s="4" t="n"/>
       <c r="P33" s="4" t="n"/>
       <c r="Q33" s="4" t="n"/>
+      <c r="R33" s="4" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n"/>
@@ -1393,11 +1431,12 @@
       <c r="J34" s="4" t="n"/>
       <c r="K34" s="4" t="n"/>
       <c r="L34" s="4" t="n"/>
-      <c r="M34" s="3" t="n"/>
+      <c r="M34" s="4" t="n"/>
       <c r="N34" s="4" t="n"/>
       <c r="O34" s="4" t="n"/>
       <c r="P34" s="4" t="n"/>
       <c r="Q34" s="4" t="n"/>
+      <c r="R34" s="4" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n"/>
@@ -1412,11 +1451,12 @@
       <c r="J35" s="4" t="n"/>
       <c r="K35" s="4" t="n"/>
       <c r="L35" s="4" t="n"/>
-      <c r="M35" s="3" t="n"/>
+      <c r="M35" s="4" t="n"/>
       <c r="N35" s="4" t="n"/>
       <c r="O35" s="4" t="n"/>
       <c r="P35" s="4" t="n"/>
       <c r="Q35" s="4" t="n"/>
+      <c r="R35" s="4" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n"/>
@@ -1431,11 +1471,12 @@
       <c r="J36" s="4" t="n"/>
       <c r="K36" s="4" t="n"/>
       <c r="L36" s="4" t="n"/>
-      <c r="M36" s="3" t="n"/>
+      <c r="M36" s="4" t="n"/>
       <c r="N36" s="4" t="n"/>
       <c r="O36" s="4" t="n"/>
       <c r="P36" s="4" t="n"/>
       <c r="Q36" s="4" t="n"/>
+      <c r="R36" s="4" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n"/>
@@ -1450,11 +1491,12 @@
       <c r="J37" s="4" t="n"/>
       <c r="K37" s="4" t="n"/>
       <c r="L37" s="4" t="n"/>
-      <c r="M37" s="3" t="n"/>
+      <c r="M37" s="4" t="n"/>
       <c r="N37" s="4" t="n"/>
       <c r="O37" s="4" t="n"/>
       <c r="P37" s="4" t="n"/>
       <c r="Q37" s="4" t="n"/>
+      <c r="R37" s="4" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n"/>
@@ -1469,11 +1511,12 @@
       <c r="J38" s="4" t="n"/>
       <c r="K38" s="4" t="n"/>
       <c r="L38" s="4" t="n"/>
-      <c r="M38" s="3" t="n"/>
+      <c r="M38" s="4" t="n"/>
       <c r="N38" s="4" t="n"/>
       <c r="O38" s="4" t="n"/>
       <c r="P38" s="4" t="n"/>
       <c r="Q38" s="4" t="n"/>
+      <c r="R38" s="4" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n"/>
@@ -1488,11 +1531,12 @@
       <c r="J39" s="4" t="n"/>
       <c r="K39" s="4" t="n"/>
       <c r="L39" s="4" t="n"/>
-      <c r="M39" s="3" t="n"/>
+      <c r="M39" s="4" t="n"/>
       <c r="N39" s="4" t="n"/>
       <c r="O39" s="4" t="n"/>
       <c r="P39" s="4" t="n"/>
       <c r="Q39" s="4" t="n"/>
+      <c r="R39" s="4" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n"/>
@@ -1507,11 +1551,12 @@
       <c r="J40" s="4" t="n"/>
       <c r="K40" s="4" t="n"/>
       <c r="L40" s="4" t="n"/>
-      <c r="M40" s="3" t="n"/>
+      <c r="M40" s="4" t="n"/>
       <c r="N40" s="4" t="n"/>
       <c r="O40" s="4" t="n"/>
       <c r="P40" s="4" t="n"/>
       <c r="Q40" s="4" t="n"/>
+      <c r="R40" s="4" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n"/>
@@ -1526,11 +1571,12 @@
       <c r="J41" s="4" t="n"/>
       <c r="K41" s="4" t="n"/>
       <c r="L41" s="4" t="n"/>
-      <c r="M41" s="3" t="n"/>
+      <c r="M41" s="4" t="n"/>
       <c r="N41" s="4" t="n"/>
       <c r="O41" s="4" t="n"/>
       <c r="P41" s="4" t="n"/>
       <c r="Q41" s="4" t="n"/>
+      <c r="R41" s="4" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n"/>
@@ -1545,11 +1591,12 @@
       <c r="J42" s="4" t="n"/>
       <c r="K42" s="4" t="n"/>
       <c r="L42" s="4" t="n"/>
-      <c r="M42" s="3" t="n"/>
+      <c r="M42" s="4" t="n"/>
       <c r="N42" s="4" t="n"/>
       <c r="O42" s="4" t="n"/>
       <c r="P42" s="4" t="n"/>
       <c r="Q42" s="4" t="n"/>
+      <c r="R42" s="4" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n"/>
@@ -1564,11 +1611,12 @@
       <c r="J43" s="4" t="n"/>
       <c r="K43" s="4" t="n"/>
       <c r="L43" s="4" t="n"/>
-      <c r="M43" s="3" t="n"/>
+      <c r="M43" s="4" t="n"/>
       <c r="N43" s="4" t="n"/>
       <c r="O43" s="4" t="n"/>
       <c r="P43" s="4" t="n"/>
       <c r="Q43" s="4" t="n"/>
+      <c r="R43" s="4" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n"/>
@@ -1583,11 +1631,12 @@
       <c r="J44" s="4" t="n"/>
       <c r="K44" s="4" t="n"/>
       <c r="L44" s="4" t="n"/>
-      <c r="M44" s="3" t="n"/>
+      <c r="M44" s="4" t="n"/>
       <c r="N44" s="4" t="n"/>
       <c r="O44" s="4" t="n"/>
       <c r="P44" s="4" t="n"/>
       <c r="Q44" s="4" t="n"/>
+      <c r="R44" s="4" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n"/>
@@ -1602,11 +1651,12 @@
       <c r="J45" s="4" t="n"/>
       <c r="K45" s="4" t="n"/>
       <c r="L45" s="4" t="n"/>
-      <c r="M45" s="3" t="n"/>
+      <c r="M45" s="4" t="n"/>
       <c r="N45" s="4" t="n"/>
       <c r="O45" s="4" t="n"/>
       <c r="P45" s="4" t="n"/>
       <c r="Q45" s="4" t="n"/>
+      <c r="R45" s="4" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n"/>
@@ -1621,11 +1671,12 @@
       <c r="J46" s="4" t="n"/>
       <c r="K46" s="4" t="n"/>
       <c r="L46" s="4" t="n"/>
-      <c r="M46" s="3" t="n"/>
+      <c r="M46" s="4" t="n"/>
       <c r="N46" s="4" t="n"/>
       <c r="O46" s="4" t="n"/>
       <c r="P46" s="4" t="n"/>
       <c r="Q46" s="4" t="n"/>
+      <c r="R46" s="4" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n"/>
@@ -1640,11 +1691,12 @@
       <c r="J47" s="4" t="n"/>
       <c r="K47" s="4" t="n"/>
       <c r="L47" s="4" t="n"/>
-      <c r="M47" s="3" t="n"/>
+      <c r="M47" s="4" t="n"/>
       <c r="N47" s="4" t="n"/>
       <c r="O47" s="4" t="n"/>
       <c r="P47" s="4" t="n"/>
       <c r="Q47" s="4" t="n"/>
+      <c r="R47" s="4" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n"/>
@@ -1659,11 +1711,12 @@
       <c r="J48" s="4" t="n"/>
       <c r="K48" s="4" t="n"/>
       <c r="L48" s="4" t="n"/>
-      <c r="M48" s="3" t="n"/>
+      <c r="M48" s="4" t="n"/>
       <c r="N48" s="4" t="n"/>
       <c r="O48" s="4" t="n"/>
       <c r="P48" s="4" t="n"/>
       <c r="Q48" s="4" t="n"/>
+      <c r="R48" s="4" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n"/>
@@ -1678,11 +1731,12 @@
       <c r="J49" s="4" t="n"/>
       <c r="K49" s="4" t="n"/>
       <c r="L49" s="4" t="n"/>
-      <c r="M49" s="3" t="n"/>
+      <c r="M49" s="4" t="n"/>
       <c r="N49" s="4" t="n"/>
       <c r="O49" s="4" t="n"/>
       <c r="P49" s="4" t="n"/>
       <c r="Q49" s="4" t="n"/>
+      <c r="R49" s="4" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n"/>
@@ -1697,11 +1751,12 @@
       <c r="J50" s="4" t="n"/>
       <c r="K50" s="4" t="n"/>
       <c r="L50" s="4" t="n"/>
-      <c r="M50" s="3" t="n"/>
+      <c r="M50" s="4" t="n"/>
       <c r="N50" s="4" t="n"/>
       <c r="O50" s="4" t="n"/>
       <c r="P50" s="4" t="n"/>
       <c r="Q50" s="4" t="n"/>
+      <c r="R50" s="4" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n"/>
@@ -1716,11 +1771,12 @@
       <c r="J51" s="4" t="n"/>
       <c r="K51" s="4" t="n"/>
       <c r="L51" s="4" t="n"/>
-      <c r="M51" s="3" t="n"/>
+      <c r="M51" s="4" t="n"/>
       <c r="N51" s="4" t="n"/>
       <c r="O51" s="4" t="n"/>
       <c r="P51" s="4" t="n"/>
       <c r="Q51" s="4" t="n"/>
+      <c r="R51" s="4" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n"/>
@@ -1735,11 +1791,12 @@
       <c r="J52" s="4" t="n"/>
       <c r="K52" s="4" t="n"/>
       <c r="L52" s="4" t="n"/>
-      <c r="M52" s="3" t="n"/>
+      <c r="M52" s="4" t="n"/>
       <c r="N52" s="4" t="n"/>
       <c r="O52" s="4" t="n"/>
       <c r="P52" s="4" t="n"/>
       <c r="Q52" s="4" t="n"/>
+      <c r="R52" s="4" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n"/>
@@ -1754,11 +1811,12 @@
       <c r="J53" s="4" t="n"/>
       <c r="K53" s="4" t="n"/>
       <c r="L53" s="4" t="n"/>
-      <c r="M53" s="3" t="n"/>
+      <c r="M53" s="4" t="n"/>
       <c r="N53" s="4" t="n"/>
       <c r="O53" s="4" t="n"/>
       <c r="P53" s="4" t="n"/>
       <c r="Q53" s="4" t="n"/>
+      <c r="R53" s="4" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n"/>
@@ -1773,11 +1831,12 @@
       <c r="J54" s="4" t="n"/>
       <c r="K54" s="4" t="n"/>
       <c r="L54" s="4" t="n"/>
-      <c r="M54" s="3" t="n"/>
+      <c r="M54" s="4" t="n"/>
       <c r="N54" s="4" t="n"/>
       <c r="O54" s="4" t="n"/>
       <c r="P54" s="4" t="n"/>
       <c r="Q54" s="4" t="n"/>
+      <c r="R54" s="4" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n"/>
@@ -1792,11 +1851,12 @@
       <c r="J55" s="4" t="n"/>
       <c r="K55" s="4" t="n"/>
       <c r="L55" s="4" t="n"/>
-      <c r="M55" s="3" t="n"/>
+      <c r="M55" s="4" t="n"/>
       <c r="N55" s="4" t="n"/>
       <c r="O55" s="4" t="n"/>
       <c r="P55" s="4" t="n"/>
       <c r="Q55" s="4" t="n"/>
+      <c r="R55" s="4" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n"/>
@@ -1811,11 +1871,12 @@
       <c r="J56" s="4" t="n"/>
       <c r="K56" s="4" t="n"/>
       <c r="L56" s="4" t="n"/>
-      <c r="M56" s="3" t="n"/>
+      <c r="M56" s="4" t="n"/>
       <c r="N56" s="4" t="n"/>
       <c r="O56" s="4" t="n"/>
       <c r="P56" s="4" t="n"/>
       <c r="Q56" s="4" t="n"/>
+      <c r="R56" s="4" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n"/>
@@ -1830,11 +1891,12 @@
       <c r="J57" s="4" t="n"/>
       <c r="K57" s="4" t="n"/>
       <c r="L57" s="4" t="n"/>
-      <c r="M57" s="3" t="n"/>
+      <c r="M57" s="4" t="n"/>
       <c r="N57" s="4" t="n"/>
       <c r="O57" s="4" t="n"/>
       <c r="P57" s="4" t="n"/>
       <c r="Q57" s="4" t="n"/>
+      <c r="R57" s="4" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n"/>
@@ -1849,11 +1911,12 @@
       <c r="J58" s="4" t="n"/>
       <c r="K58" s="4" t="n"/>
       <c r="L58" s="4" t="n"/>
-      <c r="M58" s="3" t="n"/>
+      <c r="M58" s="4" t="n"/>
       <c r="N58" s="4" t="n"/>
       <c r="O58" s="4" t="n"/>
       <c r="P58" s="4" t="n"/>
       <c r="Q58" s="4" t="n"/>
+      <c r="R58" s="4" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n"/>
@@ -1868,11 +1931,12 @@
       <c r="J59" s="4" t="n"/>
       <c r="K59" s="4" t="n"/>
       <c r="L59" s="4" t="n"/>
-      <c r="M59" s="3" t="n"/>
+      <c r="M59" s="4" t="n"/>
       <c r="N59" s="4" t="n"/>
       <c r="O59" s="4" t="n"/>
       <c r="P59" s="4" t="n"/>
       <c r="Q59" s="4" t="n"/>
+      <c r="R59" s="4" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n"/>
@@ -1887,11 +1951,12 @@
       <c r="J60" s="4" t="n"/>
       <c r="K60" s="4" t="n"/>
       <c r="L60" s="4" t="n"/>
-      <c r="M60" s="3" t="n"/>
+      <c r="M60" s="4" t="n"/>
       <c r="N60" s="4" t="n"/>
       <c r="O60" s="4" t="n"/>
       <c r="P60" s="4" t="n"/>
       <c r="Q60" s="4" t="n"/>
+      <c r="R60" s="4" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n"/>
@@ -1906,11 +1971,12 @@
       <c r="J61" s="4" t="n"/>
       <c r="K61" s="4" t="n"/>
       <c r="L61" s="4" t="n"/>
-      <c r="M61" s="3" t="n"/>
+      <c r="M61" s="4" t="n"/>
       <c r="N61" s="4" t="n"/>
       <c r="O61" s="4" t="n"/>
       <c r="P61" s="4" t="n"/>
       <c r="Q61" s="4" t="n"/>
+      <c r="R61" s="4" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n"/>
@@ -1925,11 +1991,12 @@
       <c r="J62" s="4" t="n"/>
       <c r="K62" s="4" t="n"/>
       <c r="L62" s="4" t="n"/>
-      <c r="M62" s="3" t="n"/>
+      <c r="M62" s="4" t="n"/>
       <c r="N62" s="4" t="n"/>
       <c r="O62" s="4" t="n"/>
       <c r="P62" s="4" t="n"/>
       <c r="Q62" s="4" t="n"/>
+      <c r="R62" s="4" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n"/>
@@ -1944,11 +2011,12 @@
       <c r="J63" s="4" t="n"/>
       <c r="K63" s="4" t="n"/>
       <c r="L63" s="4" t="n"/>
-      <c r="M63" s="3" t="n"/>
+      <c r="M63" s="4" t="n"/>
       <c r="N63" s="4" t="n"/>
       <c r="O63" s="4" t="n"/>
       <c r="P63" s="4" t="n"/>
       <c r="Q63" s="4" t="n"/>
+      <c r="R63" s="4" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n"/>
@@ -1963,11 +2031,12 @@
       <c r="J64" s="4" t="n"/>
       <c r="K64" s="4" t="n"/>
       <c r="L64" s="4" t="n"/>
-      <c r="M64" s="3" t="n"/>
+      <c r="M64" s="4" t="n"/>
       <c r="N64" s="4" t="n"/>
       <c r="O64" s="4" t="n"/>
       <c r="P64" s="4" t="n"/>
       <c r="Q64" s="4" t="n"/>
+      <c r="R64" s="4" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n"/>
@@ -1982,11 +2051,12 @@
       <c r="J65" s="4" t="n"/>
       <c r="K65" s="4" t="n"/>
       <c r="L65" s="4" t="n"/>
-      <c r="M65" s="3" t="n"/>
+      <c r="M65" s="4" t="n"/>
       <c r="N65" s="4" t="n"/>
       <c r="O65" s="4" t="n"/>
       <c r="P65" s="4" t="n"/>
       <c r="Q65" s="4" t="n"/>
+      <c r="R65" s="4" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n"/>
@@ -2001,11 +2071,12 @@
       <c r="J66" s="4" t="n"/>
       <c r="K66" s="4" t="n"/>
       <c r="L66" s="4" t="n"/>
-      <c r="M66" s="3" t="n"/>
+      <c r="M66" s="4" t="n"/>
       <c r="N66" s="4" t="n"/>
       <c r="O66" s="4" t="n"/>
       <c r="P66" s="4" t="n"/>
       <c r="Q66" s="4" t="n"/>
+      <c r="R66" s="4" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n"/>
@@ -2020,11 +2091,12 @@
       <c r="J67" s="4" t="n"/>
       <c r="K67" s="4" t="n"/>
       <c r="L67" s="4" t="n"/>
-      <c r="M67" s="3" t="n"/>
+      <c r="M67" s="4" t="n"/>
       <c r="N67" s="4" t="n"/>
       <c r="O67" s="4" t="n"/>
       <c r="P67" s="4" t="n"/>
       <c r="Q67" s="4" t="n"/>
+      <c r="R67" s="4" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n"/>
@@ -2039,11 +2111,12 @@
       <c r="J68" s="4" t="n"/>
       <c r="K68" s="4" t="n"/>
       <c r="L68" s="4" t="n"/>
-      <c r="M68" s="3" t="n"/>
+      <c r="M68" s="4" t="n"/>
       <c r="N68" s="4" t="n"/>
       <c r="O68" s="4" t="n"/>
       <c r="P68" s="4" t="n"/>
       <c r="Q68" s="4" t="n"/>
+      <c r="R68" s="4" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n"/>
@@ -2058,11 +2131,12 @@
       <c r="J69" s="4" t="n"/>
       <c r="K69" s="4" t="n"/>
       <c r="L69" s="4" t="n"/>
-      <c r="M69" s="3" t="n"/>
+      <c r="M69" s="4" t="n"/>
       <c r="N69" s="4" t="n"/>
       <c r="O69" s="4" t="n"/>
       <c r="P69" s="4" t="n"/>
       <c r="Q69" s="4" t="n"/>
+      <c r="R69" s="4" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n"/>
@@ -2077,11 +2151,12 @@
       <c r="J70" s="4" t="n"/>
       <c r="K70" s="4" t="n"/>
       <c r="L70" s="4" t="n"/>
-      <c r="M70" s="3" t="n"/>
+      <c r="M70" s="4" t="n"/>
       <c r="N70" s="4" t="n"/>
       <c r="O70" s="4" t="n"/>
       <c r="P70" s="4" t="n"/>
       <c r="Q70" s="4" t="n"/>
+      <c r="R70" s="4" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n"/>
@@ -2096,11 +2171,12 @@
       <c r="J71" s="4" t="n"/>
       <c r="K71" s="4" t="n"/>
       <c r="L71" s="4" t="n"/>
-      <c r="M71" s="3" t="n"/>
+      <c r="M71" s="4" t="n"/>
       <c r="N71" s="4" t="n"/>
       <c r="O71" s="4" t="n"/>
       <c r="P71" s="4" t="n"/>
       <c r="Q71" s="4" t="n"/>
+      <c r="R71" s="4" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n"/>
@@ -2115,11 +2191,12 @@
       <c r="J72" s="4" t="n"/>
       <c r="K72" s="4" t="n"/>
       <c r="L72" s="4" t="n"/>
-      <c r="M72" s="3" t="n"/>
+      <c r="M72" s="4" t="n"/>
       <c r="N72" s="4" t="n"/>
       <c r="O72" s="4" t="n"/>
       <c r="P72" s="4" t="n"/>
       <c r="Q72" s="4" t="n"/>
+      <c r="R72" s="4" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n"/>
@@ -2134,11 +2211,12 @@
       <c r="J73" s="4" t="n"/>
       <c r="K73" s="4" t="n"/>
       <c r="L73" s="4" t="n"/>
-      <c r="M73" s="3" t="n"/>
+      <c r="M73" s="4" t="n"/>
       <c r="N73" s="4" t="n"/>
       <c r="O73" s="4" t="n"/>
       <c r="P73" s="4" t="n"/>
       <c r="Q73" s="4" t="n"/>
+      <c r="R73" s="4" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n"/>
@@ -2153,11 +2231,12 @@
       <c r="J74" s="4" t="n"/>
       <c r="K74" s="4" t="n"/>
       <c r="L74" s="4" t="n"/>
-      <c r="M74" s="3" t="n"/>
+      <c r="M74" s="4" t="n"/>
       <c r="N74" s="4" t="n"/>
       <c r="O74" s="4" t="n"/>
       <c r="P74" s="4" t="n"/>
       <c r="Q74" s="4" t="n"/>
+      <c r="R74" s="4" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n"/>
@@ -2172,11 +2251,12 @@
       <c r="J75" s="4" t="n"/>
       <c r="K75" s="4" t="n"/>
       <c r="L75" s="4" t="n"/>
-      <c r="M75" s="3" t="n"/>
+      <c r="M75" s="4" t="n"/>
       <c r="N75" s="4" t="n"/>
       <c r="O75" s="4" t="n"/>
       <c r="P75" s="4" t="n"/>
       <c r="Q75" s="4" t="n"/>
+      <c r="R75" s="4" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n"/>
@@ -2191,11 +2271,12 @@
       <c r="J76" s="4" t="n"/>
       <c r="K76" s="4" t="n"/>
       <c r="L76" s="4" t="n"/>
-      <c r="M76" s="3" t="n"/>
+      <c r="M76" s="4" t="n"/>
       <c r="N76" s="4" t="n"/>
       <c r="O76" s="4" t="n"/>
       <c r="P76" s="4" t="n"/>
       <c r="Q76" s="4" t="n"/>
+      <c r="R76" s="4" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n"/>
@@ -2210,11 +2291,12 @@
       <c r="J77" s="4" t="n"/>
       <c r="K77" s="4" t="n"/>
       <c r="L77" s="4" t="n"/>
-      <c r="M77" s="3" t="n"/>
+      <c r="M77" s="4" t="n"/>
       <c r="N77" s="4" t="n"/>
       <c r="O77" s="4" t="n"/>
       <c r="P77" s="4" t="n"/>
       <c r="Q77" s="4" t="n"/>
+      <c r="R77" s="4" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n"/>
@@ -2229,11 +2311,12 @@
       <c r="J78" s="4" t="n"/>
       <c r="K78" s="4" t="n"/>
       <c r="L78" s="4" t="n"/>
-      <c r="M78" s="3" t="n"/>
+      <c r="M78" s="4" t="n"/>
       <c r="N78" s="4" t="n"/>
       <c r="O78" s="4" t="n"/>
       <c r="P78" s="4" t="n"/>
       <c r="Q78" s="4" t="n"/>
+      <c r="R78" s="4" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n"/>
@@ -2248,11 +2331,12 @@
       <c r="J79" s="4" t="n"/>
       <c r="K79" s="4" t="n"/>
       <c r="L79" s="4" t="n"/>
-      <c r="M79" s="3" t="n"/>
+      <c r="M79" s="4" t="n"/>
       <c r="N79" s="4" t="n"/>
       <c r="O79" s="4" t="n"/>
       <c r="P79" s="4" t="n"/>
       <c r="Q79" s="4" t="n"/>
+      <c r="R79" s="4" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n"/>
@@ -2267,11 +2351,12 @@
       <c r="J80" s="4" t="n"/>
       <c r="K80" s="4" t="n"/>
       <c r="L80" s="4" t="n"/>
-      <c r="M80" s="3" t="n"/>
+      <c r="M80" s="4" t="n"/>
       <c r="N80" s="4" t="n"/>
       <c r="O80" s="4" t="n"/>
       <c r="P80" s="4" t="n"/>
       <c r="Q80" s="4" t="n"/>
+      <c r="R80" s="4" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n"/>
@@ -2286,11 +2371,12 @@
       <c r="J81" s="4" t="n"/>
       <c r="K81" s="4" t="n"/>
       <c r="L81" s="4" t="n"/>
-      <c r="M81" s="3" t="n"/>
+      <c r="M81" s="4" t="n"/>
       <c r="N81" s="4" t="n"/>
       <c r="O81" s="4" t="n"/>
       <c r="P81" s="4" t="n"/>
       <c r="Q81" s="4" t="n"/>
+      <c r="R81" s="4" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n"/>
@@ -2305,11 +2391,12 @@
       <c r="J82" s="4" t="n"/>
       <c r="K82" s="4" t="n"/>
       <c r="L82" s="4" t="n"/>
-      <c r="M82" s="3" t="n"/>
+      <c r="M82" s="4" t="n"/>
       <c r="N82" s="4" t="n"/>
       <c r="O82" s="4" t="n"/>
       <c r="P82" s="4" t="n"/>
       <c r="Q82" s="4" t="n"/>
+      <c r="R82" s="4" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n"/>
@@ -2324,11 +2411,12 @@
       <c r="J83" s="4" t="n"/>
       <c r="K83" s="4" t="n"/>
       <c r="L83" s="4" t="n"/>
-      <c r="M83" s="3" t="n"/>
+      <c r="M83" s="4" t="n"/>
       <c r="N83" s="4" t="n"/>
       <c r="O83" s="4" t="n"/>
       <c r="P83" s="4" t="n"/>
       <c r="Q83" s="4" t="n"/>
+      <c r="R83" s="4" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n"/>
@@ -2343,11 +2431,12 @@
       <c r="J84" s="4" t="n"/>
       <c r="K84" s="4" t="n"/>
       <c r="L84" s="4" t="n"/>
-      <c r="M84" s="3" t="n"/>
+      <c r="M84" s="4" t="n"/>
       <c r="N84" s="4" t="n"/>
       <c r="O84" s="4" t="n"/>
       <c r="P84" s="4" t="n"/>
       <c r="Q84" s="4" t="n"/>
+      <c r="R84" s="4" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n"/>
@@ -2362,11 +2451,12 @@
       <c r="J85" s="4" t="n"/>
       <c r="K85" s="4" t="n"/>
       <c r="L85" s="4" t="n"/>
-      <c r="M85" s="3" t="n"/>
+      <c r="M85" s="4" t="n"/>
       <c r="N85" s="4" t="n"/>
       <c r="O85" s="4" t="n"/>
       <c r="P85" s="4" t="n"/>
       <c r="Q85" s="4" t="n"/>
+      <c r="R85" s="4" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n"/>
@@ -2381,11 +2471,12 @@
       <c r="J86" s="4" t="n"/>
       <c r="K86" s="4" t="n"/>
       <c r="L86" s="4" t="n"/>
-      <c r="M86" s="3" t="n"/>
+      <c r="M86" s="4" t="n"/>
       <c r="N86" s="4" t="n"/>
       <c r="O86" s="4" t="n"/>
       <c r="P86" s="4" t="n"/>
       <c r="Q86" s="4" t="n"/>
+      <c r="R86" s="4" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n"/>
@@ -2400,11 +2491,12 @@
       <c r="J87" s="4" t="n"/>
       <c r="K87" s="4" t="n"/>
       <c r="L87" s="4" t="n"/>
-      <c r="M87" s="3" t="n"/>
+      <c r="M87" s="4" t="n"/>
       <c r="N87" s="4" t="n"/>
       <c r="O87" s="4" t="n"/>
       <c r="P87" s="4" t="n"/>
       <c r="Q87" s="4" t="n"/>
+      <c r="R87" s="4" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n"/>
@@ -2419,11 +2511,12 @@
       <c r="J88" s="4" t="n"/>
       <c r="K88" s="4" t="n"/>
       <c r="L88" s="4" t="n"/>
-      <c r="M88" s="3" t="n"/>
+      <c r="M88" s="4" t="n"/>
       <c r="N88" s="4" t="n"/>
       <c r="O88" s="4" t="n"/>
       <c r="P88" s="4" t="n"/>
       <c r="Q88" s="4" t="n"/>
+      <c r="R88" s="4" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n"/>
@@ -2438,11 +2531,12 @@
       <c r="J89" s="4" t="n"/>
       <c r="K89" s="4" t="n"/>
       <c r="L89" s="4" t="n"/>
-      <c r="M89" s="3" t="n"/>
+      <c r="M89" s="4" t="n"/>
       <c r="N89" s="4" t="n"/>
       <c r="O89" s="4" t="n"/>
       <c r="P89" s="4" t="n"/>
       <c r="Q89" s="4" t="n"/>
+      <c r="R89" s="4" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n"/>
@@ -2457,11 +2551,12 @@
       <c r="J90" s="4" t="n"/>
       <c r="K90" s="4" t="n"/>
       <c r="L90" s="4" t="n"/>
-      <c r="M90" s="3" t="n"/>
+      <c r="M90" s="4" t="n"/>
       <c r="N90" s="4" t="n"/>
       <c r="O90" s="4" t="n"/>
       <c r="P90" s="4" t="n"/>
       <c r="Q90" s="4" t="n"/>
+      <c r="R90" s="4" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n"/>
@@ -2476,11 +2571,12 @@
       <c r="J91" s="4" t="n"/>
       <c r="K91" s="4" t="n"/>
       <c r="L91" s="4" t="n"/>
-      <c r="M91" s="3" t="n"/>
+      <c r="M91" s="4" t="n"/>
       <c r="N91" s="4" t="n"/>
       <c r="O91" s="4" t="n"/>
       <c r="P91" s="4" t="n"/>
       <c r="Q91" s="4" t="n"/>
+      <c r="R91" s="4" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n"/>
@@ -2495,11 +2591,12 @@
       <c r="J92" s="4" t="n"/>
       <c r="K92" s="4" t="n"/>
       <c r="L92" s="4" t="n"/>
-      <c r="M92" s="3" t="n"/>
+      <c r="M92" s="4" t="n"/>
       <c r="N92" s="4" t="n"/>
       <c r="O92" s="4" t="n"/>
       <c r="P92" s="4" t="n"/>
       <c r="Q92" s="4" t="n"/>
+      <c r="R92" s="4" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n"/>
@@ -2514,11 +2611,12 @@
       <c r="J93" s="4" t="n"/>
       <c r="K93" s="4" t="n"/>
       <c r="L93" s="4" t="n"/>
-      <c r="M93" s="3" t="n"/>
+      <c r="M93" s="4" t="n"/>
       <c r="N93" s="4" t="n"/>
       <c r="O93" s="4" t="n"/>
       <c r="P93" s="4" t="n"/>
       <c r="Q93" s="4" t="n"/>
+      <c r="R93" s="4" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n"/>
@@ -2533,11 +2631,12 @@
       <c r="J94" s="4" t="n"/>
       <c r="K94" s="4" t="n"/>
       <c r="L94" s="4" t="n"/>
-      <c r="M94" s="3" t="n"/>
+      <c r="M94" s="4" t="n"/>
       <c r="N94" s="4" t="n"/>
       <c r="O94" s="4" t="n"/>
       <c r="P94" s="4" t="n"/>
       <c r="Q94" s="4" t="n"/>
+      <c r="R94" s="4" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n"/>
@@ -2552,11 +2651,12 @@
       <c r="J95" s="4" t="n"/>
       <c r="K95" s="4" t="n"/>
       <c r="L95" s="4" t="n"/>
-      <c r="M95" s="3" t="n"/>
+      <c r="M95" s="4" t="n"/>
       <c r="N95" s="4" t="n"/>
       <c r="O95" s="4" t="n"/>
       <c r="P95" s="4" t="n"/>
       <c r="Q95" s="4" t="n"/>
+      <c r="R95" s="4" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n"/>
@@ -2571,11 +2671,12 @@
       <c r="J96" s="4" t="n"/>
       <c r="K96" s="4" t="n"/>
       <c r="L96" s="4" t="n"/>
-      <c r="M96" s="3" t="n"/>
+      <c r="M96" s="4" t="n"/>
       <c r="N96" s="4" t="n"/>
       <c r="O96" s="4" t="n"/>
       <c r="P96" s="4" t="n"/>
       <c r="Q96" s="4" t="n"/>
+      <c r="R96" s="4" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n"/>
@@ -2590,11 +2691,12 @@
       <c r="J97" s="4" t="n"/>
       <c r="K97" s="4" t="n"/>
       <c r="L97" s="4" t="n"/>
-      <c r="M97" s="3" t="n"/>
+      <c r="M97" s="4" t="n"/>
       <c r="N97" s="4" t="n"/>
       <c r="O97" s="4" t="n"/>
       <c r="P97" s="4" t="n"/>
       <c r="Q97" s="4" t="n"/>
+      <c r="R97" s="4" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n"/>
@@ -2609,11 +2711,12 @@
       <c r="J98" s="4" t="n"/>
       <c r="K98" s="4" t="n"/>
       <c r="L98" s="4" t="n"/>
-      <c r="M98" s="3" t="n"/>
+      <c r="M98" s="4" t="n"/>
       <c r="N98" s="4" t="n"/>
       <c r="O98" s="4" t="n"/>
       <c r="P98" s="4" t="n"/>
       <c r="Q98" s="4" t="n"/>
+      <c r="R98" s="4" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n"/>
@@ -2628,11 +2731,12 @@
       <c r="J99" s="4" t="n"/>
       <c r="K99" s="4" t="n"/>
       <c r="L99" s="4" t="n"/>
-      <c r="M99" s="3" t="n"/>
+      <c r="M99" s="4" t="n"/>
       <c r="N99" s="4" t="n"/>
       <c r="O99" s="4" t="n"/>
       <c r="P99" s="4" t="n"/>
       <c r="Q99" s="4" t="n"/>
+      <c r="R99" s="4" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n"/>
@@ -2647,11 +2751,12 @@
       <c r="J100" s="4" t="n"/>
       <c r="K100" s="4" t="n"/>
       <c r="L100" s="4" t="n"/>
-      <c r="M100" s="3" t="n"/>
+      <c r="M100" s="4" t="n"/>
       <c r="N100" s="4" t="n"/>
       <c r="O100" s="4" t="n"/>
       <c r="P100" s="4" t="n"/>
       <c r="Q100" s="4" t="n"/>
+      <c r="R100" s="4" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n"/>
@@ -2666,11 +2771,12 @@
       <c r="J101" s="4" t="n"/>
       <c r="K101" s="4" t="n"/>
       <c r="L101" s="4" t="n"/>
-      <c r="M101" s="3" t="n"/>
+      <c r="M101" s="4" t="n"/>
       <c r="N101" s="4" t="n"/>
       <c r="O101" s="4" t="n"/>
       <c r="P101" s="4" t="n"/>
       <c r="Q101" s="4" t="n"/>
+      <c r="R101" s="4" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n"/>
@@ -2685,11 +2791,12 @@
       <c r="J102" s="4" t="n"/>
       <c r="K102" s="4" t="n"/>
       <c r="L102" s="4" t="n"/>
-      <c r="M102" s="3" t="n"/>
+      <c r="M102" s="4" t="n"/>
       <c r="N102" s="4" t="n"/>
       <c r="O102" s="4" t="n"/>
       <c r="P102" s="4" t="n"/>
       <c r="Q102" s="4" t="n"/>
+      <c r="R102" s="4" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n"/>
@@ -2704,11 +2811,12 @@
       <c r="J103" s="4" t="n"/>
       <c r="K103" s="4" t="n"/>
       <c r="L103" s="4" t="n"/>
-      <c r="M103" s="3" t="n"/>
+      <c r="M103" s="4" t="n"/>
       <c r="N103" s="4" t="n"/>
       <c r="O103" s="4" t="n"/>
       <c r="P103" s="4" t="n"/>
       <c r="Q103" s="4" t="n"/>
+      <c r="R103" s="4" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n"/>
@@ -2723,11 +2831,12 @@
       <c r="J104" s="4" t="n"/>
       <c r="K104" s="4" t="n"/>
       <c r="L104" s="4" t="n"/>
-      <c r="M104" s="3" t="n"/>
+      <c r="M104" s="4" t="n"/>
       <c r="N104" s="4" t="n"/>
       <c r="O104" s="4" t="n"/>
       <c r="P104" s="4" t="n"/>
       <c r="Q104" s="4" t="n"/>
+      <c r="R104" s="4" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n"/>
@@ -2742,11 +2851,12 @@
       <c r="J105" s="4" t="n"/>
       <c r="K105" s="4" t="n"/>
       <c r="L105" s="4" t="n"/>
-      <c r="M105" s="3" t="n"/>
+      <c r="M105" s="4" t="n"/>
       <c r="N105" s="4" t="n"/>
       <c r="O105" s="4" t="n"/>
       <c r="P105" s="4" t="n"/>
       <c r="Q105" s="4" t="n"/>
+      <c r="R105" s="4" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n"/>
@@ -2761,11 +2871,12 @@
       <c r="J106" s="4" t="n"/>
       <c r="K106" s="4" t="n"/>
       <c r="L106" s="4" t="n"/>
-      <c r="M106" s="3" t="n"/>
+      <c r="M106" s="4" t="n"/>
       <c r="N106" s="4" t="n"/>
       <c r="O106" s="4" t="n"/>
       <c r="P106" s="4" t="n"/>
       <c r="Q106" s="4" t="n"/>
+      <c r="R106" s="4" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n"/>
@@ -2780,11 +2891,12 @@
       <c r="J107" s="4" t="n"/>
       <c r="K107" s="4" t="n"/>
       <c r="L107" s="4" t="n"/>
-      <c r="M107" s="3" t="n"/>
+      <c r="M107" s="4" t="n"/>
       <c r="N107" s="4" t="n"/>
       <c r="O107" s="4" t="n"/>
       <c r="P107" s="4" t="n"/>
       <c r="Q107" s="4" t="n"/>
+      <c r="R107" s="4" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="3" t="n"/>
@@ -2799,11 +2911,12 @@
       <c r="J108" s="4" t="n"/>
       <c r="K108" s="4" t="n"/>
       <c r="L108" s="4" t="n"/>
-      <c r="M108" s="3" t="n"/>
+      <c r="M108" s="4" t="n"/>
       <c r="N108" s="4" t="n"/>
       <c r="O108" s="4" t="n"/>
       <c r="P108" s="4" t="n"/>
       <c r="Q108" s="4" t="n"/>
+      <c r="R108" s="4" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="3" t="n"/>
@@ -2818,11 +2931,12 @@
       <c r="J109" s="4" t="n"/>
       <c r="K109" s="4" t="n"/>
       <c r="L109" s="4" t="n"/>
-      <c r="M109" s="3" t="n"/>
+      <c r="M109" s="4" t="n"/>
       <c r="N109" s="4" t="n"/>
       <c r="O109" s="4" t="n"/>
       <c r="P109" s="4" t="n"/>
       <c r="Q109" s="4" t="n"/>
+      <c r="R109" s="4" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="3" t="n"/>
@@ -2837,11 +2951,12 @@
       <c r="J110" s="4" t="n"/>
       <c r="K110" s="4" t="n"/>
       <c r="L110" s="4" t="n"/>
-      <c r="M110" s="3" t="n"/>
+      <c r="M110" s="4" t="n"/>
       <c r="N110" s="4" t="n"/>
       <c r="O110" s="4" t="n"/>
       <c r="P110" s="4" t="n"/>
       <c r="Q110" s="4" t="n"/>
+      <c r="R110" s="4" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="3" t="n"/>
@@ -2856,11 +2971,12 @@
       <c r="J111" s="4" t="n"/>
       <c r="K111" s="4" t="n"/>
       <c r="L111" s="4" t="n"/>
-      <c r="M111" s="3" t="n"/>
+      <c r="M111" s="4" t="n"/>
       <c r="N111" s="4" t="n"/>
       <c r="O111" s="4" t="n"/>
       <c r="P111" s="4" t="n"/>
       <c r="Q111" s="4" t="n"/>
+      <c r="R111" s="4" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="3" t="n"/>
@@ -2875,11 +2991,12 @@
       <c r="J112" s="4" t="n"/>
       <c r="K112" s="4" t="n"/>
       <c r="L112" s="4" t="n"/>
-      <c r="M112" s="3" t="n"/>
+      <c r="M112" s="4" t="n"/>
       <c r="N112" s="4" t="n"/>
       <c r="O112" s="4" t="n"/>
       <c r="P112" s="4" t="n"/>
       <c r="Q112" s="4" t="n"/>
+      <c r="R112" s="4" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="3" t="n"/>
@@ -2894,11 +3011,12 @@
       <c r="J113" s="4" t="n"/>
       <c r="K113" s="4" t="n"/>
       <c r="L113" s="4" t="n"/>
-      <c r="M113" s="3" t="n"/>
+      <c r="M113" s="4" t="n"/>
       <c r="N113" s="4" t="n"/>
       <c r="O113" s="4" t="n"/>
       <c r="P113" s="4" t="n"/>
       <c r="Q113" s="4" t="n"/>
+      <c r="R113" s="4" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="3" t="n"/>
@@ -2913,11 +3031,12 @@
       <c r="J114" s="4" t="n"/>
       <c r="K114" s="4" t="n"/>
       <c r="L114" s="4" t="n"/>
-      <c r="M114" s="3" t="n"/>
+      <c r="M114" s="4" t="n"/>
       <c r="N114" s="4" t="n"/>
       <c r="O114" s="4" t="n"/>
       <c r="P114" s="4" t="n"/>
       <c r="Q114" s="4" t="n"/>
+      <c r="R114" s="4" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="3" t="n"/>
@@ -2932,11 +3051,12 @@
       <c r="J115" s="4" t="n"/>
       <c r="K115" s="4" t="n"/>
       <c r="L115" s="4" t="n"/>
-      <c r="M115" s="3" t="n"/>
+      <c r="M115" s="4" t="n"/>
       <c r="N115" s="4" t="n"/>
       <c r="O115" s="4" t="n"/>
       <c r="P115" s="4" t="n"/>
       <c r="Q115" s="4" t="n"/>
+      <c r="R115" s="4" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="3" t="n"/>
@@ -2951,11 +3071,12 @@
       <c r="J116" s="4" t="n"/>
       <c r="K116" s="4" t="n"/>
       <c r="L116" s="4" t="n"/>
-      <c r="M116" s="3" t="n"/>
+      <c r="M116" s="4" t="n"/>
       <c r="N116" s="4" t="n"/>
       <c r="O116" s="4" t="n"/>
       <c r="P116" s="4" t="n"/>
       <c r="Q116" s="4" t="n"/>
+      <c r="R116" s="4" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="3" t="n"/>
@@ -2970,11 +3091,12 @@
       <c r="J117" s="4" t="n"/>
       <c r="K117" s="4" t="n"/>
       <c r="L117" s="4" t="n"/>
-      <c r="M117" s="3" t="n"/>
+      <c r="M117" s="4" t="n"/>
       <c r="N117" s="4" t="n"/>
       <c r="O117" s="4" t="n"/>
       <c r="P117" s="4" t="n"/>
       <c r="Q117" s="4" t="n"/>
+      <c r="R117" s="4" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n"/>
@@ -2989,11 +3111,12 @@
       <c r="J118" s="4" t="n"/>
       <c r="K118" s="4" t="n"/>
       <c r="L118" s="4" t="n"/>
-      <c r="M118" s="3" t="n"/>
+      <c r="M118" s="4" t="n"/>
       <c r="N118" s="4" t="n"/>
       <c r="O118" s="4" t="n"/>
       <c r="P118" s="4" t="n"/>
       <c r="Q118" s="4" t="n"/>
+      <c r="R118" s="4" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="3" t="n"/>
@@ -3008,11 +3131,12 @@
       <c r="J119" s="4" t="n"/>
       <c r="K119" s="4" t="n"/>
       <c r="L119" s="4" t="n"/>
-      <c r="M119" s="3" t="n"/>
+      <c r="M119" s="4" t="n"/>
       <c r="N119" s="4" t="n"/>
       <c r="O119" s="4" t="n"/>
       <c r="P119" s="4" t="n"/>
       <c r="Q119" s="4" t="n"/>
+      <c r="R119" s="4" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="3" t="n"/>
@@ -3027,11 +3151,12 @@
       <c r="J120" s="4" t="n"/>
       <c r="K120" s="4" t="n"/>
       <c r="L120" s="4" t="n"/>
-      <c r="M120" s="3" t="n"/>
+      <c r="M120" s="4" t="n"/>
       <c r="N120" s="4" t="n"/>
       <c r="O120" s="4" t="n"/>
       <c r="P120" s="4" t="n"/>
       <c r="Q120" s="4" t="n"/>
+      <c r="R120" s="4" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="3" t="n"/>
@@ -3046,11 +3171,12 @@
       <c r="J121" s="4" t="n"/>
       <c r="K121" s="4" t="n"/>
       <c r="L121" s="4" t="n"/>
-      <c r="M121" s="3" t="n"/>
+      <c r="M121" s="4" t="n"/>
       <c r="N121" s="4" t="n"/>
       <c r="O121" s="4" t="n"/>
       <c r="P121" s="4" t="n"/>
       <c r="Q121" s="4" t="n"/>
+      <c r="R121" s="4" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="3" t="n"/>
@@ -3065,11 +3191,12 @@
       <c r="J122" s="4" t="n"/>
       <c r="K122" s="4" t="n"/>
       <c r="L122" s="4" t="n"/>
-      <c r="M122" s="3" t="n"/>
+      <c r="M122" s="4" t="n"/>
       <c r="N122" s="4" t="n"/>
       <c r="O122" s="4" t="n"/>
       <c r="P122" s="4" t="n"/>
       <c r="Q122" s="4" t="n"/>
+      <c r="R122" s="4" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="3" t="n"/>
@@ -3084,11 +3211,12 @@
       <c r="J123" s="4" t="n"/>
       <c r="K123" s="4" t="n"/>
       <c r="L123" s="4" t="n"/>
-      <c r="M123" s="3" t="n"/>
+      <c r="M123" s="4" t="n"/>
       <c r="N123" s="4" t="n"/>
       <c r="O123" s="4" t="n"/>
       <c r="P123" s="4" t="n"/>
       <c r="Q123" s="4" t="n"/>
+      <c r="R123" s="4" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="3" t="n"/>
@@ -3103,11 +3231,12 @@
       <c r="J124" s="4" t="n"/>
       <c r="K124" s="4" t="n"/>
       <c r="L124" s="4" t="n"/>
-      <c r="M124" s="3" t="n"/>
+      <c r="M124" s="4" t="n"/>
       <c r="N124" s="4" t="n"/>
       <c r="O124" s="4" t="n"/>
       <c r="P124" s="4" t="n"/>
       <c r="Q124" s="4" t="n"/>
+      <c r="R124" s="4" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="3" t="n"/>
@@ -3122,11 +3251,12 @@
       <c r="J125" s="4" t="n"/>
       <c r="K125" s="4" t="n"/>
       <c r="L125" s="4" t="n"/>
-      <c r="M125" s="3" t="n"/>
+      <c r="M125" s="4" t="n"/>
       <c r="N125" s="4" t="n"/>
       <c r="O125" s="4" t="n"/>
       <c r="P125" s="4" t="n"/>
       <c r="Q125" s="4" t="n"/>
+      <c r="R125" s="4" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="3" t="n"/>
@@ -3141,11 +3271,12 @@
       <c r="J126" s="4" t="n"/>
       <c r="K126" s="4" t="n"/>
       <c r="L126" s="4" t="n"/>
-      <c r="M126" s="3" t="n"/>
+      <c r="M126" s="4" t="n"/>
       <c r="N126" s="4" t="n"/>
       <c r="O126" s="4" t="n"/>
       <c r="P126" s="4" t="n"/>
       <c r="Q126" s="4" t="n"/>
+      <c r="R126" s="4" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="3" t="n"/>
@@ -3160,11 +3291,12 @@
       <c r="J127" s="4" t="n"/>
       <c r="K127" s="4" t="n"/>
       <c r="L127" s="4" t="n"/>
-      <c r="M127" s="3" t="n"/>
+      <c r="M127" s="4" t="n"/>
       <c r="N127" s="4" t="n"/>
       <c r="O127" s="4" t="n"/>
       <c r="P127" s="4" t="n"/>
       <c r="Q127" s="4" t="n"/>
+      <c r="R127" s="4" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="3" t="n"/>
@@ -3179,11 +3311,12 @@
       <c r="J128" s="4" t="n"/>
       <c r="K128" s="4" t="n"/>
       <c r="L128" s="4" t="n"/>
-      <c r="M128" s="3" t="n"/>
+      <c r="M128" s="4" t="n"/>
       <c r="N128" s="4" t="n"/>
       <c r="O128" s="4" t="n"/>
       <c r="P128" s="4" t="n"/>
       <c r="Q128" s="4" t="n"/>
+      <c r="R128" s="4" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="3" t="n"/>
@@ -3198,11 +3331,12 @@
       <c r="J129" s="4" t="n"/>
       <c r="K129" s="4" t="n"/>
       <c r="L129" s="4" t="n"/>
-      <c r="M129" s="3" t="n"/>
+      <c r="M129" s="4" t="n"/>
       <c r="N129" s="4" t="n"/>
       <c r="O129" s="4" t="n"/>
       <c r="P129" s="4" t="n"/>
       <c r="Q129" s="4" t="n"/>
+      <c r="R129" s="4" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="3" t="n"/>
@@ -3217,11 +3351,12 @@
       <c r="J130" s="4" t="n"/>
       <c r="K130" s="4" t="n"/>
       <c r="L130" s="4" t="n"/>
-      <c r="M130" s="3" t="n"/>
+      <c r="M130" s="4" t="n"/>
       <c r="N130" s="4" t="n"/>
       <c r="O130" s="4" t="n"/>
       <c r="P130" s="4" t="n"/>
       <c r="Q130" s="4" t="n"/>
+      <c r="R130" s="4" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="3" t="n"/>
@@ -3236,11 +3371,12 @@
       <c r="J131" s="4" t="n"/>
       <c r="K131" s="4" t="n"/>
       <c r="L131" s="4" t="n"/>
-      <c r="M131" s="3" t="n"/>
+      <c r="M131" s="4" t="n"/>
       <c r="N131" s="4" t="n"/>
       <c r="O131" s="4" t="n"/>
       <c r="P131" s="4" t="n"/>
       <c r="Q131" s="4" t="n"/>
+      <c r="R131" s="4" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="3" t="n"/>
@@ -3255,11 +3391,12 @@
       <c r="J132" s="4" t="n"/>
       <c r="K132" s="4" t="n"/>
       <c r="L132" s="4" t="n"/>
-      <c r="M132" s="3" t="n"/>
+      <c r="M132" s="4" t="n"/>
       <c r="N132" s="4" t="n"/>
       <c r="O132" s="4" t="n"/>
       <c r="P132" s="4" t="n"/>
       <c r="Q132" s="4" t="n"/>
+      <c r="R132" s="4" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="3" t="n"/>
@@ -3274,11 +3411,12 @@
       <c r="J133" s="4" t="n"/>
       <c r="K133" s="4" t="n"/>
       <c r="L133" s="4" t="n"/>
-      <c r="M133" s="3" t="n"/>
+      <c r="M133" s="4" t="n"/>
       <c r="N133" s="4" t="n"/>
       <c r="O133" s="4" t="n"/>
       <c r="P133" s="4" t="n"/>
       <c r="Q133" s="4" t="n"/>
+      <c r="R133" s="4" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="3" t="n"/>
@@ -3293,11 +3431,12 @@
       <c r="J134" s="4" t="n"/>
       <c r="K134" s="4" t="n"/>
       <c r="L134" s="4" t="n"/>
-      <c r="M134" s="3" t="n"/>
+      <c r="M134" s="4" t="n"/>
       <c r="N134" s="4" t="n"/>
       <c r="O134" s="4" t="n"/>
       <c r="P134" s="4" t="n"/>
       <c r="Q134" s="4" t="n"/>
+      <c r="R134" s="4" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="3" t="n"/>
@@ -3312,11 +3451,12 @@
       <c r="J135" s="4" t="n"/>
       <c r="K135" s="4" t="n"/>
       <c r="L135" s="4" t="n"/>
-      <c r="M135" s="3" t="n"/>
+      <c r="M135" s="4" t="n"/>
       <c r="N135" s="4" t="n"/>
       <c r="O135" s="4" t="n"/>
       <c r="P135" s="4" t="n"/>
       <c r="Q135" s="4" t="n"/>
+      <c r="R135" s="4" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="3" t="n"/>
@@ -3331,11 +3471,12 @@
       <c r="J136" s="4" t="n"/>
       <c r="K136" s="4" t="n"/>
       <c r="L136" s="4" t="n"/>
-      <c r="M136" s="3" t="n"/>
+      <c r="M136" s="4" t="n"/>
       <c r="N136" s="4" t="n"/>
       <c r="O136" s="4" t="n"/>
       <c r="P136" s="4" t="n"/>
       <c r="Q136" s="4" t="n"/>
+      <c r="R136" s="4" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="3" t="n"/>
@@ -3350,11 +3491,12 @@
       <c r="J137" s="4" t="n"/>
       <c r="K137" s="4" t="n"/>
       <c r="L137" s="4" t="n"/>
-      <c r="M137" s="3" t="n"/>
+      <c r="M137" s="4" t="n"/>
       <c r="N137" s="4" t="n"/>
       <c r="O137" s="4" t="n"/>
       <c r="P137" s="4" t="n"/>
       <c r="Q137" s="4" t="n"/>
+      <c r="R137" s="4" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="3" t="n"/>
@@ -3369,11 +3511,12 @@
       <c r="J138" s="4" t="n"/>
       <c r="K138" s="4" t="n"/>
       <c r="L138" s="4" t="n"/>
-      <c r="M138" s="3" t="n"/>
+      <c r="M138" s="4" t="n"/>
       <c r="N138" s="4" t="n"/>
       <c r="O138" s="4" t="n"/>
       <c r="P138" s="4" t="n"/>
       <c r="Q138" s="4" t="n"/>
+      <c r="R138" s="4" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="3" t="n"/>
@@ -3388,11 +3531,12 @@
       <c r="J139" s="4" t="n"/>
       <c r="K139" s="4" t="n"/>
       <c r="L139" s="4" t="n"/>
-      <c r="M139" s="3" t="n"/>
+      <c r="M139" s="4" t="n"/>
       <c r="N139" s="4" t="n"/>
       <c r="O139" s="4" t="n"/>
       <c r="P139" s="4" t="n"/>
       <c r="Q139" s="4" t="n"/>
+      <c r="R139" s="4" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="3" t="n"/>
@@ -3407,11 +3551,12 @@
       <c r="J140" s="4" t="n"/>
       <c r="K140" s="4" t="n"/>
       <c r="L140" s="4" t="n"/>
-      <c r="M140" s="3" t="n"/>
+      <c r="M140" s="4" t="n"/>
       <c r="N140" s="4" t="n"/>
       <c r="O140" s="4" t="n"/>
       <c r="P140" s="4" t="n"/>
       <c r="Q140" s="4" t="n"/>
+      <c r="R140" s="4" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="3" t="n"/>
@@ -3426,11 +3571,12 @@
       <c r="J141" s="4" t="n"/>
       <c r="K141" s="4" t="n"/>
       <c r="L141" s="4" t="n"/>
-      <c r="M141" s="3" t="n"/>
+      <c r="M141" s="4" t="n"/>
       <c r="N141" s="4" t="n"/>
       <c r="O141" s="4" t="n"/>
       <c r="P141" s="4" t="n"/>
       <c r="Q141" s="4" t="n"/>
+      <c r="R141" s="4" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="3" t="n"/>
@@ -3445,11 +3591,12 @@
       <c r="J142" s="4" t="n"/>
       <c r="K142" s="4" t="n"/>
       <c r="L142" s="4" t="n"/>
-      <c r="M142" s="3" t="n"/>
+      <c r="M142" s="4" t="n"/>
       <c r="N142" s="4" t="n"/>
       <c r="O142" s="4" t="n"/>
       <c r="P142" s="4" t="n"/>
       <c r="Q142" s="4" t="n"/>
+      <c r="R142" s="4" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="3" t="n"/>
@@ -3464,11 +3611,12 @@
       <c r="J143" s="4" t="n"/>
       <c r="K143" s="4" t="n"/>
       <c r="L143" s="4" t="n"/>
-      <c r="M143" s="3" t="n"/>
+      <c r="M143" s="4" t="n"/>
       <c r="N143" s="4" t="n"/>
       <c r="O143" s="4" t="n"/>
       <c r="P143" s="4" t="n"/>
       <c r="Q143" s="4" t="n"/>
+      <c r="R143" s="4" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="3" t="n"/>
@@ -3483,11 +3631,12 @@
       <c r="J144" s="4" t="n"/>
       <c r="K144" s="4" t="n"/>
       <c r="L144" s="4" t="n"/>
-      <c r="M144" s="3" t="n"/>
+      <c r="M144" s="4" t="n"/>
       <c r="N144" s="4" t="n"/>
       <c r="O144" s="4" t="n"/>
       <c r="P144" s="4" t="n"/>
       <c r="Q144" s="4" t="n"/>
+      <c r="R144" s="4" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="3" t="n"/>
@@ -3502,11 +3651,12 @@
       <c r="J145" s="4" t="n"/>
       <c r="K145" s="4" t="n"/>
       <c r="L145" s="4" t="n"/>
-      <c r="M145" s="3" t="n"/>
+      <c r="M145" s="4" t="n"/>
       <c r="N145" s="4" t="n"/>
       <c r="O145" s="4" t="n"/>
       <c r="P145" s="4" t="n"/>
       <c r="Q145" s="4" t="n"/>
+      <c r="R145" s="4" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="3" t="n"/>
@@ -3521,11 +3671,12 @@
       <c r="J146" s="4" t="n"/>
       <c r="K146" s="4" t="n"/>
       <c r="L146" s="4" t="n"/>
-      <c r="M146" s="3" t="n"/>
+      <c r="M146" s="4" t="n"/>
       <c r="N146" s="4" t="n"/>
       <c r="O146" s="4" t="n"/>
       <c r="P146" s="4" t="n"/>
       <c r="Q146" s="4" t="n"/>
+      <c r="R146" s="4" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="3" t="n"/>
@@ -3540,11 +3691,12 @@
       <c r="J147" s="4" t="n"/>
       <c r="K147" s="4" t="n"/>
       <c r="L147" s="4" t="n"/>
-      <c r="M147" s="3" t="n"/>
+      <c r="M147" s="4" t="n"/>
       <c r="N147" s="4" t="n"/>
       <c r="O147" s="4" t="n"/>
       <c r="P147" s="4" t="n"/>
       <c r="Q147" s="4" t="n"/>
+      <c r="R147" s="4" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="3" t="n"/>
@@ -3559,11 +3711,12 @@
       <c r="J148" s="4" t="n"/>
       <c r="K148" s="4" t="n"/>
       <c r="L148" s="4" t="n"/>
-      <c r="M148" s="3" t="n"/>
+      <c r="M148" s="4" t="n"/>
       <c r="N148" s="4" t="n"/>
       <c r="O148" s="4" t="n"/>
       <c r="P148" s="4" t="n"/>
       <c r="Q148" s="4" t="n"/>
+      <c r="R148" s="4" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="3" t="n"/>
@@ -3578,11 +3731,12 @@
       <c r="J149" s="4" t="n"/>
       <c r="K149" s="4" t="n"/>
       <c r="L149" s="4" t="n"/>
-      <c r="M149" s="3" t="n"/>
+      <c r="M149" s="4" t="n"/>
       <c r="N149" s="4" t="n"/>
       <c r="O149" s="4" t="n"/>
       <c r="P149" s="4" t="n"/>
       <c r="Q149" s="4" t="n"/>
+      <c r="R149" s="4" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="3" t="n"/>
@@ -3597,11 +3751,12 @@
       <c r="J150" s="4" t="n"/>
       <c r="K150" s="4" t="n"/>
       <c r="L150" s="4" t="n"/>
-      <c r="M150" s="3" t="n"/>
+      <c r="M150" s="4" t="n"/>
       <c r="N150" s="4" t="n"/>
       <c r="O150" s="4" t="n"/>
       <c r="P150" s="4" t="n"/>
       <c r="Q150" s="4" t="n"/>
+      <c r="R150" s="4" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="3" t="n"/>
@@ -3616,11 +3771,12 @@
       <c r="J151" s="4" t="n"/>
       <c r="K151" s="4" t="n"/>
       <c r="L151" s="4" t="n"/>
-      <c r="M151" s="3" t="n"/>
+      <c r="M151" s="4" t="n"/>
       <c r="N151" s="4" t="n"/>
       <c r="O151" s="4" t="n"/>
       <c r="P151" s="4" t="n"/>
       <c r="Q151" s="4" t="n"/>
+      <c r="R151" s="4" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="3" t="n"/>
@@ -3635,11 +3791,12 @@
       <c r="J152" s="4" t="n"/>
       <c r="K152" s="4" t="n"/>
       <c r="L152" s="4" t="n"/>
-      <c r="M152" s="3" t="n"/>
+      <c r="M152" s="4" t="n"/>
       <c r="N152" s="4" t="n"/>
       <c r="O152" s="4" t="n"/>
       <c r="P152" s="4" t="n"/>
       <c r="Q152" s="4" t="n"/>
+      <c r="R152" s="4" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="3" t="n"/>
@@ -3654,11 +3811,12 @@
       <c r="J153" s="4" t="n"/>
       <c r="K153" s="4" t="n"/>
       <c r="L153" s="4" t="n"/>
-      <c r="M153" s="3" t="n"/>
+      <c r="M153" s="4" t="n"/>
       <c r="N153" s="4" t="n"/>
       <c r="O153" s="4" t="n"/>
       <c r="P153" s="4" t="n"/>
       <c r="Q153" s="4" t="n"/>
+      <c r="R153" s="4" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="3" t="n"/>
@@ -3673,11 +3831,12 @@
       <c r="J154" s="4" t="n"/>
       <c r="K154" s="4" t="n"/>
       <c r="L154" s="4" t="n"/>
-      <c r="M154" s="3" t="n"/>
+      <c r="M154" s="4" t="n"/>
       <c r="N154" s="4" t="n"/>
       <c r="O154" s="4" t="n"/>
       <c r="P154" s="4" t="n"/>
       <c r="Q154" s="4" t="n"/>
+      <c r="R154" s="4" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="3" t="n"/>
@@ -3692,11 +3851,12 @@
       <c r="J155" s="4" t="n"/>
       <c r="K155" s="4" t="n"/>
       <c r="L155" s="4" t="n"/>
-      <c r="M155" s="3" t="n"/>
+      <c r="M155" s="4" t="n"/>
       <c r="N155" s="4" t="n"/>
       <c r="O155" s="4" t="n"/>
       <c r="P155" s="4" t="n"/>
       <c r="Q155" s="4" t="n"/>
+      <c r="R155" s="4" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="3" t="n"/>
@@ -3711,11 +3871,12 @@
       <c r="J156" s="4" t="n"/>
       <c r="K156" s="4" t="n"/>
       <c r="L156" s="4" t="n"/>
-      <c r="M156" s="3" t="n"/>
+      <c r="M156" s="4" t="n"/>
       <c r="N156" s="4" t="n"/>
       <c r="O156" s="4" t="n"/>
       <c r="P156" s="4" t="n"/>
       <c r="Q156" s="4" t="n"/>
+      <c r="R156" s="4" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="3" t="n"/>
@@ -3730,11 +3891,12 @@
       <c r="J157" s="4" t="n"/>
       <c r="K157" s="4" t="n"/>
       <c r="L157" s="4" t="n"/>
-      <c r="M157" s="3" t="n"/>
+      <c r="M157" s="4" t="n"/>
       <c r="N157" s="4" t="n"/>
       <c r="O157" s="4" t="n"/>
       <c r="P157" s="4" t="n"/>
       <c r="Q157" s="4" t="n"/>
+      <c r="R157" s="4" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="3" t="n"/>
@@ -3749,11 +3911,12 @@
       <c r="J158" s="4" t="n"/>
       <c r="K158" s="4" t="n"/>
       <c r="L158" s="4" t="n"/>
-      <c r="M158" s="3" t="n"/>
+      <c r="M158" s="4" t="n"/>
       <c r="N158" s="4" t="n"/>
       <c r="O158" s="4" t="n"/>
       <c r="P158" s="4" t="n"/>
       <c r="Q158" s="4" t="n"/>
+      <c r="R158" s="4" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="3" t="n"/>
@@ -3768,11 +3931,12 @@
       <c r="J159" s="4" t="n"/>
       <c r="K159" s="4" t="n"/>
       <c r="L159" s="4" t="n"/>
-      <c r="M159" s="3" t="n"/>
+      <c r="M159" s="4" t="n"/>
       <c r="N159" s="4" t="n"/>
       <c r="O159" s="4" t="n"/>
       <c r="P159" s="4" t="n"/>
       <c r="Q159" s="4" t="n"/>
+      <c r="R159" s="4" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="3" t="n"/>
@@ -3787,11 +3951,12 @@
       <c r="J160" s="4" t="n"/>
       <c r="K160" s="4" t="n"/>
       <c r="L160" s="4" t="n"/>
-      <c r="M160" s="3" t="n"/>
+      <c r="M160" s="4" t="n"/>
       <c r="N160" s="4" t="n"/>
       <c r="O160" s="4" t="n"/>
       <c r="P160" s="4" t="n"/>
       <c r="Q160" s="4" t="n"/>
+      <c r="R160" s="4" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="3" t="n"/>
@@ -3806,11 +3971,12 @@
       <c r="J161" s="4" t="n"/>
       <c r="K161" s="4" t="n"/>
       <c r="L161" s="4" t="n"/>
-      <c r="M161" s="3" t="n"/>
+      <c r="M161" s="4" t="n"/>
       <c r="N161" s="4" t="n"/>
       <c r="O161" s="4" t="n"/>
       <c r="P161" s="4" t="n"/>
       <c r="Q161" s="4" t="n"/>
+      <c r="R161" s="4" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="3" t="n"/>
@@ -3825,11 +3991,12 @@
       <c r="J162" s="4" t="n"/>
       <c r="K162" s="4" t="n"/>
       <c r="L162" s="4" t="n"/>
-      <c r="M162" s="3" t="n"/>
+      <c r="M162" s="4" t="n"/>
       <c r="N162" s="4" t="n"/>
       <c r="O162" s="4" t="n"/>
       <c r="P162" s="4" t="n"/>
       <c r="Q162" s="4" t="n"/>
+      <c r="R162" s="4" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="3" t="n"/>
@@ -3844,11 +4011,12 @@
       <c r="J163" s="4" t="n"/>
       <c r="K163" s="4" t="n"/>
       <c r="L163" s="4" t="n"/>
-      <c r="M163" s="3" t="n"/>
+      <c r="M163" s="4" t="n"/>
       <c r="N163" s="4" t="n"/>
       <c r="O163" s="4" t="n"/>
       <c r="P163" s="4" t="n"/>
       <c r="Q163" s="4" t="n"/>
+      <c r="R163" s="4" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="3" t="n"/>
@@ -3863,11 +4031,12 @@
       <c r="J164" s="4" t="n"/>
       <c r="K164" s="4" t="n"/>
       <c r="L164" s="4" t="n"/>
-      <c r="M164" s="3" t="n"/>
+      <c r="M164" s="4" t="n"/>
       <c r="N164" s="4" t="n"/>
       <c r="O164" s="4" t="n"/>
       <c r="P164" s="4" t="n"/>
       <c r="Q164" s="4" t="n"/>
+      <c r="R164" s="4" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="3" t="n"/>
@@ -3882,11 +4051,12 @@
       <c r="J165" s="4" t="n"/>
       <c r="K165" s="4" t="n"/>
       <c r="L165" s="4" t="n"/>
-      <c r="M165" s="3" t="n"/>
+      <c r="M165" s="4" t="n"/>
       <c r="N165" s="4" t="n"/>
       <c r="O165" s="4" t="n"/>
       <c r="P165" s="4" t="n"/>
       <c r="Q165" s="4" t="n"/>
+      <c r="R165" s="4" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="3" t="n"/>
@@ -3901,11 +4071,12 @@
       <c r="J166" s="4" t="n"/>
       <c r="K166" s="4" t="n"/>
       <c r="L166" s="4" t="n"/>
-      <c r="M166" s="3" t="n"/>
+      <c r="M166" s="4" t="n"/>
       <c r="N166" s="4" t="n"/>
       <c r="O166" s="4" t="n"/>
       <c r="P166" s="4" t="n"/>
       <c r="Q166" s="4" t="n"/>
+      <c r="R166" s="4" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="3" t="n"/>
@@ -3920,11 +4091,12 @@
       <c r="J167" s="4" t="n"/>
       <c r="K167" s="4" t="n"/>
       <c r="L167" s="4" t="n"/>
-      <c r="M167" s="3" t="n"/>
+      <c r="M167" s="4" t="n"/>
       <c r="N167" s="4" t="n"/>
       <c r="O167" s="4" t="n"/>
       <c r="P167" s="4" t="n"/>
       <c r="Q167" s="4" t="n"/>
+      <c r="R167" s="4" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="3" t="n"/>
@@ -3939,11 +4111,12 @@
       <c r="J168" s="4" t="n"/>
       <c r="K168" s="4" t="n"/>
       <c r="L168" s="4" t="n"/>
-      <c r="M168" s="3" t="n"/>
+      <c r="M168" s="4" t="n"/>
       <c r="N168" s="4" t="n"/>
       <c r="O168" s="4" t="n"/>
       <c r="P168" s="4" t="n"/>
       <c r="Q168" s="4" t="n"/>
+      <c r="R168" s="4" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="3" t="n"/>
@@ -3958,11 +4131,12 @@
       <c r="J169" s="4" t="n"/>
       <c r="K169" s="4" t="n"/>
       <c r="L169" s="4" t="n"/>
-      <c r="M169" s="3" t="n"/>
+      <c r="M169" s="4" t="n"/>
       <c r="N169" s="4" t="n"/>
       <c r="O169" s="4" t="n"/>
       <c r="P169" s="4" t="n"/>
       <c r="Q169" s="4" t="n"/>
+      <c r="R169" s="4" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="3" t="n"/>
@@ -3977,11 +4151,12 @@
       <c r="J170" s="4" t="n"/>
       <c r="K170" s="4" t="n"/>
       <c r="L170" s="4" t="n"/>
-      <c r="M170" s="3" t="n"/>
+      <c r="M170" s="4" t="n"/>
       <c r="N170" s="4" t="n"/>
       <c r="O170" s="4" t="n"/>
       <c r="P170" s="4" t="n"/>
       <c r="Q170" s="4" t="n"/>
+      <c r="R170" s="4" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="3" t="n"/>
@@ -3996,11 +4171,12 @@
       <c r="J171" s="4" t="n"/>
       <c r="K171" s="4" t="n"/>
       <c r="L171" s="4" t="n"/>
-      <c r="M171" s="3" t="n"/>
+      <c r="M171" s="4" t="n"/>
       <c r="N171" s="4" t="n"/>
       <c r="O171" s="4" t="n"/>
       <c r="P171" s="4" t="n"/>
       <c r="Q171" s="4" t="n"/>
+      <c r="R171" s="4" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="3" t="n"/>
@@ -4015,11 +4191,12 @@
       <c r="J172" s="4" t="n"/>
       <c r="K172" s="4" t="n"/>
       <c r="L172" s="4" t="n"/>
-      <c r="M172" s="3" t="n"/>
+      <c r="M172" s="4" t="n"/>
       <c r="N172" s="4" t="n"/>
       <c r="O172" s="4" t="n"/>
       <c r="P172" s="4" t="n"/>
       <c r="Q172" s="4" t="n"/>
+      <c r="R172" s="4" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="3" t="n"/>
@@ -4034,11 +4211,12 @@
       <c r="J173" s="4" t="n"/>
       <c r="K173" s="4" t="n"/>
       <c r="L173" s="4" t="n"/>
-      <c r="M173" s="3" t="n"/>
+      <c r="M173" s="4" t="n"/>
       <c r="N173" s="4" t="n"/>
       <c r="O173" s="4" t="n"/>
       <c r="P173" s="4" t="n"/>
       <c r="Q173" s="4" t="n"/>
+      <c r="R173" s="4" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="3" t="n"/>
@@ -4053,11 +4231,12 @@
       <c r="J174" s="4" t="n"/>
       <c r="K174" s="4" t="n"/>
       <c r="L174" s="4" t="n"/>
-      <c r="M174" s="3" t="n"/>
+      <c r="M174" s="4" t="n"/>
       <c r="N174" s="4" t="n"/>
       <c r="O174" s="4" t="n"/>
       <c r="P174" s="4" t="n"/>
       <c r="Q174" s="4" t="n"/>
+      <c r="R174" s="4" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="3" t="n"/>
@@ -4072,11 +4251,12 @@
       <c r="J175" s="4" t="n"/>
       <c r="K175" s="4" t="n"/>
       <c r="L175" s="4" t="n"/>
-      <c r="M175" s="3" t="n"/>
+      <c r="M175" s="4" t="n"/>
       <c r="N175" s="4" t="n"/>
       <c r="O175" s="4" t="n"/>
       <c r="P175" s="4" t="n"/>
       <c r="Q175" s="4" t="n"/>
+      <c r="R175" s="4" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="3" t="n"/>
@@ -4091,11 +4271,12 @@
       <c r="J176" s="4" t="n"/>
       <c r="K176" s="4" t="n"/>
       <c r="L176" s="4" t="n"/>
-      <c r="M176" s="3" t="n"/>
+      <c r="M176" s="4" t="n"/>
       <c r="N176" s="4" t="n"/>
       <c r="O176" s="4" t="n"/>
       <c r="P176" s="4" t="n"/>
       <c r="Q176" s="4" t="n"/>
+      <c r="R176" s="4" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="3" t="n"/>
@@ -4110,11 +4291,12 @@
       <c r="J177" s="4" t="n"/>
       <c r="K177" s="4" t="n"/>
       <c r="L177" s="4" t="n"/>
-      <c r="M177" s="3" t="n"/>
+      <c r="M177" s="4" t="n"/>
       <c r="N177" s="4" t="n"/>
       <c r="O177" s="4" t="n"/>
       <c r="P177" s="4" t="n"/>
       <c r="Q177" s="4" t="n"/>
+      <c r="R177" s="4" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="3" t="n"/>
@@ -4129,11 +4311,12 @@
       <c r="J178" s="4" t="n"/>
       <c r="K178" s="4" t="n"/>
       <c r="L178" s="4" t="n"/>
-      <c r="M178" s="3" t="n"/>
+      <c r="M178" s="4" t="n"/>
       <c r="N178" s="4" t="n"/>
       <c r="O178" s="4" t="n"/>
       <c r="P178" s="4" t="n"/>
       <c r="Q178" s="4" t="n"/>
+      <c r="R178" s="4" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="3" t="n"/>
@@ -4148,11 +4331,12 @@
       <c r="J179" s="4" t="n"/>
       <c r="K179" s="4" t="n"/>
       <c r="L179" s="4" t="n"/>
-      <c r="M179" s="3" t="n"/>
+      <c r="M179" s="4" t="n"/>
       <c r="N179" s="4" t="n"/>
       <c r="O179" s="4" t="n"/>
       <c r="P179" s="4" t="n"/>
       <c r="Q179" s="4" t="n"/>
+      <c r="R179" s="4" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="3" t="n"/>
@@ -4167,11 +4351,12 @@
       <c r="J180" s="4" t="n"/>
       <c r="K180" s="4" t="n"/>
       <c r="L180" s="4" t="n"/>
-      <c r="M180" s="3" t="n"/>
+      <c r="M180" s="4" t="n"/>
       <c r="N180" s="4" t="n"/>
       <c r="O180" s="4" t="n"/>
       <c r="P180" s="4" t="n"/>
       <c r="Q180" s="4" t="n"/>
+      <c r="R180" s="4" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="3" t="n"/>
@@ -4186,11 +4371,12 @@
       <c r="J181" s="4" t="n"/>
       <c r="K181" s="4" t="n"/>
       <c r="L181" s="4" t="n"/>
-      <c r="M181" s="3" t="n"/>
+      <c r="M181" s="4" t="n"/>
       <c r="N181" s="4" t="n"/>
       <c r="O181" s="4" t="n"/>
       <c r="P181" s="4" t="n"/>
       <c r="Q181" s="4" t="n"/>
+      <c r="R181" s="4" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="3" t="n"/>
@@ -4205,11 +4391,12 @@
       <c r="J182" s="4" t="n"/>
       <c r="K182" s="4" t="n"/>
       <c r="L182" s="4" t="n"/>
-      <c r="M182" s="3" t="n"/>
+      <c r="M182" s="4" t="n"/>
       <c r="N182" s="4" t="n"/>
       <c r="O182" s="4" t="n"/>
       <c r="P182" s="4" t="n"/>
       <c r="Q182" s="4" t="n"/>
+      <c r="R182" s="4" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="3" t="n"/>
@@ -4224,11 +4411,12 @@
       <c r="J183" s="4" t="n"/>
       <c r="K183" s="4" t="n"/>
       <c r="L183" s="4" t="n"/>
-      <c r="M183" s="3" t="n"/>
+      <c r="M183" s="4" t="n"/>
       <c r="N183" s="4" t="n"/>
       <c r="O183" s="4" t="n"/>
       <c r="P183" s="4" t="n"/>
       <c r="Q183" s="4" t="n"/>
+      <c r="R183" s="4" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="3" t="n"/>
@@ -4243,11 +4431,12 @@
       <c r="J184" s="4" t="n"/>
       <c r="K184" s="4" t="n"/>
       <c r="L184" s="4" t="n"/>
-      <c r="M184" s="3" t="n"/>
+      <c r="M184" s="4" t="n"/>
       <c r="N184" s="4" t="n"/>
       <c r="O184" s="4" t="n"/>
       <c r="P184" s="4" t="n"/>
       <c r="Q184" s="4" t="n"/>
+      <c r="R184" s="4" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="3" t="n"/>
@@ -4262,11 +4451,12 @@
       <c r="J185" s="4" t="n"/>
       <c r="K185" s="4" t="n"/>
       <c r="L185" s="4" t="n"/>
-      <c r="M185" s="3" t="n"/>
+      <c r="M185" s="4" t="n"/>
       <c r="N185" s="4" t="n"/>
       <c r="O185" s="4" t="n"/>
       <c r="P185" s="4" t="n"/>
       <c r="Q185" s="4" t="n"/>
+      <c r="R185" s="4" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="3" t="n"/>
@@ -4281,11 +4471,12 @@
       <c r="J186" s="4" t="n"/>
       <c r="K186" s="4" t="n"/>
       <c r="L186" s="4" t="n"/>
-      <c r="M186" s="3" t="n"/>
+      <c r="M186" s="4" t="n"/>
       <c r="N186" s="4" t="n"/>
       <c r="O186" s="4" t="n"/>
       <c r="P186" s="4" t="n"/>
       <c r="Q186" s="4" t="n"/>
+      <c r="R186" s="4" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="3" t="n"/>
@@ -4300,11 +4491,12 @@
       <c r="J187" s="4" t="n"/>
       <c r="K187" s="4" t="n"/>
       <c r="L187" s="4" t="n"/>
-      <c r="M187" s="3" t="n"/>
+      <c r="M187" s="4" t="n"/>
       <c r="N187" s="4" t="n"/>
       <c r="O187" s="4" t="n"/>
       <c r="P187" s="4" t="n"/>
       <c r="Q187" s="4" t="n"/>
+      <c r="R187" s="4" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="3" t="n"/>
@@ -4319,11 +4511,12 @@
       <c r="J188" s="4" t="n"/>
       <c r="K188" s="4" t="n"/>
       <c r="L188" s="4" t="n"/>
-      <c r="M188" s="3" t="n"/>
+      <c r="M188" s="4" t="n"/>
       <c r="N188" s="4" t="n"/>
       <c r="O188" s="4" t="n"/>
       <c r="P188" s="4" t="n"/>
       <c r="Q188" s="4" t="n"/>
+      <c r="R188" s="4" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="3" t="n"/>
@@ -4338,11 +4531,12 @@
       <c r="J189" s="4" t="n"/>
       <c r="K189" s="4" t="n"/>
       <c r="L189" s="4" t="n"/>
-      <c r="M189" s="3" t="n"/>
+      <c r="M189" s="4" t="n"/>
       <c r="N189" s="4" t="n"/>
       <c r="O189" s="4" t="n"/>
       <c r="P189" s="4" t="n"/>
       <c r="Q189" s="4" t="n"/>
+      <c r="R189" s="4" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="3" t="n"/>
@@ -4357,11 +4551,12 @@
       <c r="J190" s="4" t="n"/>
       <c r="K190" s="4" t="n"/>
       <c r="L190" s="4" t="n"/>
-      <c r="M190" s="3" t="n"/>
+      <c r="M190" s="4" t="n"/>
       <c r="N190" s="4" t="n"/>
       <c r="O190" s="4" t="n"/>
       <c r="P190" s="4" t="n"/>
       <c r="Q190" s="4" t="n"/>
+      <c r="R190" s="4" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="3" t="n"/>
@@ -4376,11 +4571,12 @@
       <c r="J191" s="4" t="n"/>
       <c r="K191" s="4" t="n"/>
       <c r="L191" s="4" t="n"/>
-      <c r="M191" s="3" t="n"/>
+      <c r="M191" s="4" t="n"/>
       <c r="N191" s="4" t="n"/>
       <c r="O191" s="4" t="n"/>
       <c r="P191" s="4" t="n"/>
       <c r="Q191" s="4" t="n"/>
+      <c r="R191" s="4" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="3" t="n"/>
@@ -4395,11 +4591,12 @@
       <c r="J192" s="4" t="n"/>
       <c r="K192" s="4" t="n"/>
       <c r="L192" s="4" t="n"/>
-      <c r="M192" s="3" t="n"/>
+      <c r="M192" s="4" t="n"/>
       <c r="N192" s="4" t="n"/>
       <c r="O192" s="4" t="n"/>
       <c r="P192" s="4" t="n"/>
       <c r="Q192" s="4" t="n"/>
+      <c r="R192" s="4" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="3" t="n"/>
@@ -4414,11 +4611,12 @@
       <c r="J193" s="4" t="n"/>
       <c r="K193" s="4" t="n"/>
       <c r="L193" s="4" t="n"/>
-      <c r="M193" s="3" t="n"/>
+      <c r="M193" s="4" t="n"/>
       <c r="N193" s="4" t="n"/>
       <c r="O193" s="4" t="n"/>
       <c r="P193" s="4" t="n"/>
       <c r="Q193" s="4" t="n"/>
+      <c r="R193" s="4" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="3" t="n"/>
@@ -4433,11 +4631,12 @@
       <c r="J194" s="4" t="n"/>
       <c r="K194" s="4" t="n"/>
       <c r="L194" s="4" t="n"/>
-      <c r="M194" s="3" t="n"/>
+      <c r="M194" s="4" t="n"/>
       <c r="N194" s="4" t="n"/>
       <c r="O194" s="4" t="n"/>
       <c r="P194" s="4" t="n"/>
       <c r="Q194" s="4" t="n"/>
+      <c r="R194" s="4" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="3" t="n"/>
@@ -4452,11 +4651,12 @@
       <c r="J195" s="4" t="n"/>
       <c r="K195" s="4" t="n"/>
       <c r="L195" s="4" t="n"/>
-      <c r="M195" s="3" t="n"/>
+      <c r="M195" s="4" t="n"/>
       <c r="N195" s="4" t="n"/>
       <c r="O195" s="4" t="n"/>
       <c r="P195" s="4" t="n"/>
       <c r="Q195" s="4" t="n"/>
+      <c r="R195" s="4" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="3" t="n"/>
@@ -4471,11 +4671,12 @@
       <c r="J196" s="4" t="n"/>
       <c r="K196" s="4" t="n"/>
       <c r="L196" s="4" t="n"/>
-      <c r="M196" s="3" t="n"/>
+      <c r="M196" s="4" t="n"/>
       <c r="N196" s="4" t="n"/>
       <c r="O196" s="4" t="n"/>
       <c r="P196" s="4" t="n"/>
       <c r="Q196" s="4" t="n"/>
+      <c r="R196" s="4" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="3" t="n"/>
@@ -4490,11 +4691,12 @@
       <c r="J197" s="4" t="n"/>
       <c r="K197" s="4" t="n"/>
       <c r="L197" s="4" t="n"/>
-      <c r="M197" s="3" t="n"/>
+      <c r="M197" s="4" t="n"/>
       <c r="N197" s="4" t="n"/>
       <c r="O197" s="4" t="n"/>
       <c r="P197" s="4" t="n"/>
       <c r="Q197" s="4" t="n"/>
+      <c r="R197" s="4" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="3" t="n"/>
@@ -4509,11 +4711,12 @@
       <c r="J198" s="4" t="n"/>
       <c r="K198" s="4" t="n"/>
       <c r="L198" s="4" t="n"/>
-      <c r="M198" s="3" t="n"/>
+      <c r="M198" s="4" t="n"/>
       <c r="N198" s="4" t="n"/>
       <c r="O198" s="4" t="n"/>
       <c r="P198" s="4" t="n"/>
       <c r="Q198" s="4" t="n"/>
+      <c r="R198" s="4" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="3" t="n"/>
@@ -4528,11 +4731,12 @@
       <c r="J199" s="4" t="n"/>
       <c r="K199" s="4" t="n"/>
       <c r="L199" s="4" t="n"/>
-      <c r="M199" s="3" t="n"/>
+      <c r="M199" s="4" t="n"/>
       <c r="N199" s="4" t="n"/>
       <c r="O199" s="4" t="n"/>
       <c r="P199" s="4" t="n"/>
       <c r="Q199" s="4" t="n"/>
+      <c r="R199" s="4" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="3" t="n"/>
@@ -4547,11 +4751,12 @@
       <c r="J200" s="4" t="n"/>
       <c r="K200" s="4" t="n"/>
       <c r="L200" s="4" t="n"/>
-      <c r="M200" s="3" t="n"/>
+      <c r="M200" s="4" t="n"/>
       <c r="N200" s="4" t="n"/>
       <c r="O200" s="4" t="n"/>
       <c r="P200" s="4" t="n"/>
       <c r="Q200" s="4" t="n"/>
+      <c r="R200" s="4" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="3" t="n"/>
@@ -4566,11 +4771,12 @@
       <c r="J201" s="4" t="n"/>
       <c r="K201" s="4" t="n"/>
       <c r="L201" s="4" t="n"/>
-      <c r="M201" s="3" t="n"/>
+      <c r="M201" s="4" t="n"/>
       <c r="N201" s="4" t="n"/>
       <c r="O201" s="4" t="n"/>
       <c r="P201" s="4" t="n"/>
       <c r="Q201" s="4" t="n"/>
+      <c r="R201" s="4" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="3" t="n"/>
@@ -4585,11 +4791,12 @@
       <c r="J202" s="4" t="n"/>
       <c r="K202" s="4" t="n"/>
       <c r="L202" s="4" t="n"/>
-      <c r="M202" s="3" t="n"/>
+      <c r="M202" s="4" t="n"/>
       <c r="N202" s="4" t="n"/>
       <c r="O202" s="4" t="n"/>
       <c r="P202" s="4" t="n"/>
       <c r="Q202" s="4" t="n"/>
+      <c r="R202" s="4" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="3" t="n"/>
@@ -4604,11 +4811,12 @@
       <c r="J203" s="4" t="n"/>
       <c r="K203" s="4" t="n"/>
       <c r="L203" s="4" t="n"/>
-      <c r="M203" s="3" t="n"/>
+      <c r="M203" s="4" t="n"/>
       <c r="N203" s="4" t="n"/>
       <c r="O203" s="4" t="n"/>
       <c r="P203" s="4" t="n"/>
       <c r="Q203" s="4" t="n"/>
+      <c r="R203" s="4" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="3" t="n"/>
@@ -4623,11 +4831,12 @@
       <c r="J204" s="4" t="n"/>
       <c r="K204" s="4" t="n"/>
       <c r="L204" s="4" t="n"/>
-      <c r="M204" s="3" t="n"/>
+      <c r="M204" s="4" t="n"/>
       <c r="N204" s="4" t="n"/>
       <c r="O204" s="4" t="n"/>
       <c r="P204" s="4" t="n"/>
       <c r="Q204" s="4" t="n"/>
+      <c r="R204" s="4" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="3" t="n"/>
@@ -4642,11 +4851,12 @@
       <c r="J205" s="4" t="n"/>
       <c r="K205" s="4" t="n"/>
       <c r="L205" s="4" t="n"/>
-      <c r="M205" s="3" t="n"/>
+      <c r="M205" s="4" t="n"/>
       <c r="N205" s="4" t="n"/>
       <c r="O205" s="4" t="n"/>
       <c r="P205" s="4" t="n"/>
       <c r="Q205" s="4" t="n"/>
+      <c r="R205" s="4" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="3" t="n"/>
@@ -4661,11 +4871,12 @@
       <c r="J206" s="4" t="n"/>
       <c r="K206" s="4" t="n"/>
       <c r="L206" s="4" t="n"/>
-      <c r="M206" s="3" t="n"/>
+      <c r="M206" s="4" t="n"/>
       <c r="N206" s="4" t="n"/>
       <c r="O206" s="4" t="n"/>
       <c r="P206" s="4" t="n"/>
       <c r="Q206" s="4" t="n"/>
+      <c r="R206" s="4" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="3" t="n"/>
@@ -4680,11 +4891,12 @@
       <c r="J207" s="4" t="n"/>
       <c r="K207" s="4" t="n"/>
       <c r="L207" s="4" t="n"/>
-      <c r="M207" s="3" t="n"/>
+      <c r="M207" s="4" t="n"/>
       <c r="N207" s="4" t="n"/>
       <c r="O207" s="4" t="n"/>
       <c r="P207" s="4" t="n"/>
       <c r="Q207" s="4" t="n"/>
+      <c r="R207" s="4" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="3" t="n"/>
@@ -4699,11 +4911,12 @@
       <c r="J208" s="4" t="n"/>
       <c r="K208" s="4" t="n"/>
       <c r="L208" s="4" t="n"/>
-      <c r="M208" s="3" t="n"/>
+      <c r="M208" s="4" t="n"/>
       <c r="N208" s="4" t="n"/>
       <c r="O208" s="4" t="n"/>
       <c r="P208" s="4" t="n"/>
       <c r="Q208" s="4" t="n"/>
+      <c r="R208" s="4" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="3" t="n"/>
@@ -4718,11 +4931,12 @@
       <c r="J209" s="4" t="n"/>
       <c r="K209" s="4" t="n"/>
       <c r="L209" s="4" t="n"/>
-      <c r="M209" s="3" t="n"/>
+      <c r="M209" s="4" t="n"/>
       <c r="N209" s="4" t="n"/>
       <c r="O209" s="4" t="n"/>
       <c r="P209" s="4" t="n"/>
       <c r="Q209" s="4" t="n"/>
+      <c r="R209" s="4" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="3" t="n"/>
@@ -4737,11 +4951,12 @@
       <c r="J210" s="4" t="n"/>
       <c r="K210" s="4" t="n"/>
       <c r="L210" s="4" t="n"/>
-      <c r="M210" s="3" t="n"/>
+      <c r="M210" s="4" t="n"/>
       <c r="N210" s="4" t="n"/>
       <c r="O210" s="4" t="n"/>
       <c r="P210" s="4" t="n"/>
       <c r="Q210" s="4" t="n"/>
+      <c r="R210" s="4" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="3" t="n"/>
@@ -4756,11 +4971,12 @@
       <c r="J211" s="4" t="n"/>
       <c r="K211" s="4" t="n"/>
       <c r="L211" s="4" t="n"/>
-      <c r="M211" s="3" t="n"/>
+      <c r="M211" s="4" t="n"/>
       <c r="N211" s="4" t="n"/>
       <c r="O211" s="4" t="n"/>
       <c r="P211" s="4" t="n"/>
       <c r="Q211" s="4" t="n"/>
+      <c r="R211" s="4" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="3" t="n"/>
@@ -4775,11 +4991,12 @@
       <c r="J212" s="4" t="n"/>
       <c r="K212" s="4" t="n"/>
       <c r="L212" s="4" t="n"/>
-      <c r="M212" s="3" t="n"/>
+      <c r="M212" s="4" t="n"/>
       <c r="N212" s="4" t="n"/>
       <c r="O212" s="4" t="n"/>
       <c r="P212" s="4" t="n"/>
       <c r="Q212" s="4" t="n"/>
+      <c r="R212" s="4" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="3" t="n"/>
@@ -4794,11 +5011,12 @@
       <c r="J213" s="4" t="n"/>
       <c r="K213" s="4" t="n"/>
       <c r="L213" s="4" t="n"/>
-      <c r="M213" s="3" t="n"/>
+      <c r="M213" s="4" t="n"/>
       <c r="N213" s="4" t="n"/>
       <c r="O213" s="4" t="n"/>
       <c r="P213" s="4" t="n"/>
       <c r="Q213" s="4" t="n"/>
+      <c r="R213" s="4" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="3" t="n"/>
@@ -4813,11 +5031,12 @@
       <c r="J214" s="4" t="n"/>
       <c r="K214" s="4" t="n"/>
       <c r="L214" s="4" t="n"/>
-      <c r="M214" s="3" t="n"/>
+      <c r="M214" s="4" t="n"/>
       <c r="N214" s="4" t="n"/>
       <c r="O214" s="4" t="n"/>
       <c r="P214" s="4" t="n"/>
       <c r="Q214" s="4" t="n"/>
+      <c r="R214" s="4" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="3" t="n"/>
@@ -4832,11 +5051,12 @@
       <c r="J215" s="4" t="n"/>
       <c r="K215" s="4" t="n"/>
       <c r="L215" s="4" t="n"/>
-      <c r="M215" s="3" t="n"/>
+      <c r="M215" s="4" t="n"/>
       <c r="N215" s="4" t="n"/>
       <c r="O215" s="4" t="n"/>
       <c r="P215" s="4" t="n"/>
       <c r="Q215" s="4" t="n"/>
+      <c r="R215" s="4" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="3" t="n"/>
@@ -4851,11 +5071,12 @@
       <c r="J216" s="4" t="n"/>
       <c r="K216" s="4" t="n"/>
       <c r="L216" s="4" t="n"/>
-      <c r="M216" s="3" t="n"/>
+      <c r="M216" s="4" t="n"/>
       <c r="N216" s="4" t="n"/>
       <c r="O216" s="4" t="n"/>
       <c r="P216" s="4" t="n"/>
       <c r="Q216" s="4" t="n"/>
+      <c r="R216" s="4" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="3" t="n"/>
@@ -4870,11 +5091,12 @@
       <c r="J217" s="4" t="n"/>
       <c r="K217" s="4" t="n"/>
       <c r="L217" s="4" t="n"/>
-      <c r="M217" s="3" t="n"/>
+      <c r="M217" s="4" t="n"/>
       <c r="N217" s="4" t="n"/>
       <c r="O217" s="4" t="n"/>
       <c r="P217" s="4" t="n"/>
       <c r="Q217" s="4" t="n"/>
+      <c r="R217" s="4" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="3" t="n"/>
@@ -4889,11 +5111,12 @@
       <c r="J218" s="4" t="n"/>
       <c r="K218" s="4" t="n"/>
       <c r="L218" s="4" t="n"/>
-      <c r="M218" s="3" t="n"/>
+      <c r="M218" s="4" t="n"/>
       <c r="N218" s="4" t="n"/>
       <c r="O218" s="4" t="n"/>
       <c r="P218" s="4" t="n"/>
       <c r="Q218" s="4" t="n"/>
+      <c r="R218" s="4" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="3" t="n"/>
@@ -4908,11 +5131,12 @@
       <c r="J219" s="4" t="n"/>
       <c r="K219" s="4" t="n"/>
       <c r="L219" s="4" t="n"/>
-      <c r="M219" s="3" t="n"/>
+      <c r="M219" s="4" t="n"/>
       <c r="N219" s="4" t="n"/>
       <c r="O219" s="4" t="n"/>
       <c r="P219" s="4" t="n"/>
       <c r="Q219" s="4" t="n"/>
+      <c r="R219" s="4" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="3" t="n"/>
@@ -4927,11 +5151,12 @@
       <c r="J220" s="4" t="n"/>
       <c r="K220" s="4" t="n"/>
       <c r="L220" s="4" t="n"/>
-      <c r="M220" s="3" t="n"/>
+      <c r="M220" s="4" t="n"/>
       <c r="N220" s="4" t="n"/>
       <c r="O220" s="4" t="n"/>
       <c r="P220" s="4" t="n"/>
       <c r="Q220" s="4" t="n"/>
+      <c r="R220" s="4" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="3" t="n"/>
@@ -4946,11 +5171,12 @@
       <c r="J221" s="4" t="n"/>
       <c r="K221" s="4" t="n"/>
       <c r="L221" s="4" t="n"/>
-      <c r="M221" s="3" t="n"/>
+      <c r="M221" s="4" t="n"/>
       <c r="N221" s="4" t="n"/>
       <c r="O221" s="4" t="n"/>
       <c r="P221" s="4" t="n"/>
       <c r="Q221" s="4" t="n"/>
+      <c r="R221" s="4" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="3" t="n"/>
@@ -4965,11 +5191,12 @@
       <c r="J222" s="4" t="n"/>
       <c r="K222" s="4" t="n"/>
       <c r="L222" s="4" t="n"/>
-      <c r="M222" s="3" t="n"/>
+      <c r="M222" s="4" t="n"/>
       <c r="N222" s="4" t="n"/>
       <c r="O222" s="4" t="n"/>
       <c r="P222" s="4" t="n"/>
       <c r="Q222" s="4" t="n"/>
+      <c r="R222" s="4" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="3" t="n"/>
@@ -4984,11 +5211,12 @@
       <c r="J223" s="4" t="n"/>
       <c r="K223" s="4" t="n"/>
       <c r="L223" s="4" t="n"/>
-      <c r="M223" s="3" t="n"/>
+      <c r="M223" s="4" t="n"/>
       <c r="N223" s="4" t="n"/>
       <c r="O223" s="4" t="n"/>
       <c r="P223" s="4" t="n"/>
       <c r="Q223" s="4" t="n"/>
+      <c r="R223" s="4" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="3" t="n"/>
@@ -5003,11 +5231,12 @@
       <c r="J224" s="4" t="n"/>
       <c r="K224" s="4" t="n"/>
       <c r="L224" s="4" t="n"/>
-      <c r="M224" s="3" t="n"/>
+      <c r="M224" s="4" t="n"/>
       <c r="N224" s="4" t="n"/>
       <c r="O224" s="4" t="n"/>
       <c r="P224" s="4" t="n"/>
       <c r="Q224" s="4" t="n"/>
+      <c r="R224" s="4" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="3" t="n"/>
@@ -5022,11 +5251,12 @@
       <c r="J225" s="4" t="n"/>
       <c r="K225" s="4" t="n"/>
       <c r="L225" s="4" t="n"/>
-      <c r="M225" s="3" t="n"/>
+      <c r="M225" s="4" t="n"/>
       <c r="N225" s="4" t="n"/>
       <c r="O225" s="4" t="n"/>
       <c r="P225" s="4" t="n"/>
       <c r="Q225" s="4" t="n"/>
+      <c r="R225" s="4" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="3" t="n"/>
@@ -5041,11 +5271,12 @@
       <c r="J226" s="4" t="n"/>
       <c r="K226" s="4" t="n"/>
       <c r="L226" s="4" t="n"/>
-      <c r="M226" s="3" t="n"/>
+      <c r="M226" s="4" t="n"/>
       <c r="N226" s="4" t="n"/>
       <c r="O226" s="4" t="n"/>
       <c r="P226" s="4" t="n"/>
       <c r="Q226" s="4" t="n"/>
+      <c r="R226" s="4" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="3" t="n"/>
@@ -5060,11 +5291,12 @@
       <c r="J227" s="4" t="n"/>
       <c r="K227" s="4" t="n"/>
       <c r="L227" s="4" t="n"/>
-      <c r="M227" s="3" t="n"/>
+      <c r="M227" s="4" t="n"/>
       <c r="N227" s="4" t="n"/>
       <c r="O227" s="4" t="n"/>
       <c r="P227" s="4" t="n"/>
       <c r="Q227" s="4" t="n"/>
+      <c r="R227" s="4" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="3" t="n"/>
@@ -5079,11 +5311,12 @@
       <c r="J228" s="4" t="n"/>
       <c r="K228" s="4" t="n"/>
       <c r="L228" s="4" t="n"/>
-      <c r="M228" s="3" t="n"/>
+      <c r="M228" s="4" t="n"/>
       <c r="N228" s="4" t="n"/>
       <c r="O228" s="4" t="n"/>
       <c r="P228" s="4" t="n"/>
       <c r="Q228" s="4" t="n"/>
+      <c r="R228" s="4" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="3" t="n"/>
@@ -5098,11 +5331,12 @@
       <c r="J229" s="4" t="n"/>
       <c r="K229" s="4" t="n"/>
       <c r="L229" s="4" t="n"/>
-      <c r="M229" s="3" t="n"/>
+      <c r="M229" s="4" t="n"/>
       <c r="N229" s="4" t="n"/>
       <c r="O229" s="4" t="n"/>
       <c r="P229" s="4" t="n"/>
       <c r="Q229" s="4" t="n"/>
+      <c r="R229" s="4" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="3" t="n"/>
@@ -5117,11 +5351,12 @@
       <c r="J230" s="4" t="n"/>
       <c r="K230" s="4" t="n"/>
       <c r="L230" s="4" t="n"/>
-      <c r="M230" s="3" t="n"/>
+      <c r="M230" s="4" t="n"/>
       <c r="N230" s="4" t="n"/>
       <c r="O230" s="4" t="n"/>
       <c r="P230" s="4" t="n"/>
       <c r="Q230" s="4" t="n"/>
+      <c r="R230" s="4" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="3" t="n"/>
@@ -5136,11 +5371,12 @@
       <c r="J231" s="4" t="n"/>
       <c r="K231" s="4" t="n"/>
       <c r="L231" s="4" t="n"/>
-      <c r="M231" s="3" t="n"/>
+      <c r="M231" s="4" t="n"/>
       <c r="N231" s="4" t="n"/>
       <c r="O231" s="4" t="n"/>
       <c r="P231" s="4" t="n"/>
       <c r="Q231" s="4" t="n"/>
+      <c r="R231" s="4" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="3" t="n"/>
@@ -5155,11 +5391,12 @@
       <c r="J232" s="4" t="n"/>
       <c r="K232" s="4" t="n"/>
       <c r="L232" s="4" t="n"/>
-      <c r="M232" s="3" t="n"/>
+      <c r="M232" s="4" t="n"/>
       <c r="N232" s="4" t="n"/>
       <c r="O232" s="4" t="n"/>
       <c r="P232" s="4" t="n"/>
       <c r="Q232" s="4" t="n"/>
+      <c r="R232" s="4" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="3" t="n"/>
@@ -5174,11 +5411,12 @@
       <c r="J233" s="4" t="n"/>
       <c r="K233" s="4" t="n"/>
       <c r="L233" s="4" t="n"/>
-      <c r="M233" s="3" t="n"/>
+      <c r="M233" s="4" t="n"/>
       <c r="N233" s="4" t="n"/>
       <c r="O233" s="4" t="n"/>
       <c r="P233" s="4" t="n"/>
       <c r="Q233" s="4" t="n"/>
+      <c r="R233" s="4" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="3" t="n"/>
@@ -5193,11 +5431,12 @@
       <c r="J234" s="4" t="n"/>
       <c r="K234" s="4" t="n"/>
       <c r="L234" s="4" t="n"/>
-      <c r="M234" s="3" t="n"/>
+      <c r="M234" s="4" t="n"/>
       <c r="N234" s="4" t="n"/>
       <c r="O234" s="4" t="n"/>
       <c r="P234" s="4" t="n"/>
       <c r="Q234" s="4" t="n"/>
+      <c r="R234" s="4" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="3" t="n"/>
@@ -5212,11 +5451,12 @@
       <c r="J235" s="4" t="n"/>
       <c r="K235" s="4" t="n"/>
       <c r="L235" s="4" t="n"/>
-      <c r="M235" s="3" t="n"/>
+      <c r="M235" s="4" t="n"/>
       <c r="N235" s="4" t="n"/>
       <c r="O235" s="4" t="n"/>
       <c r="P235" s="4" t="n"/>
       <c r="Q235" s="4" t="n"/>
+      <c r="R235" s="4" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="3" t="n"/>
@@ -5231,11 +5471,12 @@
       <c r="J236" s="4" t="n"/>
       <c r="K236" s="4" t="n"/>
       <c r="L236" s="4" t="n"/>
-      <c r="M236" s="3" t="n"/>
+      <c r="M236" s="4" t="n"/>
       <c r="N236" s="4" t="n"/>
       <c r="O236" s="4" t="n"/>
       <c r="P236" s="4" t="n"/>
       <c r="Q236" s="4" t="n"/>
+      <c r="R236" s="4" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="3" t="n"/>
@@ -5250,11 +5491,12 @@
       <c r="J237" s="4" t="n"/>
       <c r="K237" s="4" t="n"/>
       <c r="L237" s="4" t="n"/>
-      <c r="M237" s="3" t="n"/>
+      <c r="M237" s="4" t="n"/>
       <c r="N237" s="4" t="n"/>
       <c r="O237" s="4" t="n"/>
       <c r="P237" s="4" t="n"/>
       <c r="Q237" s="4" t="n"/>
+      <c r="R237" s="4" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="3" t="n"/>
@@ -5269,11 +5511,12 @@
       <c r="J238" s="4" t="n"/>
       <c r="K238" s="4" t="n"/>
       <c r="L238" s="4" t="n"/>
-      <c r="M238" s="3" t="n"/>
+      <c r="M238" s="4" t="n"/>
       <c r="N238" s="4" t="n"/>
       <c r="O238" s="4" t="n"/>
       <c r="P238" s="4" t="n"/>
       <c r="Q238" s="4" t="n"/>
+      <c r="R238" s="4" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="3" t="n"/>
@@ -5288,11 +5531,12 @@
       <c r="J239" s="4" t="n"/>
       <c r="K239" s="4" t="n"/>
       <c r="L239" s="4" t="n"/>
-      <c r="M239" s="3" t="n"/>
+      <c r="M239" s="4" t="n"/>
       <c r="N239" s="4" t="n"/>
       <c r="O239" s="4" t="n"/>
       <c r="P239" s="4" t="n"/>
       <c r="Q239" s="4" t="n"/>
+      <c r="R239" s="4" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="3" t="n"/>
@@ -5307,11 +5551,12 @@
       <c r="J240" s="4" t="n"/>
       <c r="K240" s="4" t="n"/>
       <c r="L240" s="4" t="n"/>
-      <c r="M240" s="3" t="n"/>
+      <c r="M240" s="4" t="n"/>
       <c r="N240" s="4" t="n"/>
       <c r="O240" s="4" t="n"/>
       <c r="P240" s="4" t="n"/>
       <c r="Q240" s="4" t="n"/>
+      <c r="R240" s="4" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="3" t="n"/>
@@ -5326,11 +5571,12 @@
       <c r="J241" s="4" t="n"/>
       <c r="K241" s="4" t="n"/>
       <c r="L241" s="4" t="n"/>
-      <c r="M241" s="3" t="n"/>
+      <c r="M241" s="4" t="n"/>
       <c r="N241" s="4" t="n"/>
       <c r="O241" s="4" t="n"/>
       <c r="P241" s="4" t="n"/>
       <c r="Q241" s="4" t="n"/>
+      <c r="R241" s="4" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="3" t="n"/>
@@ -5345,11 +5591,12 @@
       <c r="J242" s="4" t="n"/>
       <c r="K242" s="4" t="n"/>
       <c r="L242" s="4" t="n"/>
-      <c r="M242" s="3" t="n"/>
+      <c r="M242" s="4" t="n"/>
       <c r="N242" s="4" t="n"/>
       <c r="O242" s="4" t="n"/>
       <c r="P242" s="4" t="n"/>
       <c r="Q242" s="4" t="n"/>
+      <c r="R242" s="4" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="3" t="n"/>
@@ -5364,11 +5611,12 @@
       <c r="J243" s="4" t="n"/>
       <c r="K243" s="4" t="n"/>
       <c r="L243" s="4" t="n"/>
-      <c r="M243" s="3" t="n"/>
+      <c r="M243" s="4" t="n"/>
       <c r="N243" s="4" t="n"/>
       <c r="O243" s="4" t="n"/>
       <c r="P243" s="4" t="n"/>
       <c r="Q243" s="4" t="n"/>
+      <c r="R243" s="4" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="3" t="n"/>
@@ -5383,11 +5631,12 @@
       <c r="J244" s="4" t="n"/>
       <c r="K244" s="4" t="n"/>
       <c r="L244" s="4" t="n"/>
-      <c r="M244" s="3" t="n"/>
+      <c r="M244" s="4" t="n"/>
       <c r="N244" s="4" t="n"/>
       <c r="O244" s="4" t="n"/>
       <c r="P244" s="4" t="n"/>
       <c r="Q244" s="4" t="n"/>
+      <c r="R244" s="4" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="3" t="n"/>
@@ -5402,11 +5651,12 @@
       <c r="J245" s="4" t="n"/>
       <c r="K245" s="4" t="n"/>
       <c r="L245" s="4" t="n"/>
-      <c r="M245" s="3" t="n"/>
+      <c r="M245" s="4" t="n"/>
       <c r="N245" s="4" t="n"/>
       <c r="O245" s="4" t="n"/>
       <c r="P245" s="4" t="n"/>
       <c r="Q245" s="4" t="n"/>
+      <c r="R245" s="4" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="3" t="n"/>
@@ -5421,11 +5671,12 @@
       <c r="J246" s="4" t="n"/>
       <c r="K246" s="4" t="n"/>
       <c r="L246" s="4" t="n"/>
-      <c r="M246" s="3" t="n"/>
+      <c r="M246" s="4" t="n"/>
       <c r="N246" s="4" t="n"/>
       <c r="O246" s="4" t="n"/>
       <c r="P246" s="4" t="n"/>
       <c r="Q246" s="4" t="n"/>
+      <c r="R246" s="4" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="3" t="n"/>
@@ -5440,11 +5691,12 @@
       <c r="J247" s="4" t="n"/>
       <c r="K247" s="4" t="n"/>
       <c r="L247" s="4" t="n"/>
-      <c r="M247" s="3" t="n"/>
+      <c r="M247" s="4" t="n"/>
       <c r="N247" s="4" t="n"/>
       <c r="O247" s="4" t="n"/>
       <c r="P247" s="4" t="n"/>
       <c r="Q247" s="4" t="n"/>
+      <c r="R247" s="4" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="3" t="n"/>
@@ -5459,11 +5711,12 @@
       <c r="J248" s="4" t="n"/>
       <c r="K248" s="4" t="n"/>
       <c r="L248" s="4" t="n"/>
-      <c r="M248" s="3" t="n"/>
+      <c r="M248" s="4" t="n"/>
       <c r="N248" s="4" t="n"/>
       <c r="O248" s="4" t="n"/>
       <c r="P248" s="4" t="n"/>
       <c r="Q248" s="4" t="n"/>
+      <c r="R248" s="4" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="3" t="n"/>
@@ -5478,11 +5731,12 @@
       <c r="J249" s="4" t="n"/>
       <c r="K249" s="4" t="n"/>
       <c r="L249" s="4" t="n"/>
-      <c r="M249" s="3" t="n"/>
+      <c r="M249" s="4" t="n"/>
       <c r="N249" s="4" t="n"/>
       <c r="O249" s="4" t="n"/>
       <c r="P249" s="4" t="n"/>
       <c r="Q249" s="4" t="n"/>
+      <c r="R249" s="4" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="3" t="n"/>
@@ -5497,11 +5751,12 @@
       <c r="J250" s="4" t="n"/>
       <c r="K250" s="4" t="n"/>
       <c r="L250" s="4" t="n"/>
-      <c r="M250" s="3" t="n"/>
+      <c r="M250" s="4" t="n"/>
       <c r="N250" s="4" t="n"/>
       <c r="O250" s="4" t="n"/>
       <c r="P250" s="4" t="n"/>
       <c r="Q250" s="4" t="n"/>
+      <c r="R250" s="4" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="3" t="n"/>
@@ -5516,11 +5771,12 @@
       <c r="J251" s="4" t="n"/>
       <c r="K251" s="4" t="n"/>
       <c r="L251" s="4" t="n"/>
-      <c r="M251" s="3" t="n"/>
+      <c r="M251" s="4" t="n"/>
       <c r="N251" s="4" t="n"/>
       <c r="O251" s="4" t="n"/>
       <c r="P251" s="4" t="n"/>
       <c r="Q251" s="4" t="n"/>
+      <c r="R251" s="4" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="3" t="n"/>
@@ -5535,11 +5791,12 @@
       <c r="J252" s="4" t="n"/>
       <c r="K252" s="4" t="n"/>
       <c r="L252" s="4" t="n"/>
-      <c r="M252" s="3" t="n"/>
+      <c r="M252" s="4" t="n"/>
       <c r="N252" s="4" t="n"/>
       <c r="O252" s="4" t="n"/>
       <c r="P252" s="4" t="n"/>
       <c r="Q252" s="4" t="n"/>
+      <c r="R252" s="4" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="3" t="n"/>
@@ -5554,11 +5811,12 @@
       <c r="J253" s="4" t="n"/>
       <c r="K253" s="4" t="n"/>
       <c r="L253" s="4" t="n"/>
-      <c r="M253" s="3" t="n"/>
+      <c r="M253" s="4" t="n"/>
       <c r="N253" s="4" t="n"/>
       <c r="O253" s="4" t="n"/>
       <c r="P253" s="4" t="n"/>
       <c r="Q253" s="4" t="n"/>
+      <c r="R253" s="4" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="3" t="n"/>
@@ -5573,11 +5831,12 @@
       <c r="J254" s="4" t="n"/>
       <c r="K254" s="4" t="n"/>
       <c r="L254" s="4" t="n"/>
-      <c r="M254" s="3" t="n"/>
+      <c r="M254" s="4" t="n"/>
       <c r="N254" s="4" t="n"/>
       <c r="O254" s="4" t="n"/>
       <c r="P254" s="4" t="n"/>
       <c r="Q254" s="4" t="n"/>
+      <c r="R254" s="4" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="3" t="n"/>
@@ -5592,11 +5851,12 @@
       <c r="J255" s="4" t="n"/>
       <c r="K255" s="4" t="n"/>
       <c r="L255" s="4" t="n"/>
-      <c r="M255" s="3" t="n"/>
+      <c r="M255" s="4" t="n"/>
       <c r="N255" s="4" t="n"/>
       <c r="O255" s="4" t="n"/>
       <c r="P255" s="4" t="n"/>
       <c r="Q255" s="4" t="n"/>
+      <c r="R255" s="4" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="3" t="n"/>
@@ -5611,11 +5871,12 @@
       <c r="J256" s="4" t="n"/>
       <c r="K256" s="4" t="n"/>
       <c r="L256" s="4" t="n"/>
-      <c r="M256" s="3" t="n"/>
+      <c r="M256" s="4" t="n"/>
       <c r="N256" s="4" t="n"/>
       <c r="O256" s="4" t="n"/>
       <c r="P256" s="4" t="n"/>
       <c r="Q256" s="4" t="n"/>
+      <c r="R256" s="4" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="3" t="n"/>
@@ -5630,11 +5891,12 @@
       <c r="J257" s="4" t="n"/>
       <c r="K257" s="4" t="n"/>
       <c r="L257" s="4" t="n"/>
-      <c r="M257" s="3" t="n"/>
+      <c r="M257" s="4" t="n"/>
       <c r="N257" s="4" t="n"/>
       <c r="O257" s="4" t="n"/>
       <c r="P257" s="4" t="n"/>
       <c r="Q257" s="4" t="n"/>
+      <c r="R257" s="4" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="3" t="n"/>
@@ -5649,11 +5911,12 @@
       <c r="J258" s="4" t="n"/>
       <c r="K258" s="4" t="n"/>
       <c r="L258" s="4" t="n"/>
-      <c r="M258" s="3" t="n"/>
+      <c r="M258" s="4" t="n"/>
       <c r="N258" s="4" t="n"/>
       <c r="O258" s="4" t="n"/>
       <c r="P258" s="4" t="n"/>
       <c r="Q258" s="4" t="n"/>
+      <c r="R258" s="4" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="3" t="n"/>
@@ -5668,11 +5931,12 @@
       <c r="J259" s="4" t="n"/>
       <c r="K259" s="4" t="n"/>
       <c r="L259" s="4" t="n"/>
-      <c r="M259" s="3" t="n"/>
+      <c r="M259" s="4" t="n"/>
       <c r="N259" s="4" t="n"/>
       <c r="O259" s="4" t="n"/>
       <c r="P259" s="4" t="n"/>
       <c r="Q259" s="4" t="n"/>
+      <c r="R259" s="4" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="3" t="n"/>
@@ -5687,11 +5951,12 @@
       <c r="J260" s="4" t="n"/>
       <c r="K260" s="4" t="n"/>
       <c r="L260" s="4" t="n"/>
-      <c r="M260" s="3" t="n"/>
+      <c r="M260" s="4" t="n"/>
       <c r="N260" s="4" t="n"/>
       <c r="O260" s="4" t="n"/>
       <c r="P260" s="4" t="n"/>
       <c r="Q260" s="4" t="n"/>
+      <c r="R260" s="4" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="3" t="n"/>
@@ -5706,11 +5971,12 @@
       <c r="J261" s="4" t="n"/>
       <c r="K261" s="4" t="n"/>
       <c r="L261" s="4" t="n"/>
-      <c r="M261" s="3" t="n"/>
+      <c r="M261" s="4" t="n"/>
       <c r="N261" s="4" t="n"/>
       <c r="O261" s="4" t="n"/>
       <c r="P261" s="4" t="n"/>
       <c r="Q261" s="4" t="n"/>
+      <c r="R261" s="4" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="3" t="n"/>
@@ -5725,11 +5991,12 @@
       <c r="J262" s="4" t="n"/>
       <c r="K262" s="4" t="n"/>
       <c r="L262" s="4" t="n"/>
-      <c r="M262" s="3" t="n"/>
+      <c r="M262" s="4" t="n"/>
       <c r="N262" s="4" t="n"/>
       <c r="O262" s="4" t="n"/>
       <c r="P262" s="4" t="n"/>
       <c r="Q262" s="4" t="n"/>
+      <c r="R262" s="4" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="3" t="n"/>
@@ -5744,11 +6011,12 @@
       <c r="J263" s="4" t="n"/>
       <c r="K263" s="4" t="n"/>
       <c r="L263" s="4" t="n"/>
-      <c r="M263" s="3" t="n"/>
+      <c r="M263" s="4" t="n"/>
       <c r="N263" s="4" t="n"/>
       <c r="O263" s="4" t="n"/>
       <c r="P263" s="4" t="n"/>
       <c r="Q263" s="4" t="n"/>
+      <c r="R263" s="4" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="3" t="n"/>
@@ -5763,11 +6031,12 @@
       <c r="J264" s="4" t="n"/>
       <c r="K264" s="4" t="n"/>
       <c r="L264" s="4" t="n"/>
-      <c r="M264" s="3" t="n"/>
+      <c r="M264" s="4" t="n"/>
       <c r="N264" s="4" t="n"/>
       <c r="O264" s="4" t="n"/>
       <c r="P264" s="4" t="n"/>
       <c r="Q264" s="4" t="n"/>
+      <c r="R264" s="4" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="3" t="n"/>
@@ -5782,11 +6051,12 @@
       <c r="J265" s="4" t="n"/>
       <c r="K265" s="4" t="n"/>
       <c r="L265" s="4" t="n"/>
-      <c r="M265" s="3" t="n"/>
+      <c r="M265" s="4" t="n"/>
       <c r="N265" s="4" t="n"/>
       <c r="O265" s="4" t="n"/>
       <c r="P265" s="4" t="n"/>
       <c r="Q265" s="4" t="n"/>
+      <c r="R265" s="4" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="3" t="n"/>
@@ -5801,11 +6071,12 @@
       <c r="J266" s="4" t="n"/>
       <c r="K266" s="4" t="n"/>
       <c r="L266" s="4" t="n"/>
-      <c r="M266" s="3" t="n"/>
+      <c r="M266" s="4" t="n"/>
       <c r="N266" s="4" t="n"/>
       <c r="O266" s="4" t="n"/>
       <c r="P266" s="4" t="n"/>
       <c r="Q266" s="4" t="n"/>
+      <c r="R266" s="4" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="3" t="n"/>
@@ -5820,11 +6091,12 @@
       <c r="J267" s="4" t="n"/>
       <c r="K267" s="4" t="n"/>
       <c r="L267" s="4" t="n"/>
-      <c r="M267" s="3" t="n"/>
+      <c r="M267" s="4" t="n"/>
       <c r="N267" s="4" t="n"/>
       <c r="O267" s="4" t="n"/>
       <c r="P267" s="4" t="n"/>
       <c r="Q267" s="4" t="n"/>
+      <c r="R267" s="4" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="3" t="n"/>
@@ -5839,11 +6111,12 @@
       <c r="J268" s="4" t="n"/>
       <c r="K268" s="4" t="n"/>
       <c r="L268" s="4" t="n"/>
-      <c r="M268" s="3" t="n"/>
+      <c r="M268" s="4" t="n"/>
       <c r="N268" s="4" t="n"/>
       <c r="O268" s="4" t="n"/>
       <c r="P268" s="4" t="n"/>
       <c r="Q268" s="4" t="n"/>
+      <c r="R268" s="4" t="n"/>
     </row>
     <row r="269">
       <c r="A269" s="3" t="n"/>
@@ -5858,11 +6131,12 @@
       <c r="J269" s="4" t="n"/>
       <c r="K269" s="4" t="n"/>
       <c r="L269" s="4" t="n"/>
-      <c r="M269" s="3" t="n"/>
+      <c r="M269" s="4" t="n"/>
       <c r="N269" s="4" t="n"/>
       <c r="O269" s="4" t="n"/>
       <c r="P269" s="4" t="n"/>
       <c r="Q269" s="4" t="n"/>
+      <c r="R269" s="4" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="3" t="n"/>
@@ -5877,11 +6151,12 @@
       <c r="J270" s="4" t="n"/>
       <c r="K270" s="4" t="n"/>
       <c r="L270" s="4" t="n"/>
-      <c r="M270" s="3" t="n"/>
+      <c r="M270" s="4" t="n"/>
       <c r="N270" s="4" t="n"/>
       <c r="O270" s="4" t="n"/>
       <c r="P270" s="4" t="n"/>
       <c r="Q270" s="4" t="n"/>
+      <c r="R270" s="4" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="3" t="n"/>
@@ -5896,11 +6171,12 @@
       <c r="J271" s="4" t="n"/>
       <c r="K271" s="4" t="n"/>
       <c r="L271" s="4" t="n"/>
-      <c r="M271" s="3" t="n"/>
+      <c r="M271" s="4" t="n"/>
       <c r="N271" s="4" t="n"/>
       <c r="O271" s="4" t="n"/>
       <c r="P271" s="4" t="n"/>
       <c r="Q271" s="4" t="n"/>
+      <c r="R271" s="4" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="3" t="n"/>
@@ -5915,11 +6191,12 @@
       <c r="J272" s="4" t="n"/>
       <c r="K272" s="4" t="n"/>
       <c r="L272" s="4" t="n"/>
-      <c r="M272" s="3" t="n"/>
+      <c r="M272" s="4" t="n"/>
       <c r="N272" s="4" t="n"/>
       <c r="O272" s="4" t="n"/>
       <c r="P272" s="4" t="n"/>
       <c r="Q272" s="4" t="n"/>
+      <c r="R272" s="4" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="3" t="n"/>
@@ -5934,11 +6211,12 @@
       <c r="J273" s="4" t="n"/>
       <c r="K273" s="4" t="n"/>
       <c r="L273" s="4" t="n"/>
-      <c r="M273" s="3" t="n"/>
+      <c r="M273" s="4" t="n"/>
       <c r="N273" s="4" t="n"/>
       <c r="O273" s="4" t="n"/>
       <c r="P273" s="4" t="n"/>
       <c r="Q273" s="4" t="n"/>
+      <c r="R273" s="4" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="3" t="n"/>
@@ -5953,11 +6231,12 @@
       <c r="J274" s="4" t="n"/>
       <c r="K274" s="4" t="n"/>
       <c r="L274" s="4" t="n"/>
-      <c r="M274" s="3" t="n"/>
+      <c r="M274" s="4" t="n"/>
       <c r="N274" s="4" t="n"/>
       <c r="O274" s="4" t="n"/>
       <c r="P274" s="4" t="n"/>
       <c r="Q274" s="4" t="n"/>
+      <c r="R274" s="4" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="3" t="n"/>
@@ -5972,11 +6251,12 @@
       <c r="J275" s="4" t="n"/>
       <c r="K275" s="4" t="n"/>
       <c r="L275" s="4" t="n"/>
-      <c r="M275" s="3" t="n"/>
+      <c r="M275" s="4" t="n"/>
       <c r="N275" s="4" t="n"/>
       <c r="O275" s="4" t="n"/>
       <c r="P275" s="4" t="n"/>
       <c r="Q275" s="4" t="n"/>
+      <c r="R275" s="4" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="3" t="n"/>
@@ -5991,11 +6271,12 @@
       <c r="J276" s="4" t="n"/>
       <c r="K276" s="4" t="n"/>
       <c r="L276" s="4" t="n"/>
-      <c r="M276" s="3" t="n"/>
+      <c r="M276" s="4" t="n"/>
       <c r="N276" s="4" t="n"/>
       <c r="O276" s="4" t="n"/>
       <c r="P276" s="4" t="n"/>
       <c r="Q276" s="4" t="n"/>
+      <c r="R276" s="4" t="n"/>
     </row>
     <row r="277">
       <c r="A277" s="3" t="n"/>
@@ -6010,11 +6291,12 @@
       <c r="J277" s="4" t="n"/>
       <c r="K277" s="4" t="n"/>
       <c r="L277" s="4" t="n"/>
-      <c r="M277" s="3" t="n"/>
+      <c r="M277" s="4" t="n"/>
       <c r="N277" s="4" t="n"/>
       <c r="O277" s="4" t="n"/>
       <c r="P277" s="4" t="n"/>
       <c r="Q277" s="4" t="n"/>
+      <c r="R277" s="4" t="n"/>
     </row>
     <row r="278">
       <c r="A278" s="3" t="n"/>
@@ -6029,11 +6311,12 @@
       <c r="J278" s="4" t="n"/>
       <c r="K278" s="4" t="n"/>
       <c r="L278" s="4" t="n"/>
-      <c r="M278" s="3" t="n"/>
+      <c r="M278" s="4" t="n"/>
       <c r="N278" s="4" t="n"/>
       <c r="O278" s="4" t="n"/>
       <c r="P278" s="4" t="n"/>
       <c r="Q278" s="4" t="n"/>
+      <c r="R278" s="4" t="n"/>
     </row>
     <row r="279">
       <c r="A279" s="3" t="n"/>
@@ -6048,11 +6331,12 @@
       <c r="J279" s="4" t="n"/>
       <c r="K279" s="4" t="n"/>
       <c r="L279" s="4" t="n"/>
-      <c r="M279" s="3" t="n"/>
+      <c r="M279" s="4" t="n"/>
       <c r="N279" s="4" t="n"/>
       <c r="O279" s="4" t="n"/>
       <c r="P279" s="4" t="n"/>
       <c r="Q279" s="4" t="n"/>
+      <c r="R279" s="4" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="3" t="n"/>
@@ -6067,11 +6351,12 @@
       <c r="J280" s="4" t="n"/>
       <c r="K280" s="4" t="n"/>
       <c r="L280" s="4" t="n"/>
-      <c r="M280" s="3" t="n"/>
+      <c r="M280" s="4" t="n"/>
       <c r="N280" s="4" t="n"/>
       <c r="O280" s="4" t="n"/>
       <c r="P280" s="4" t="n"/>
       <c r="Q280" s="4" t="n"/>
+      <c r="R280" s="4" t="n"/>
     </row>
     <row r="281">
       <c r="A281" s="3" t="n"/>
@@ -6086,11 +6371,12 @@
       <c r="J281" s="4" t="n"/>
       <c r="K281" s="4" t="n"/>
       <c r="L281" s="4" t="n"/>
-      <c r="M281" s="3" t="n"/>
+      <c r="M281" s="4" t="n"/>
       <c r="N281" s="4" t="n"/>
       <c r="O281" s="4" t="n"/>
       <c r="P281" s="4" t="n"/>
       <c r="Q281" s="4" t="n"/>
+      <c r="R281" s="4" t="n"/>
     </row>
     <row r="282">
       <c r="A282" s="3" t="n"/>
@@ -6105,11 +6391,12 @@
       <c r="J282" s="4" t="n"/>
       <c r="K282" s="4" t="n"/>
       <c r="L282" s="4" t="n"/>
-      <c r="M282" s="3" t="n"/>
+      <c r="M282" s="4" t="n"/>
       <c r="N282" s="4" t="n"/>
       <c r="O282" s="4" t="n"/>
       <c r="P282" s="4" t="n"/>
       <c r="Q282" s="4" t="n"/>
+      <c r="R282" s="4" t="n"/>
     </row>
     <row r="283">
       <c r="A283" s="3" t="n"/>
@@ -6124,11 +6411,12 @@
       <c r="J283" s="4" t="n"/>
       <c r="K283" s="4" t="n"/>
       <c r="L283" s="4" t="n"/>
-      <c r="M283" s="3" t="n"/>
+      <c r="M283" s="4" t="n"/>
       <c r="N283" s="4" t="n"/>
       <c r="O283" s="4" t="n"/>
       <c r="P283" s="4" t="n"/>
       <c r="Q283" s="4" t="n"/>
+      <c r="R283" s="4" t="n"/>
     </row>
     <row r="284">
       <c r="A284" s="3" t="n"/>
@@ -6143,11 +6431,12 @@
       <c r="J284" s="4" t="n"/>
       <c r="K284" s="4" t="n"/>
       <c r="L284" s="4" t="n"/>
-      <c r="M284" s="3" t="n"/>
+      <c r="M284" s="4" t="n"/>
       <c r="N284" s="4" t="n"/>
       <c r="O284" s="4" t="n"/>
       <c r="P284" s="4" t="n"/>
       <c r="Q284" s="4" t="n"/>
+      <c r="R284" s="4" t="n"/>
     </row>
     <row r="285">
       <c r="A285" s="3" t="n"/>
@@ -6162,11 +6451,12 @@
       <c r="J285" s="4" t="n"/>
       <c r="K285" s="4" t="n"/>
       <c r="L285" s="4" t="n"/>
-      <c r="M285" s="3" t="n"/>
+      <c r="M285" s="4" t="n"/>
       <c r="N285" s="4" t="n"/>
       <c r="O285" s="4" t="n"/>
       <c r="P285" s="4" t="n"/>
       <c r="Q285" s="4" t="n"/>
+      <c r="R285" s="4" t="n"/>
     </row>
     <row r="286">
       <c r="A286" s="3" t="n"/>
@@ -6181,11 +6471,12 @@
       <c r="J286" s="4" t="n"/>
       <c r="K286" s="4" t="n"/>
       <c r="L286" s="4" t="n"/>
-      <c r="M286" s="3" t="n"/>
+      <c r="M286" s="4" t="n"/>
       <c r="N286" s="4" t="n"/>
       <c r="O286" s="4" t="n"/>
       <c r="P286" s="4" t="n"/>
       <c r="Q286" s="4" t="n"/>
+      <c r="R286" s="4" t="n"/>
     </row>
     <row r="287">
       <c r="A287" s="3" t="n"/>
@@ -6200,11 +6491,12 @@
       <c r="J287" s="4" t="n"/>
       <c r="K287" s="4" t="n"/>
       <c r="L287" s="4" t="n"/>
-      <c r="M287" s="3" t="n"/>
+      <c r="M287" s="4" t="n"/>
       <c r="N287" s="4" t="n"/>
       <c r="O287" s="4" t="n"/>
       <c r="P287" s="4" t="n"/>
       <c r="Q287" s="4" t="n"/>
+      <c r="R287" s="4" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="3" t="n"/>
@@ -6219,11 +6511,12 @@
       <c r="J288" s="4" t="n"/>
       <c r="K288" s="4" t="n"/>
       <c r="L288" s="4" t="n"/>
-      <c r="M288" s="3" t="n"/>
+      <c r="M288" s="4" t="n"/>
       <c r="N288" s="4" t="n"/>
       <c r="O288" s="4" t="n"/>
       <c r="P288" s="4" t="n"/>
       <c r="Q288" s="4" t="n"/>
+      <c r="R288" s="4" t="n"/>
     </row>
     <row r="289">
       <c r="A289" s="3" t="n"/>
@@ -6238,11 +6531,12 @@
       <c r="J289" s="4" t="n"/>
       <c r="K289" s="4" t="n"/>
       <c r="L289" s="4" t="n"/>
-      <c r="M289" s="3" t="n"/>
+      <c r="M289" s="4" t="n"/>
       <c r="N289" s="4" t="n"/>
       <c r="O289" s="4" t="n"/>
       <c r="P289" s="4" t="n"/>
       <c r="Q289" s="4" t="n"/>
+      <c r="R289" s="4" t="n"/>
     </row>
     <row r="290">
       <c r="A290" s="3" t="n"/>
@@ -6257,11 +6551,12 @@
       <c r="J290" s="4" t="n"/>
       <c r="K290" s="4" t="n"/>
       <c r="L290" s="4" t="n"/>
-      <c r="M290" s="3" t="n"/>
+      <c r="M290" s="4" t="n"/>
       <c r="N290" s="4" t="n"/>
       <c r="O290" s="4" t="n"/>
       <c r="P290" s="4" t="n"/>
       <c r="Q290" s="4" t="n"/>
+      <c r="R290" s="4" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="3" t="n"/>
@@ -6276,11 +6571,12 @@
       <c r="J291" s="4" t="n"/>
       <c r="K291" s="4" t="n"/>
       <c r="L291" s="4" t="n"/>
-      <c r="M291" s="3" t="n"/>
+      <c r="M291" s="4" t="n"/>
       <c r="N291" s="4" t="n"/>
       <c r="O291" s="4" t="n"/>
       <c r="P291" s="4" t="n"/>
       <c r="Q291" s="4" t="n"/>
+      <c r="R291" s="4" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="3" t="n"/>
@@ -6295,11 +6591,12 @@
       <c r="J292" s="4" t="n"/>
       <c r="K292" s="4" t="n"/>
       <c r="L292" s="4" t="n"/>
-      <c r="M292" s="3" t="n"/>
+      <c r="M292" s="4" t="n"/>
       <c r="N292" s="4" t="n"/>
       <c r="O292" s="4" t="n"/>
       <c r="P292" s="4" t="n"/>
       <c r="Q292" s="4" t="n"/>
+      <c r="R292" s="4" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="3" t="n"/>
@@ -6314,11 +6611,12 @@
       <c r="J293" s="4" t="n"/>
       <c r="K293" s="4" t="n"/>
       <c r="L293" s="4" t="n"/>
-      <c r="M293" s="3" t="n"/>
+      <c r="M293" s="4" t="n"/>
       <c r="N293" s="4" t="n"/>
       <c r="O293" s="4" t="n"/>
       <c r="P293" s="4" t="n"/>
       <c r="Q293" s="4" t="n"/>
+      <c r="R293" s="4" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="3" t="n"/>
@@ -6333,11 +6631,12 @@
       <c r="J294" s="4" t="n"/>
       <c r="K294" s="4" t="n"/>
       <c r="L294" s="4" t="n"/>
-      <c r="M294" s="3" t="n"/>
+      <c r="M294" s="4" t="n"/>
       <c r="N294" s="4" t="n"/>
       <c r="O294" s="4" t="n"/>
       <c r="P294" s="4" t="n"/>
       <c r="Q294" s="4" t="n"/>
+      <c r="R294" s="4" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="3" t="n"/>
@@ -6352,11 +6651,12 @@
       <c r="J295" s="4" t="n"/>
       <c r="K295" s="4" t="n"/>
       <c r="L295" s="4" t="n"/>
-      <c r="M295" s="3" t="n"/>
+      <c r="M295" s="4" t="n"/>
       <c r="N295" s="4" t="n"/>
       <c r="O295" s="4" t="n"/>
       <c r="P295" s="4" t="n"/>
       <c r="Q295" s="4" t="n"/>
+      <c r="R295" s="4" t="n"/>
     </row>
     <row r="296">
       <c r="A296" s="3" t="n"/>
@@ -6371,11 +6671,12 @@
       <c r="J296" s="4" t="n"/>
       <c r="K296" s="4" t="n"/>
       <c r="L296" s="4" t="n"/>
-      <c r="M296" s="3" t="n"/>
+      <c r="M296" s="4" t="n"/>
       <c r="N296" s="4" t="n"/>
       <c r="O296" s="4" t="n"/>
       <c r="P296" s="4" t="n"/>
       <c r="Q296" s="4" t="n"/>
+      <c r="R296" s="4" t="n"/>
     </row>
     <row r="297">
       <c r="A297" s="3" t="n"/>
@@ -6390,11 +6691,12 @@
       <c r="J297" s="4" t="n"/>
       <c r="K297" s="4" t="n"/>
       <c r="L297" s="4" t="n"/>
-      <c r="M297" s="3" t="n"/>
+      <c r="M297" s="4" t="n"/>
       <c r="N297" s="4" t="n"/>
       <c r="O297" s="4" t="n"/>
       <c r="P297" s="4" t="n"/>
       <c r="Q297" s="4" t="n"/>
+      <c r="R297" s="4" t="n"/>
     </row>
     <row r="298">
       <c r="A298" s="3" t="n"/>
@@ -6409,11 +6711,12 @@
       <c r="J298" s="4" t="n"/>
       <c r="K298" s="4" t="n"/>
       <c r="L298" s="4" t="n"/>
-      <c r="M298" s="3" t="n"/>
+      <c r="M298" s="4" t="n"/>
       <c r="N298" s="4" t="n"/>
       <c r="O298" s="4" t="n"/>
       <c r="P298" s="4" t="n"/>
       <c r="Q298" s="4" t="n"/>
+      <c r="R298" s="4" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="3" t="n"/>
@@ -6428,11 +6731,12 @@
       <c r="J299" s="4" t="n"/>
       <c r="K299" s="4" t="n"/>
       <c r="L299" s="4" t="n"/>
-      <c r="M299" s="3" t="n"/>
+      <c r="M299" s="4" t="n"/>
       <c r="N299" s="4" t="n"/>
       <c r="O299" s="4" t="n"/>
       <c r="P299" s="4" t="n"/>
       <c r="Q299" s="4" t="n"/>
+      <c r="R299" s="4" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="3" t="n"/>
@@ -6447,11 +6751,12 @@
       <c r="J300" s="4" t="n"/>
       <c r="K300" s="4" t="n"/>
       <c r="L300" s="4" t="n"/>
-      <c r="M300" s="3" t="n"/>
+      <c r="M300" s="4" t="n"/>
       <c r="N300" s="4" t="n"/>
       <c r="O300" s="4" t="n"/>
       <c r="P300" s="4" t="n"/>
       <c r="Q300" s="4" t="n"/>
+      <c r="R300" s="4" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="3" t="n"/>
@@ -6466,11 +6771,12 @@
       <c r="J301" s="4" t="n"/>
       <c r="K301" s="4" t="n"/>
       <c r="L301" s="4" t="n"/>
-      <c r="M301" s="3" t="n"/>
+      <c r="M301" s="4" t="n"/>
       <c r="N301" s="4" t="n"/>
       <c r="O301" s="4" t="n"/>
       <c r="P301" s="4" t="n"/>
       <c r="Q301" s="4" t="n"/>
+      <c r="R301" s="4" t="n"/>
     </row>
     <row r="302">
       <c r="A302" s="3" t="n"/>
@@ -6485,11 +6791,12 @@
       <c r="J302" s="4" t="n"/>
       <c r="K302" s="4" t="n"/>
       <c r="L302" s="4" t="n"/>
-      <c r="M302" s="3" t="n"/>
+      <c r="M302" s="4" t="n"/>
       <c r="N302" s="4" t="n"/>
       <c r="O302" s="4" t="n"/>
       <c r="P302" s="4" t="n"/>
       <c r="Q302" s="4" t="n"/>
+      <c r="R302" s="4" t="n"/>
     </row>
     <row r="303">
       <c r="A303" s="3" t="n"/>
@@ -6504,11 +6811,12 @@
       <c r="J303" s="4" t="n"/>
       <c r="K303" s="4" t="n"/>
       <c r="L303" s="4" t="n"/>
-      <c r="M303" s="3" t="n"/>
+      <c r="M303" s="4" t="n"/>
       <c r="N303" s="4" t="n"/>
       <c r="O303" s="4" t="n"/>
       <c r="P303" s="4" t="n"/>
       <c r="Q303" s="4" t="n"/>
+      <c r="R303" s="4" t="n"/>
     </row>
     <row r="304">
       <c r="A304" s="3" t="n"/>
@@ -6523,11 +6831,12 @@
       <c r="J304" s="4" t="n"/>
       <c r="K304" s="4" t="n"/>
       <c r="L304" s="4" t="n"/>
-      <c r="M304" s="3" t="n"/>
+      <c r="M304" s="4" t="n"/>
       <c r="N304" s="4" t="n"/>
       <c r="O304" s="4" t="n"/>
       <c r="P304" s="4" t="n"/>
       <c r="Q304" s="4" t="n"/>
+      <c r="R304" s="4" t="n"/>
     </row>
     <row r="305">
       <c r="A305" s="3" t="n"/>
@@ -6542,11 +6851,12 @@
       <c r="J305" s="4" t="n"/>
       <c r="K305" s="4" t="n"/>
       <c r="L305" s="4" t="n"/>
-      <c r="M305" s="3" t="n"/>
+      <c r="M305" s="4" t="n"/>
       <c r="N305" s="4" t="n"/>
       <c r="O305" s="4" t="n"/>
       <c r="P305" s="4" t="n"/>
       <c r="Q305" s="4" t="n"/>
+      <c r="R305" s="4" t="n"/>
     </row>
     <row r="306">
       <c r="A306" s="3" t="n"/>
@@ -6561,11 +6871,12 @@
       <c r="J306" s="4" t="n"/>
       <c r="K306" s="4" t="n"/>
       <c r="L306" s="4" t="n"/>
-      <c r="M306" s="3" t="n"/>
+      <c r="M306" s="4" t="n"/>
       <c r="N306" s="4" t="n"/>
       <c r="O306" s="4" t="n"/>
       <c r="P306" s="4" t="n"/>
       <c r="Q306" s="4" t="n"/>
+      <c r="R306" s="4" t="n"/>
     </row>
     <row r="307">
       <c r="A307" s="3" t="n"/>
@@ -6580,11 +6891,12 @@
       <c r="J307" s="4" t="n"/>
       <c r="K307" s="4" t="n"/>
       <c r="L307" s="4" t="n"/>
-      <c r="M307" s="3" t="n"/>
+      <c r="M307" s="4" t="n"/>
       <c r="N307" s="4" t="n"/>
       <c r="O307" s="4" t="n"/>
       <c r="P307" s="4" t="n"/>
       <c r="Q307" s="4" t="n"/>
+      <c r="R307" s="4" t="n"/>
     </row>
     <row r="308">
       <c r="A308" s="3" t="n"/>
@@ -6599,11 +6911,12 @@
       <c r="J308" s="4" t="n"/>
       <c r="K308" s="4" t="n"/>
       <c r="L308" s="4" t="n"/>
-      <c r="M308" s="3" t="n"/>
+      <c r="M308" s="4" t="n"/>
       <c r="N308" s="4" t="n"/>
       <c r="O308" s="4" t="n"/>
       <c r="P308" s="4" t="n"/>
       <c r="Q308" s="4" t="n"/>
+      <c r="R308" s="4" t="n"/>
     </row>
     <row r="309">
       <c r="A309" s="3" t="n"/>
@@ -6618,11 +6931,12 @@
       <c r="J309" s="4" t="n"/>
       <c r="K309" s="4" t="n"/>
       <c r="L309" s="4" t="n"/>
-      <c r="M309" s="3" t="n"/>
+      <c r="M309" s="4" t="n"/>
       <c r="N309" s="4" t="n"/>
       <c r="O309" s="4" t="n"/>
       <c r="P309" s="4" t="n"/>
       <c r="Q309" s="4" t="n"/>
+      <c r="R309" s="4" t="n"/>
     </row>
     <row r="310">
       <c r="A310" s="3" t="n"/>
@@ -6637,11 +6951,12 @@
       <c r="J310" s="4" t="n"/>
       <c r="K310" s="4" t="n"/>
       <c r="L310" s="4" t="n"/>
-      <c r="M310" s="3" t="n"/>
+      <c r="M310" s="4" t="n"/>
       <c r="N310" s="4" t="n"/>
       <c r="O310" s="4" t="n"/>
       <c r="P310" s="4" t="n"/>
       <c r="Q310" s="4" t="n"/>
+      <c r="R310" s="4" t="n"/>
     </row>
     <row r="311">
       <c r="A311" s="3" t="n"/>
@@ -6656,11 +6971,12 @@
       <c r="J311" s="4" t="n"/>
       <c r="K311" s="4" t="n"/>
       <c r="L311" s="4" t="n"/>
-      <c r="M311" s="3" t="n"/>
+      <c r="M311" s="4" t="n"/>
       <c r="N311" s="4" t="n"/>
       <c r="O311" s="4" t="n"/>
       <c r="P311" s="4" t="n"/>
       <c r="Q311" s="4" t="n"/>
+      <c r="R311" s="4" t="n"/>
     </row>
     <row r="312">
       <c r="A312" s="3" t="n"/>
@@ -6675,11 +6991,12 @@
       <c r="J312" s="4" t="n"/>
       <c r="K312" s="4" t="n"/>
       <c r="L312" s="4" t="n"/>
-      <c r="M312" s="3" t="n"/>
+      <c r="M312" s="4" t="n"/>
       <c r="N312" s="4" t="n"/>
       <c r="O312" s="4" t="n"/>
       <c r="P312" s="4" t="n"/>
       <c r="Q312" s="4" t="n"/>
+      <c r="R312" s="4" t="n"/>
     </row>
     <row r="313">
       <c r="A313" s="3" t="n"/>
@@ -6694,11 +7011,12 @@
       <c r="J313" s="4" t="n"/>
       <c r="K313" s="4" t="n"/>
       <c r="L313" s="4" t="n"/>
-      <c r="M313" s="3" t="n"/>
+      <c r="M313" s="4" t="n"/>
       <c r="N313" s="4" t="n"/>
       <c r="O313" s="4" t="n"/>
       <c r="P313" s="4" t="n"/>
       <c r="Q313" s="4" t="n"/>
+      <c r="R313" s="4" t="n"/>
     </row>
     <row r="314">
       <c r="A314" s="3" t="n"/>
@@ -6713,11 +7031,12 @@
       <c r="J314" s="4" t="n"/>
       <c r="K314" s="4" t="n"/>
       <c r="L314" s="4" t="n"/>
-      <c r="M314" s="3" t="n"/>
+      <c r="M314" s="4" t="n"/>
       <c r="N314" s="4" t="n"/>
       <c r="O314" s="4" t="n"/>
       <c r="P314" s="4" t="n"/>
       <c r="Q314" s="4" t="n"/>
+      <c r="R314" s="4" t="n"/>
     </row>
     <row r="315">
       <c r="A315" s="3" t="n"/>
@@ -6732,11 +7051,12 @@
       <c r="J315" s="4" t="n"/>
       <c r="K315" s="4" t="n"/>
       <c r="L315" s="4" t="n"/>
-      <c r="M315" s="3" t="n"/>
+      <c r="M315" s="4" t="n"/>
       <c r="N315" s="4" t="n"/>
       <c r="O315" s="4" t="n"/>
       <c r="P315" s="4" t="n"/>
       <c r="Q315" s="4" t="n"/>
+      <c r="R315" s="4" t="n"/>
     </row>
     <row r="316">
       <c r="A316" s="3" t="n"/>
@@ -6751,11 +7071,12 @@
       <c r="J316" s="4" t="n"/>
       <c r="K316" s="4" t="n"/>
       <c r="L316" s="4" t="n"/>
-      <c r="M316" s="3" t="n"/>
+      <c r="M316" s="4" t="n"/>
       <c r="N316" s="4" t="n"/>
       <c r="O316" s="4" t="n"/>
       <c r="P316" s="4" t="n"/>
       <c r="Q316" s="4" t="n"/>
+      <c r="R316" s="4" t="n"/>
     </row>
     <row r="317">
       <c r="A317" s="3" t="n"/>
@@ -6770,11 +7091,12 @@
       <c r="J317" s="4" t="n"/>
       <c r="K317" s="4" t="n"/>
       <c r="L317" s="4" t="n"/>
-      <c r="M317" s="3" t="n"/>
+      <c r="M317" s="4" t="n"/>
       <c r="N317" s="4" t="n"/>
       <c r="O317" s="4" t="n"/>
       <c r="P317" s="4" t="n"/>
       <c r="Q317" s="4" t="n"/>
+      <c r="R317" s="4" t="n"/>
     </row>
     <row r="318">
       <c r="A318" s="3" t="n"/>
@@ -6789,11 +7111,12 @@
       <c r="J318" s="4" t="n"/>
       <c r="K318" s="4" t="n"/>
       <c r="L318" s="4" t="n"/>
-      <c r="M318" s="3" t="n"/>
+      <c r="M318" s="4" t="n"/>
       <c r="N318" s="4" t="n"/>
       <c r="O318" s="4" t="n"/>
       <c r="P318" s="4" t="n"/>
       <c r="Q318" s="4" t="n"/>
+      <c r="R318" s="4" t="n"/>
     </row>
     <row r="319">
       <c r="A319" s="3" t="n"/>
@@ -6808,11 +7131,12 @@
       <c r="J319" s="4" t="n"/>
       <c r="K319" s="4" t="n"/>
       <c r="L319" s="4" t="n"/>
-      <c r="M319" s="3" t="n"/>
+      <c r="M319" s="4" t="n"/>
       <c r="N319" s="4" t="n"/>
       <c r="O319" s="4" t="n"/>
       <c r="P319" s="4" t="n"/>
       <c r="Q319" s="4" t="n"/>
+      <c r="R319" s="4" t="n"/>
     </row>
     <row r="320">
       <c r="A320" s="3" t="n"/>
@@ -6827,11 +7151,12 @@
       <c r="J320" s="4" t="n"/>
       <c r="K320" s="4" t="n"/>
       <c r="L320" s="4" t="n"/>
-      <c r="M320" s="3" t="n"/>
+      <c r="M320" s="4" t="n"/>
       <c r="N320" s="4" t="n"/>
       <c r="O320" s="4" t="n"/>
       <c r="P320" s="4" t="n"/>
       <c r="Q320" s="4" t="n"/>
+      <c r="R320" s="4" t="n"/>
     </row>
     <row r="321">
       <c r="A321" s="3" t="n"/>
@@ -6846,11 +7171,12 @@
       <c r="J321" s="4" t="n"/>
       <c r="K321" s="4" t="n"/>
       <c r="L321" s="4" t="n"/>
-      <c r="M321" s="3" t="n"/>
+      <c r="M321" s="4" t="n"/>
       <c r="N321" s="4" t="n"/>
       <c r="O321" s="4" t="n"/>
       <c r="P321" s="4" t="n"/>
       <c r="Q321" s="4" t="n"/>
+      <c r="R321" s="4" t="n"/>
     </row>
     <row r="322">
       <c r="A322" s="3" t="n"/>
@@ -6865,11 +7191,12 @@
       <c r="J322" s="4" t="n"/>
       <c r="K322" s="4" t="n"/>
       <c r="L322" s="4" t="n"/>
-      <c r="M322" s="3" t="n"/>
+      <c r="M322" s="4" t="n"/>
       <c r="N322" s="4" t="n"/>
       <c r="O322" s="4" t="n"/>
       <c r="P322" s="4" t="n"/>
       <c r="Q322" s="4" t="n"/>
+      <c r="R322" s="4" t="n"/>
     </row>
     <row r="323">
       <c r="A323" s="3" t="n"/>
@@ -6884,11 +7211,12 @@
       <c r="J323" s="4" t="n"/>
       <c r="K323" s="4" t="n"/>
       <c r="L323" s="4" t="n"/>
-      <c r="M323" s="3" t="n"/>
+      <c r="M323" s="4" t="n"/>
       <c r="N323" s="4" t="n"/>
       <c r="O323" s="4" t="n"/>
       <c r="P323" s="4" t="n"/>
       <c r="Q323" s="4" t="n"/>
+      <c r="R323" s="4" t="n"/>
     </row>
     <row r="324">
       <c r="A324" s="3" t="n"/>
@@ -6903,11 +7231,12 @@
       <c r="J324" s="4" t="n"/>
       <c r="K324" s="4" t="n"/>
       <c r="L324" s="4" t="n"/>
-      <c r="M324" s="3" t="n"/>
+      <c r="M324" s="4" t="n"/>
       <c r="N324" s="4" t="n"/>
       <c r="O324" s="4" t="n"/>
       <c r="P324" s="4" t="n"/>
       <c r="Q324" s="4" t="n"/>
+      <c r="R324" s="4" t="n"/>
     </row>
     <row r="325">
       <c r="A325" s="3" t="n"/>
@@ -6922,11 +7251,12 @@
       <c r="J325" s="4" t="n"/>
       <c r="K325" s="4" t="n"/>
       <c r="L325" s="4" t="n"/>
-      <c r="M325" s="3" t="n"/>
+      <c r="M325" s="4" t="n"/>
       <c r="N325" s="4" t="n"/>
       <c r="O325" s="4" t="n"/>
       <c r="P325" s="4" t="n"/>
       <c r="Q325" s="4" t="n"/>
+      <c r="R325" s="4" t="n"/>
     </row>
     <row r="326">
       <c r="A326" s="3" t="n"/>
@@ -6941,11 +7271,12 @@
       <c r="J326" s="4" t="n"/>
       <c r="K326" s="4" t="n"/>
       <c r="L326" s="4" t="n"/>
-      <c r="M326" s="3" t="n"/>
+      <c r="M326" s="4" t="n"/>
       <c r="N326" s="4" t="n"/>
       <c r="O326" s="4" t="n"/>
       <c r="P326" s="4" t="n"/>
       <c r="Q326" s="4" t="n"/>
+      <c r="R326" s="4" t="n"/>
     </row>
     <row r="327">
       <c r="A327" s="3" t="n"/>
@@ -6960,11 +7291,12 @@
       <c r="J327" s="4" t="n"/>
       <c r="K327" s="4" t="n"/>
       <c r="L327" s="4" t="n"/>
-      <c r="M327" s="3" t="n"/>
+      <c r="M327" s="4" t="n"/>
       <c r="N327" s="4" t="n"/>
       <c r="O327" s="4" t="n"/>
       <c r="P327" s="4" t="n"/>
       <c r="Q327" s="4" t="n"/>
+      <c r="R327" s="4" t="n"/>
     </row>
     <row r="328">
       <c r="A328" s="3" t="n"/>
@@ -6979,11 +7311,12 @@
       <c r="J328" s="4" t="n"/>
       <c r="K328" s="4" t="n"/>
       <c r="L328" s="4" t="n"/>
-      <c r="M328" s="3" t="n"/>
+      <c r="M328" s="4" t="n"/>
       <c r="N328" s="4" t="n"/>
       <c r="O328" s="4" t="n"/>
       <c r="P328" s="4" t="n"/>
       <c r="Q328" s="4" t="n"/>
+      <c r="R328" s="4" t="n"/>
     </row>
     <row r="329">
       <c r="A329" s="3" t="n"/>
@@ -6998,11 +7331,12 @@
       <c r="J329" s="4" t="n"/>
       <c r="K329" s="4" t="n"/>
       <c r="L329" s="4" t="n"/>
-      <c r="M329" s="3" t="n"/>
+      <c r="M329" s="4" t="n"/>
       <c r="N329" s="4" t="n"/>
       <c r="O329" s="4" t="n"/>
       <c r="P329" s="4" t="n"/>
       <c r="Q329" s="4" t="n"/>
+      <c r="R329" s="4" t="n"/>
     </row>
     <row r="330">
       <c r="A330" s="3" t="n"/>
@@ -7017,11 +7351,12 @@
       <c r="J330" s="4" t="n"/>
       <c r="K330" s="4" t="n"/>
       <c r="L330" s="4" t="n"/>
-      <c r="M330" s="3" t="n"/>
+      <c r="M330" s="4" t="n"/>
       <c r="N330" s="4" t="n"/>
       <c r="O330" s="4" t="n"/>
       <c r="P330" s="4" t="n"/>
       <c r="Q330" s="4" t="n"/>
+      <c r="R330" s="4" t="n"/>
     </row>
     <row r="331">
       <c r="A331" s="3" t="n"/>
@@ -7036,11 +7371,12 @@
       <c r="J331" s="4" t="n"/>
       <c r="K331" s="4" t="n"/>
       <c r="L331" s="4" t="n"/>
-      <c r="M331" s="3" t="n"/>
+      <c r="M331" s="4" t="n"/>
       <c r="N331" s="4" t="n"/>
       <c r="O331" s="4" t="n"/>
       <c r="P331" s="4" t="n"/>
       <c r="Q331" s="4" t="n"/>
+      <c r="R331" s="4" t="n"/>
     </row>
     <row r="332">
       <c r="A332" s="3" t="n"/>
@@ -7055,11 +7391,12 @@
       <c r="J332" s="4" t="n"/>
       <c r="K332" s="4" t="n"/>
       <c r="L332" s="4" t="n"/>
-      <c r="M332" s="3" t="n"/>
+      <c r="M332" s="4" t="n"/>
       <c r="N332" s="4" t="n"/>
       <c r="O332" s="4" t="n"/>
       <c r="P332" s="4" t="n"/>
       <c r="Q332" s="4" t="n"/>
+      <c r="R332" s="4" t="n"/>
     </row>
     <row r="333">
       <c r="A333" s="3" t="n"/>
@@ -7074,11 +7411,12 @@
       <c r="J333" s="4" t="n"/>
       <c r="K333" s="4" t="n"/>
       <c r="L333" s="4" t="n"/>
-      <c r="M333" s="3" t="n"/>
+      <c r="M333" s="4" t="n"/>
       <c r="N333" s="4" t="n"/>
       <c r="O333" s="4" t="n"/>
       <c r="P333" s="4" t="n"/>
       <c r="Q333" s="4" t="n"/>
+      <c r="R333" s="4" t="n"/>
     </row>
     <row r="334">
       <c r="A334" s="3" t="n"/>
@@ -7093,11 +7431,12 @@
       <c r="J334" s="4" t="n"/>
       <c r="K334" s="4" t="n"/>
       <c r="L334" s="4" t="n"/>
-      <c r="M334" s="3" t="n"/>
+      <c r="M334" s="4" t="n"/>
       <c r="N334" s="4" t="n"/>
       <c r="O334" s="4" t="n"/>
       <c r="P334" s="4" t="n"/>
       <c r="Q334" s="4" t="n"/>
+      <c r="R334" s="4" t="n"/>
     </row>
     <row r="335">
       <c r="A335" s="3" t="n"/>
@@ -7112,11 +7451,12 @@
       <c r="J335" s="4" t="n"/>
       <c r="K335" s="4" t="n"/>
       <c r="L335" s="4" t="n"/>
-      <c r="M335" s="3" t="n"/>
+      <c r="M335" s="4" t="n"/>
       <c r="N335" s="4" t="n"/>
       <c r="O335" s="4" t="n"/>
       <c r="P335" s="4" t="n"/>
       <c r="Q335" s="4" t="n"/>
+      <c r="R335" s="4" t="n"/>
     </row>
     <row r="336">
       <c r="A336" s="3" t="n"/>
@@ -7131,11 +7471,12 @@
       <c r="J336" s="4" t="n"/>
       <c r="K336" s="4" t="n"/>
       <c r="L336" s="4" t="n"/>
-      <c r="M336" s="3" t="n"/>
+      <c r="M336" s="4" t="n"/>
       <c r="N336" s="4" t="n"/>
       <c r="O336" s="4" t="n"/>
       <c r="P336" s="4" t="n"/>
       <c r="Q336" s="4" t="n"/>
+      <c r="R336" s="4" t="n"/>
     </row>
     <row r="337">
       <c r="A337" s="3" t="n"/>
@@ -7150,11 +7491,12 @@
       <c r="J337" s="4" t="n"/>
       <c r="K337" s="4" t="n"/>
       <c r="L337" s="4" t="n"/>
-      <c r="M337" s="3" t="n"/>
+      <c r="M337" s="4" t="n"/>
       <c r="N337" s="4" t="n"/>
       <c r="O337" s="4" t="n"/>
       <c r="P337" s="4" t="n"/>
       <c r="Q337" s="4" t="n"/>
+      <c r="R337" s="4" t="n"/>
     </row>
     <row r="338">
       <c r="A338" s="3" t="n"/>
@@ -7169,11 +7511,12 @@
       <c r="J338" s="4" t="n"/>
       <c r="K338" s="4" t="n"/>
       <c r="L338" s="4" t="n"/>
-      <c r="M338" s="3" t="n"/>
+      <c r="M338" s="4" t="n"/>
       <c r="N338" s="4" t="n"/>
       <c r="O338" s="4" t="n"/>
       <c r="P338" s="4" t="n"/>
       <c r="Q338" s="4" t="n"/>
+      <c r="R338" s="4" t="n"/>
     </row>
     <row r="339">
       <c r="A339" s="3" t="n"/>
@@ -7188,11 +7531,12 @@
       <c r="J339" s="4" t="n"/>
       <c r="K339" s="4" t="n"/>
       <c r="L339" s="4" t="n"/>
-      <c r="M339" s="3" t="n"/>
+      <c r="M339" s="4" t="n"/>
       <c r="N339" s="4" t="n"/>
       <c r="O339" s="4" t="n"/>
       <c r="P339" s="4" t="n"/>
       <c r="Q339" s="4" t="n"/>
+      <c r="R339" s="4" t="n"/>
     </row>
     <row r="340">
       <c r="A340" s="3" t="n"/>
@@ -7207,11 +7551,12 @@
       <c r="J340" s="4" t="n"/>
       <c r="K340" s="4" t="n"/>
       <c r="L340" s="4" t="n"/>
-      <c r="M340" s="3" t="n"/>
+      <c r="M340" s="4" t="n"/>
       <c r="N340" s="4" t="n"/>
       <c r="O340" s="4" t="n"/>
       <c r="P340" s="4" t="n"/>
       <c r="Q340" s="4" t="n"/>
+      <c r="R340" s="4" t="n"/>
     </row>
     <row r="341">
       <c r="A341" s="3" t="n"/>
@@ -7226,11 +7571,12 @@
       <c r="J341" s="4" t="n"/>
       <c r="K341" s="4" t="n"/>
       <c r="L341" s="4" t="n"/>
-      <c r="M341" s="3" t="n"/>
+      <c r="M341" s="4" t="n"/>
       <c r="N341" s="4" t="n"/>
       <c r="O341" s="4" t="n"/>
       <c r="P341" s="4" t="n"/>
       <c r="Q341" s="4" t="n"/>
+      <c r="R341" s="4" t="n"/>
     </row>
     <row r="342">
       <c r="A342" s="3" t="n"/>
@@ -7245,11 +7591,12 @@
       <c r="J342" s="4" t="n"/>
       <c r="K342" s="4" t="n"/>
       <c r="L342" s="4" t="n"/>
-      <c r="M342" s="3" t="n"/>
+      <c r="M342" s="4" t="n"/>
       <c r="N342" s="4" t="n"/>
       <c r="O342" s="4" t="n"/>
       <c r="P342" s="4" t="n"/>
       <c r="Q342" s="4" t="n"/>
+      <c r="R342" s="4" t="n"/>
     </row>
     <row r="343">
       <c r="A343" s="3" t="n"/>
@@ -7264,11 +7611,12 @@
       <c r="J343" s="4" t="n"/>
       <c r="K343" s="4" t="n"/>
       <c r="L343" s="4" t="n"/>
-      <c r="M343" s="3" t="n"/>
+      <c r="M343" s="4" t="n"/>
       <c r="N343" s="4" t="n"/>
       <c r="O343" s="4" t="n"/>
       <c r="P343" s="4" t="n"/>
       <c r="Q343" s="4" t="n"/>
+      <c r="R343" s="4" t="n"/>
     </row>
     <row r="344">
       <c r="A344" s="3" t="n"/>
@@ -7283,11 +7631,12 @@
       <c r="J344" s="4" t="n"/>
       <c r="K344" s="4" t="n"/>
       <c r="L344" s="4" t="n"/>
-      <c r="M344" s="3" t="n"/>
+      <c r="M344" s="4" t="n"/>
       <c r="N344" s="4" t="n"/>
       <c r="O344" s="4" t="n"/>
       <c r="P344" s="4" t="n"/>
       <c r="Q344" s="4" t="n"/>
+      <c r="R344" s="4" t="n"/>
     </row>
     <row r="345">
       <c r="A345" s="3" t="n"/>
@@ -7302,11 +7651,12 @@
       <c r="J345" s="4" t="n"/>
       <c r="K345" s="4" t="n"/>
       <c r="L345" s="4" t="n"/>
-      <c r="M345" s="3" t="n"/>
+      <c r="M345" s="4" t="n"/>
       <c r="N345" s="4" t="n"/>
       <c r="O345" s="4" t="n"/>
       <c r="P345" s="4" t="n"/>
       <c r="Q345" s="4" t="n"/>
+      <c r="R345" s="4" t="n"/>
     </row>
     <row r="346">
       <c r="A346" s="3" t="n"/>
@@ -7321,11 +7671,12 @@
       <c r="J346" s="4" t="n"/>
       <c r="K346" s="4" t="n"/>
       <c r="L346" s="4" t="n"/>
-      <c r="M346" s="3" t="n"/>
+      <c r="M346" s="4" t="n"/>
       <c r="N346" s="4" t="n"/>
       <c r="O346" s="4" t="n"/>
       <c r="P346" s="4" t="n"/>
       <c r="Q346" s="4" t="n"/>
+      <c r="R346" s="4" t="n"/>
     </row>
     <row r="347">
       <c r="A347" s="3" t="n"/>
@@ -7340,11 +7691,12 @@
       <c r="J347" s="4" t="n"/>
       <c r="K347" s="4" t="n"/>
       <c r="L347" s="4" t="n"/>
-      <c r="M347" s="3" t="n"/>
+      <c r="M347" s="4" t="n"/>
       <c r="N347" s="4" t="n"/>
       <c r="O347" s="4" t="n"/>
       <c r="P347" s="4" t="n"/>
       <c r="Q347" s="4" t="n"/>
+      <c r="R347" s="4" t="n"/>
     </row>
     <row r="348">
       <c r="A348" s="3" t="n"/>
@@ -7359,11 +7711,12 @@
       <c r="J348" s="4" t="n"/>
       <c r="K348" s="4" t="n"/>
       <c r="L348" s="4" t="n"/>
-      <c r="M348" s="3" t="n"/>
+      <c r="M348" s="4" t="n"/>
       <c r="N348" s="4" t="n"/>
       <c r="O348" s="4" t="n"/>
       <c r="P348" s="4" t="n"/>
       <c r="Q348" s="4" t="n"/>
+      <c r="R348" s="4" t="n"/>
     </row>
     <row r="349">
       <c r="A349" s="3" t="n"/>
@@ -7378,11 +7731,12 @@
       <c r="J349" s="4" t="n"/>
       <c r="K349" s="4" t="n"/>
       <c r="L349" s="4" t="n"/>
-      <c r="M349" s="3" t="n"/>
+      <c r="M349" s="4" t="n"/>
       <c r="N349" s="4" t="n"/>
       <c r="O349" s="4" t="n"/>
       <c r="P349" s="4" t="n"/>
       <c r="Q349" s="4" t="n"/>
+      <c r="R349" s="4" t="n"/>
     </row>
     <row r="350">
       <c r="A350" s="3" t="n"/>
@@ -7397,11 +7751,12 @@
       <c r="J350" s="4" t="n"/>
       <c r="K350" s="4" t="n"/>
       <c r="L350" s="4" t="n"/>
-      <c r="M350" s="3" t="n"/>
+      <c r="M350" s="4" t="n"/>
       <c r="N350" s="4" t="n"/>
       <c r="O350" s="4" t="n"/>
       <c r="P350" s="4" t="n"/>
       <c r="Q350" s="4" t="n"/>
+      <c r="R350" s="4" t="n"/>
     </row>
     <row r="351">
       <c r="A351" s="3" t="n"/>
@@ -7416,11 +7771,12 @@
       <c r="J351" s="4" t="n"/>
       <c r="K351" s="4" t="n"/>
       <c r="L351" s="4" t="n"/>
-      <c r="M351" s="3" t="n"/>
+      <c r="M351" s="4" t="n"/>
       <c r="N351" s="4" t="n"/>
       <c r="O351" s="4" t="n"/>
       <c r="P351" s="4" t="n"/>
       <c r="Q351" s="4" t="n"/>
+      <c r="R351" s="4" t="n"/>
     </row>
     <row r="352">
       <c r="A352" s="3" t="n"/>
@@ -7435,11 +7791,12 @@
       <c r="J352" s="4" t="n"/>
       <c r="K352" s="4" t="n"/>
       <c r="L352" s="4" t="n"/>
-      <c r="M352" s="3" t="n"/>
+      <c r="M352" s="4" t="n"/>
       <c r="N352" s="4" t="n"/>
       <c r="O352" s="4" t="n"/>
       <c r="P352" s="4" t="n"/>
       <c r="Q352" s="4" t="n"/>
+      <c r="R352" s="4" t="n"/>
     </row>
     <row r="353">
       <c r="A353" s="3" t="n"/>
@@ -7454,11 +7811,12 @@
       <c r="J353" s="4" t="n"/>
       <c r="K353" s="4" t="n"/>
       <c r="L353" s="4" t="n"/>
-      <c r="M353" s="3" t="n"/>
+      <c r="M353" s="4" t="n"/>
       <c r="N353" s="4" t="n"/>
       <c r="O353" s="4" t="n"/>
       <c r="P353" s="4" t="n"/>
       <c r="Q353" s="4" t="n"/>
+      <c r="R353" s="4" t="n"/>
     </row>
     <row r="354">
       <c r="A354" s="3" t="n"/>
@@ -7473,11 +7831,12 @@
       <c r="J354" s="4" t="n"/>
       <c r="K354" s="4" t="n"/>
       <c r="L354" s="4" t="n"/>
-      <c r="M354" s="3" t="n"/>
+      <c r="M354" s="4" t="n"/>
       <c r="N354" s="4" t="n"/>
       <c r="O354" s="4" t="n"/>
       <c r="P354" s="4" t="n"/>
       <c r="Q354" s="4" t="n"/>
+      <c r="R354" s="4" t="n"/>
     </row>
     <row r="355">
       <c r="A355" s="3" t="n"/>
@@ -7492,11 +7851,12 @@
       <c r="J355" s="4" t="n"/>
       <c r="K355" s="4" t="n"/>
       <c r="L355" s="4" t="n"/>
-      <c r="M355" s="3" t="n"/>
+      <c r="M355" s="4" t="n"/>
       <c r="N355" s="4" t="n"/>
       <c r="O355" s="4" t="n"/>
       <c r="P355" s="4" t="n"/>
       <c r="Q355" s="4" t="n"/>
+      <c r="R355" s="4" t="n"/>
     </row>
     <row r="356">
       <c r="A356" s="3" t="n"/>
@@ -7511,11 +7871,12 @@
       <c r="J356" s="4" t="n"/>
       <c r="K356" s="4" t="n"/>
       <c r="L356" s="4" t="n"/>
-      <c r="M356" s="3" t="n"/>
+      <c r="M356" s="4" t="n"/>
       <c r="N356" s="4" t="n"/>
       <c r="O356" s="4" t="n"/>
       <c r="P356" s="4" t="n"/>
       <c r="Q356" s="4" t="n"/>
+      <c r="R356" s="4" t="n"/>
     </row>
     <row r="357">
       <c r="A357" s="3" t="n"/>
@@ -7530,11 +7891,12 @@
       <c r="J357" s="4" t="n"/>
       <c r="K357" s="4" t="n"/>
       <c r="L357" s="4" t="n"/>
-      <c r="M357" s="3" t="n"/>
+      <c r="M357" s="4" t="n"/>
       <c r="N357" s="4" t="n"/>
       <c r="O357" s="4" t="n"/>
       <c r="P357" s="4" t="n"/>
       <c r="Q357" s="4" t="n"/>
+      <c r="R357" s="4" t="n"/>
     </row>
     <row r="358">
       <c r="A358" s="3" t="n"/>
@@ -7549,11 +7911,12 @@
       <c r="J358" s="4" t="n"/>
       <c r="K358" s="4" t="n"/>
       <c r="L358" s="4" t="n"/>
-      <c r="M358" s="3" t="n"/>
+      <c r="M358" s="4" t="n"/>
       <c r="N358" s="4" t="n"/>
       <c r="O358" s="4" t="n"/>
       <c r="P358" s="4" t="n"/>
       <c r="Q358" s="4" t="n"/>
+      <c r="R358" s="4" t="n"/>
     </row>
     <row r="359">
       <c r="A359" s="3" t="n"/>
@@ -7568,11 +7931,12 @@
       <c r="J359" s="4" t="n"/>
       <c r="K359" s="4" t="n"/>
       <c r="L359" s="4" t="n"/>
-      <c r="M359" s="3" t="n"/>
+      <c r="M359" s="4" t="n"/>
       <c r="N359" s="4" t="n"/>
       <c r="O359" s="4" t="n"/>
       <c r="P359" s="4" t="n"/>
       <c r="Q359" s="4" t="n"/>
+      <c r="R359" s="4" t="n"/>
     </row>
     <row r="360">
       <c r="A360" s="3" t="n"/>
@@ -7587,11 +7951,12 @@
       <c r="J360" s="4" t="n"/>
       <c r="K360" s="4" t="n"/>
       <c r="L360" s="4" t="n"/>
-      <c r="M360" s="3" t="n"/>
+      <c r="M360" s="4" t="n"/>
       <c r="N360" s="4" t="n"/>
       <c r="O360" s="4" t="n"/>
       <c r="P360" s="4" t="n"/>
       <c r="Q360" s="4" t="n"/>
+      <c r="R360" s="4" t="n"/>
     </row>
     <row r="361">
       <c r="A361" s="3" t="n"/>
@@ -7606,11 +7971,12 @@
       <c r="J361" s="4" t="n"/>
       <c r="K361" s="4" t="n"/>
       <c r="L361" s="4" t="n"/>
-      <c r="M361" s="3" t="n"/>
+      <c r="M361" s="4" t="n"/>
       <c r="N361" s="4" t="n"/>
       <c r="O361" s="4" t="n"/>
       <c r="P361" s="4" t="n"/>
       <c r="Q361" s="4" t="n"/>
+      <c r="R361" s="4" t="n"/>
     </row>
     <row r="362">
       <c r="A362" s="3" t="n"/>
@@ -7625,11 +7991,12 @@
       <c r="J362" s="4" t="n"/>
       <c r="K362" s="4" t="n"/>
       <c r="L362" s="4" t="n"/>
-      <c r="M362" s="3" t="n"/>
+      <c r="M362" s="4" t="n"/>
       <c r="N362" s="4" t="n"/>
       <c r="O362" s="4" t="n"/>
       <c r="P362" s="4" t="n"/>
       <c r="Q362" s="4" t="n"/>
+      <c r="R362" s="4" t="n"/>
     </row>
     <row r="363">
       <c r="A363" s="3" t="n"/>
@@ -7644,11 +8011,12 @@
       <c r="J363" s="4" t="n"/>
       <c r="K363" s="4" t="n"/>
       <c r="L363" s="4" t="n"/>
-      <c r="M363" s="3" t="n"/>
+      <c r="M363" s="4" t="n"/>
       <c r="N363" s="4" t="n"/>
       <c r="O363" s="4" t="n"/>
       <c r="P363" s="4" t="n"/>
       <c r="Q363" s="4" t="n"/>
+      <c r="R363" s="4" t="n"/>
     </row>
     <row r="364">
       <c r="A364" s="3" t="n"/>
@@ -7663,11 +8031,12 @@
       <c r="J364" s="4" t="n"/>
       <c r="K364" s="4" t="n"/>
       <c r="L364" s="4" t="n"/>
-      <c r="M364" s="3" t="n"/>
+      <c r="M364" s="4" t="n"/>
       <c r="N364" s="4" t="n"/>
       <c r="O364" s="4" t="n"/>
       <c r="P364" s="4" t="n"/>
       <c r="Q364" s="4" t="n"/>
+      <c r="R364" s="4" t="n"/>
     </row>
     <row r="365">
       <c r="A365" s="3" t="n"/>
@@ -7682,11 +8051,12 @@
       <c r="J365" s="4" t="n"/>
       <c r="K365" s="4" t="n"/>
       <c r="L365" s="4" t="n"/>
-      <c r="M365" s="3" t="n"/>
+      <c r="M365" s="4" t="n"/>
       <c r="N365" s="4" t="n"/>
       <c r="O365" s="4" t="n"/>
       <c r="P365" s="4" t="n"/>
       <c r="Q365" s="4" t="n"/>
+      <c r="R365" s="4" t="n"/>
     </row>
     <row r="366">
       <c r="A366" s="3" t="n"/>
@@ -7701,11 +8071,12 @@
       <c r="J366" s="4" t="n"/>
       <c r="K366" s="4" t="n"/>
       <c r="L366" s="4" t="n"/>
-      <c r="M366" s="3" t="n"/>
+      <c r="M366" s="4" t="n"/>
       <c r="N366" s="4" t="n"/>
       <c r="O366" s="4" t="n"/>
       <c r="P366" s="4" t="n"/>
       <c r="Q366" s="4" t="n"/>
+      <c r="R366" s="4" t="n"/>
     </row>
     <row r="367">
       <c r="A367" s="3" t="n"/>
@@ -7720,11 +8091,12 @@
       <c r="J367" s="4" t="n"/>
       <c r="K367" s="4" t="n"/>
       <c r="L367" s="4" t="n"/>
-      <c r="M367" s="3" t="n"/>
+      <c r="M367" s="4" t="n"/>
       <c r="N367" s="4" t="n"/>
       <c r="O367" s="4" t="n"/>
       <c r="P367" s="4" t="n"/>
       <c r="Q367" s="4" t="n"/>
+      <c r="R367" s="4" t="n"/>
     </row>
     <row r="368">
       <c r="A368" s="3" t="n"/>
@@ -7739,11 +8111,12 @@
       <c r="J368" s="4" t="n"/>
       <c r="K368" s="4" t="n"/>
       <c r="L368" s="4" t="n"/>
-      <c r="M368" s="3" t="n"/>
+      <c r="M368" s="4" t="n"/>
       <c r="N368" s="4" t="n"/>
       <c r="O368" s="4" t="n"/>
       <c r="P368" s="4" t="n"/>
       <c r="Q368" s="4" t="n"/>
+      <c r="R368" s="4" t="n"/>
     </row>
     <row r="369">
       <c r="A369" s="3" t="n"/>
@@ -7758,11 +8131,12 @@
       <c r="J369" s="4" t="n"/>
       <c r="K369" s="4" t="n"/>
       <c r="L369" s="4" t="n"/>
-      <c r="M369" s="3" t="n"/>
+      <c r="M369" s="4" t="n"/>
       <c r="N369" s="4" t="n"/>
       <c r="O369" s="4" t="n"/>
       <c r="P369" s="4" t="n"/>
       <c r="Q369" s="4" t="n"/>
+      <c r="R369" s="4" t="n"/>
     </row>
     <row r="370">
       <c r="A370" s="3" t="n"/>
@@ -7777,11 +8151,12 @@
       <c r="J370" s="4" t="n"/>
       <c r="K370" s="4" t="n"/>
       <c r="L370" s="4" t="n"/>
-      <c r="M370" s="3" t="n"/>
+      <c r="M370" s="4" t="n"/>
       <c r="N370" s="4" t="n"/>
       <c r="O370" s="4" t="n"/>
       <c r="P370" s="4" t="n"/>
       <c r="Q370" s="4" t="n"/>
+      <c r="R370" s="4" t="n"/>
     </row>
     <row r="371">
       <c r="A371" s="3" t="n"/>
@@ -7796,11 +8171,12 @@
       <c r="J371" s="4" t="n"/>
       <c r="K371" s="4" t="n"/>
       <c r="L371" s="4" t="n"/>
-      <c r="M371" s="3" t="n"/>
+      <c r="M371" s="4" t="n"/>
       <c r="N371" s="4" t="n"/>
       <c r="O371" s="4" t="n"/>
       <c r="P371" s="4" t="n"/>
       <c r="Q371" s="4" t="n"/>
+      <c r="R371" s="4" t="n"/>
     </row>
     <row r="372">
       <c r="A372" s="3" t="n"/>
@@ -7815,11 +8191,12 @@
       <c r="J372" s="4" t="n"/>
       <c r="K372" s="4" t="n"/>
       <c r="L372" s="4" t="n"/>
-      <c r="M372" s="3" t="n"/>
+      <c r="M372" s="4" t="n"/>
       <c r="N372" s="4" t="n"/>
       <c r="O372" s="4" t="n"/>
       <c r="P372" s="4" t="n"/>
       <c r="Q372" s="4" t="n"/>
+      <c r="R372" s="4" t="n"/>
     </row>
     <row r="373">
       <c r="A373" s="3" t="n"/>
@@ -7834,11 +8211,12 @@
       <c r="J373" s="4" t="n"/>
       <c r="K373" s="4" t="n"/>
       <c r="L373" s="4" t="n"/>
-      <c r="M373" s="3" t="n"/>
+      <c r="M373" s="4" t="n"/>
       <c r="N373" s="4" t="n"/>
       <c r="O373" s="4" t="n"/>
       <c r="P373" s="4" t="n"/>
       <c r="Q373" s="4" t="n"/>
+      <c r="R373" s="4" t="n"/>
     </row>
     <row r="374">
       <c r="A374" s="3" t="n"/>
@@ -7853,11 +8231,12 @@
       <c r="J374" s="4" t="n"/>
       <c r="K374" s="4" t="n"/>
       <c r="L374" s="4" t="n"/>
-      <c r="M374" s="3" t="n"/>
+      <c r="M374" s="4" t="n"/>
       <c r="N374" s="4" t="n"/>
       <c r="O374" s="4" t="n"/>
       <c r="P374" s="4" t="n"/>
       <c r="Q374" s="4" t="n"/>
+      <c r="R374" s="4" t="n"/>
     </row>
     <row r="375">
       <c r="A375" s="3" t="n"/>
@@ -7872,11 +8251,12 @@
       <c r="J375" s="4" t="n"/>
       <c r="K375" s="4" t="n"/>
       <c r="L375" s="4" t="n"/>
-      <c r="M375" s="3" t="n"/>
+      <c r="M375" s="4" t="n"/>
       <c r="N375" s="4" t="n"/>
       <c r="O375" s="4" t="n"/>
       <c r="P375" s="4" t="n"/>
       <c r="Q375" s="4" t="n"/>
+      <c r="R375" s="4" t="n"/>
     </row>
     <row r="376">
       <c r="A376" s="3" t="n"/>
@@ -7891,11 +8271,12 @@
       <c r="J376" s="4" t="n"/>
       <c r="K376" s="4" t="n"/>
       <c r="L376" s="4" t="n"/>
-      <c r="M376" s="3" t="n"/>
+      <c r="M376" s="4" t="n"/>
       <c r="N376" s="4" t="n"/>
       <c r="O376" s="4" t="n"/>
       <c r="P376" s="4" t="n"/>
       <c r="Q376" s="4" t="n"/>
+      <c r="R376" s="4" t="n"/>
     </row>
     <row r="377">
       <c r="A377" s="3" t="n"/>
@@ -7910,11 +8291,12 @@
       <c r="J377" s="4" t="n"/>
       <c r="K377" s="4" t="n"/>
       <c r="L377" s="4" t="n"/>
-      <c r="M377" s="3" t="n"/>
+      <c r="M377" s="4" t="n"/>
       <c r="N377" s="4" t="n"/>
       <c r="O377" s="4" t="n"/>
       <c r="P377" s="4" t="n"/>
       <c r="Q377" s="4" t="n"/>
+      <c r="R377" s="4" t="n"/>
     </row>
     <row r="378">
       <c r="A378" s="3" t="n"/>
@@ -7929,11 +8311,12 @@
       <c r="J378" s="4" t="n"/>
       <c r="K378" s="4" t="n"/>
       <c r="L378" s="4" t="n"/>
-      <c r="M378" s="3" t="n"/>
+      <c r="M378" s="4" t="n"/>
       <c r="N378" s="4" t="n"/>
       <c r="O378" s="4" t="n"/>
       <c r="P378" s="4" t="n"/>
       <c r="Q378" s="4" t="n"/>
+      <c r="R378" s="4" t="n"/>
     </row>
     <row r="379">
       <c r="A379" s="3" t="n"/>
@@ -7948,11 +8331,12 @@
       <c r="J379" s="4" t="n"/>
       <c r="K379" s="4" t="n"/>
       <c r="L379" s="4" t="n"/>
-      <c r="M379" s="3" t="n"/>
+      <c r="M379" s="4" t="n"/>
       <c r="N379" s="4" t="n"/>
       <c r="O379" s="4" t="n"/>
       <c r="P379" s="4" t="n"/>
       <c r="Q379" s="4" t="n"/>
+      <c r="R379" s="4" t="n"/>
     </row>
     <row r="380">
       <c r="A380" s="3" t="n"/>
@@ -7967,11 +8351,12 @@
       <c r="J380" s="4" t="n"/>
       <c r="K380" s="4" t="n"/>
       <c r="L380" s="4" t="n"/>
-      <c r="M380" s="3" t="n"/>
+      <c r="M380" s="4" t="n"/>
       <c r="N380" s="4" t="n"/>
       <c r="O380" s="4" t="n"/>
       <c r="P380" s="4" t="n"/>
       <c r="Q380" s="4" t="n"/>
+      <c r="R380" s="4" t="n"/>
     </row>
     <row r="381">
       <c r="A381" s="3" t="n"/>
@@ -7986,11 +8371,12 @@
       <c r="J381" s="4" t="n"/>
       <c r="K381" s="4" t="n"/>
       <c r="L381" s="4" t="n"/>
-      <c r="M381" s="3" t="n"/>
+      <c r="M381" s="4" t="n"/>
       <c r="N381" s="4" t="n"/>
       <c r="O381" s="4" t="n"/>
       <c r="P381" s="4" t="n"/>
       <c r="Q381" s="4" t="n"/>
+      <c r="R381" s="4" t="n"/>
     </row>
     <row r="382">
       <c r="A382" s="3" t="n"/>
@@ -8005,11 +8391,12 @@
       <c r="J382" s="4" t="n"/>
       <c r="K382" s="4" t="n"/>
       <c r="L382" s="4" t="n"/>
-      <c r="M382" s="3" t="n"/>
+      <c r="M382" s="4" t="n"/>
       <c r="N382" s="4" t="n"/>
       <c r="O382" s="4" t="n"/>
       <c r="P382" s="4" t="n"/>
       <c r="Q382" s="4" t="n"/>
+      <c r="R382" s="4" t="n"/>
     </row>
     <row r="383">
       <c r="A383" s="3" t="n"/>
@@ -8024,11 +8411,12 @@
       <c r="J383" s="4" t="n"/>
       <c r="K383" s="4" t="n"/>
       <c r="L383" s="4" t="n"/>
-      <c r="M383" s="3" t="n"/>
+      <c r="M383" s="4" t="n"/>
       <c r="N383" s="4" t="n"/>
       <c r="O383" s="4" t="n"/>
       <c r="P383" s="4" t="n"/>
       <c r="Q383" s="4" t="n"/>
+      <c r="R383" s="4" t="n"/>
     </row>
     <row r="384">
       <c r="A384" s="3" t="n"/>
@@ -8043,11 +8431,12 @@
       <c r="J384" s="4" t="n"/>
       <c r="K384" s="4" t="n"/>
       <c r="L384" s="4" t="n"/>
-      <c r="M384" s="3" t="n"/>
+      <c r="M384" s="4" t="n"/>
       <c r="N384" s="4" t="n"/>
       <c r="O384" s="4" t="n"/>
       <c r="P384" s="4" t="n"/>
       <c r="Q384" s="4" t="n"/>
+      <c r="R384" s="4" t="n"/>
     </row>
     <row r="385">
       <c r="A385" s="3" t="n"/>
@@ -8062,11 +8451,12 @@
       <c r="J385" s="4" t="n"/>
       <c r="K385" s="4" t="n"/>
       <c r="L385" s="4" t="n"/>
-      <c r="M385" s="3" t="n"/>
+      <c r="M385" s="4" t="n"/>
       <c r="N385" s="4" t="n"/>
       <c r="O385" s="4" t="n"/>
       <c r="P385" s="4" t="n"/>
       <c r="Q385" s="4" t="n"/>
+      <c r="R385" s="4" t="n"/>
     </row>
     <row r="386">
       <c r="A386" s="3" t="n"/>
@@ -8081,11 +8471,12 @@
       <c r="J386" s="4" t="n"/>
       <c r="K386" s="4" t="n"/>
       <c r="L386" s="4" t="n"/>
-      <c r="M386" s="3" t="n"/>
+      <c r="M386" s="4" t="n"/>
       <c r="N386" s="4" t="n"/>
       <c r="O386" s="4" t="n"/>
       <c r="P386" s="4" t="n"/>
       <c r="Q386" s="4" t="n"/>
+      <c r="R386" s="4" t="n"/>
     </row>
     <row r="387">
       <c r="A387" s="3" t="n"/>
@@ -8100,11 +8491,12 @@
       <c r="J387" s="4" t="n"/>
       <c r="K387" s="4" t="n"/>
       <c r="L387" s="4" t="n"/>
-      <c r="M387" s="3" t="n"/>
+      <c r="M387" s="4" t="n"/>
       <c r="N387" s="4" t="n"/>
       <c r="O387" s="4" t="n"/>
       <c r="P387" s="4" t="n"/>
       <c r="Q387" s="4" t="n"/>
+      <c r="R387" s="4" t="n"/>
     </row>
     <row r="388">
       <c r="A388" s="3" t="n"/>
@@ -8119,11 +8511,12 @@
       <c r="J388" s="4" t="n"/>
       <c r="K388" s="4" t="n"/>
       <c r="L388" s="4" t="n"/>
-      <c r="M388" s="3" t="n"/>
+      <c r="M388" s="4" t="n"/>
       <c r="N388" s="4" t="n"/>
       <c r="O388" s="4" t="n"/>
       <c r="P388" s="4" t="n"/>
       <c r="Q388" s="4" t="n"/>
+      <c r="R388" s="4" t="n"/>
     </row>
     <row r="389">
       <c r="A389" s="3" t="n"/>
@@ -8138,11 +8531,12 @@
       <c r="J389" s="4" t="n"/>
       <c r="K389" s="4" t="n"/>
       <c r="L389" s="4" t="n"/>
-      <c r="M389" s="3" t="n"/>
+      <c r="M389" s="4" t="n"/>
       <c r="N389" s="4" t="n"/>
       <c r="O389" s="4" t="n"/>
       <c r="P389" s="4" t="n"/>
       <c r="Q389" s="4" t="n"/>
+      <c r="R389" s="4" t="n"/>
     </row>
     <row r="390">
       <c r="A390" s="3" t="n"/>
@@ -8157,11 +8551,12 @@
       <c r="J390" s="4" t="n"/>
       <c r="K390" s="4" t="n"/>
       <c r="L390" s="4" t="n"/>
-      <c r="M390" s="3" t="n"/>
+      <c r="M390" s="4" t="n"/>
       <c r="N390" s="4" t="n"/>
       <c r="O390" s="4" t="n"/>
       <c r="P390" s="4" t="n"/>
       <c r="Q390" s="4" t="n"/>
+      <c r="R390" s="4" t="n"/>
     </row>
     <row r="391">
       <c r="A391" s="3" t="n"/>
@@ -8176,11 +8571,12 @@
       <c r="J391" s="4" t="n"/>
       <c r="K391" s="4" t="n"/>
       <c r="L391" s="4" t="n"/>
-      <c r="M391" s="3" t="n"/>
+      <c r="M391" s="4" t="n"/>
       <c r="N391" s="4" t="n"/>
       <c r="O391" s="4" t="n"/>
       <c r="P391" s="4" t="n"/>
       <c r="Q391" s="4" t="n"/>
+      <c r="R391" s="4" t="n"/>
     </row>
     <row r="392">
       <c r="A392" s="3" t="n"/>
@@ -8195,11 +8591,12 @@
       <c r="J392" s="4" t="n"/>
       <c r="K392" s="4" t="n"/>
       <c r="L392" s="4" t="n"/>
-      <c r="M392" s="3" t="n"/>
+      <c r="M392" s="4" t="n"/>
       <c r="N392" s="4" t="n"/>
       <c r="O392" s="4" t="n"/>
       <c r="P392" s="4" t="n"/>
       <c r="Q392" s="4" t="n"/>
+      <c r="R392" s="4" t="n"/>
     </row>
     <row r="393">
       <c r="A393" s="3" t="n"/>
@@ -8214,11 +8611,12 @@
       <c r="J393" s="4" t="n"/>
       <c r="K393" s="4" t="n"/>
       <c r="L393" s="4" t="n"/>
-      <c r="M393" s="3" t="n"/>
+      <c r="M393" s="4" t="n"/>
       <c r="N393" s="4" t="n"/>
       <c r="O393" s="4" t="n"/>
       <c r="P393" s="4" t="n"/>
       <c r="Q393" s="4" t="n"/>
+      <c r="R393" s="4" t="n"/>
     </row>
     <row r="394">
       <c r="A394" s="3" t="n"/>
@@ -8233,11 +8631,12 @@
       <c r="J394" s="4" t="n"/>
       <c r="K394" s="4" t="n"/>
       <c r="L394" s="4" t="n"/>
-      <c r="M394" s="3" t="n"/>
+      <c r="M394" s="4" t="n"/>
       <c r="N394" s="4" t="n"/>
       <c r="O394" s="4" t="n"/>
       <c r="P394" s="4" t="n"/>
       <c r="Q394" s="4" t="n"/>
+      <c r="R394" s="4" t="n"/>
     </row>
     <row r="395">
       <c r="A395" s="3" t="n"/>
@@ -8252,11 +8651,12 @@
       <c r="J395" s="4" t="n"/>
       <c r="K395" s="4" t="n"/>
       <c r="L395" s="4" t="n"/>
-      <c r="M395" s="3" t="n"/>
+      <c r="M395" s="4" t="n"/>
       <c r="N395" s="4" t="n"/>
       <c r="O395" s="4" t="n"/>
       <c r="P395" s="4" t="n"/>
       <c r="Q395" s="4" t="n"/>
+      <c r="R395" s="4" t="n"/>
     </row>
     <row r="396">
       <c r="A396" s="3" t="n"/>
@@ -8271,11 +8671,12 @@
       <c r="J396" s="4" t="n"/>
       <c r="K396" s="4" t="n"/>
       <c r="L396" s="4" t="n"/>
-      <c r="M396" s="3" t="n"/>
+      <c r="M396" s="4" t="n"/>
       <c r="N396" s="4" t="n"/>
       <c r="O396" s="4" t="n"/>
       <c r="P396" s="4" t="n"/>
       <c r="Q396" s="4" t="n"/>
+      <c r="R396" s="4" t="n"/>
     </row>
     <row r="397">
       <c r="A397" s="3" t="n"/>
@@ -8290,11 +8691,12 @@
       <c r="J397" s="4" t="n"/>
       <c r="K397" s="4" t="n"/>
       <c r="L397" s="4" t="n"/>
-      <c r="M397" s="3" t="n"/>
+      <c r="M397" s="4" t="n"/>
       <c r="N397" s="4" t="n"/>
       <c r="O397" s="4" t="n"/>
       <c r="P397" s="4" t="n"/>
       <c r="Q397" s="4" t="n"/>
+      <c r="R397" s="4" t="n"/>
     </row>
     <row r="398">
       <c r="A398" s="3" t="n"/>
@@ -8309,11 +8711,12 @@
       <c r="J398" s="4" t="n"/>
       <c r="K398" s="4" t="n"/>
       <c r="L398" s="4" t="n"/>
-      <c r="M398" s="3" t="n"/>
+      <c r="M398" s="4" t="n"/>
       <c r="N398" s="4" t="n"/>
       <c r="O398" s="4" t="n"/>
       <c r="P398" s="4" t="n"/>
       <c r="Q398" s="4" t="n"/>
+      <c r="R398" s="4" t="n"/>
     </row>
     <row r="399">
       <c r="A399" s="3" t="n"/>
@@ -8328,14 +8731,15 @@
       <c r="J399" s="4" t="n"/>
       <c r="K399" s="4" t="n"/>
       <c r="L399" s="4" t="n"/>
-      <c r="M399" s="3" t="n"/>
+      <c r="M399" s="4" t="n"/>
       <c r="N399" s="4" t="n"/>
       <c r="O399" s="4" t="n"/>
       <c r="P399" s="4" t="n"/>
       <c r="Q399" s="4" t="n"/>
+      <c r="R399" s="4" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q1"/>
+  <autoFilter ref="A1:R1"/>
   <dataValidations count="4">
     <dataValidation sqref="C2:C399" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not a category" error="Pick one of the listed categories — matching works on this column." type="list">
       <formula1>"bed,sofa,chair,table,desk,wardrobe,storage,lighting,rug,soft-furnishing,decor,appliance"</formula1>
@@ -8343,7 +8747,7 @@
     <dataValidation sqref="E2:E399" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"INR,GBP,USD"</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O399" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="P2:P399" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"yes,no"</formula1>
     </dataValidation>
     <dataValidation sqref="D2:D399 F2:F399 G2:G399 H2:H399" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not a number" error="Must be a positive number — no symbols, no commas." type="decimal" operator="greaterThan">
@@ -8360,7 +8764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -8394,7 +8798,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Do NOT paste pictures into this sheet. Put the WEB ADDRESS of each photo in the image_url column.</t>
+          <t>Do NOT paste pictures into this sheet. Fill in ONE of two columns.</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8806,7 @@
       <c r="A6" s="6" t="inlineStr"/>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>If the photo is already on your website: right-click it, choose 'Copy image address', paste that.</t>
+          <t>image_url — if the photo is already on your website. Right-click it, 'Copy image address', paste that.</t>
         </is>
       </c>
     </row>
@@ -8410,7 +8814,7 @@
       <c r="A7" s="6" t="inlineStr"/>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>If it is only on a computer: put the photos in a Google Drive folder, set the folder to 'Anyone with the link', then copy each file's link.</t>
+          <t>image_file — if the photos are only on a computer. Put them all in one folder, name each file after the product, and put the FILENAME here (hale-wardrobe-2400.jpg). Send the folder with the sheet.</t>
         </is>
       </c>
     </row>
@@ -8418,101 +8822,109 @@
       <c r="A8" s="6" t="inlineStr"/>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>A picture pasted into a cell cannot be read by anything. A link can.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+          <t>Either works. Do not do both for the same row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr"/>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>A picture pasted into a cell floats above the grid, belongs to no row, and cannot be read by anything. A link or a filename can.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>The measurements</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>width_mm, depth_mm and height_mm matter more than any other column. Without them we cannot tell whether a piece fits the wall it is going against, and fitting is the whole point. Millimetres, whole numbers: a 2.4 metre wardrobe is 2400.</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>The yellow cells</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>Yellow means required. A row missing any of those is skipped on import and reported back to you, not silently dropped.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Pick from the drop-down. Free text matches nothing — 'desk' finds the desks, 'Study Table (Wooden)' finds nothing.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>style_tags</t>
+          <t>category</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Comma separated, from the Style list tab. A piece can carry several.</t>
+          <t>Pick from the drop-down. Free text matches nothing — 'desk' finds the desks, 'Study Table (Wooden)' finds nothing.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
+          <t>style_tags</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Comma separated, from the Style list tab. A piece can carry several.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
           <t>room_tags</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>Semicolon separated, from the Room list tab. Semicolons, because room names contain commas.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>How many rows</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>About fifty, spread across every category, beats two thousand wardrobes. Breadth is what makes it work; depth can come later.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>Sending it back</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>File &gt; Download &gt; Comma Separated Values (.csv), or Save As CSV in Excel. Send that file.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>Worth knowing</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>One honest limit: the render is steered towards these pieces, it is not a photograph of them. The design shows something very like the Fenn desk; the product list beside it is the orderable truth.</t>
         </is>
